--- a/data/HAHEBO_leadbestand_pilot.xlsx
+++ b/data/HAHEBO_leadbestand_pilot.xlsx
@@ -712,14 +712,12 @@
           <t>nog niet gecontroleerd</t>
         </is>
       </c>
-      <c r="Y2" s="3" t="inlineStr">
-        <is>
-          <t>15-09-2026</t>
-        </is>
+      <c r="Y2" s="3" t="n">
+        <v>46280</v>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>Segment toegekend op basis van een actuele locatiepagina zonder expliciete peildatum. Het aantal valt met de eigen marge van de bron volledig in het bereik 50 of meer. Eerder gevonden afwijkende cijfers veranderen dit niet: circa 1.400 betreft heel Nederland en valt af op meetniveau, circa 2.100 komt uit een C-bron en wijst dezelfde kant op. Geen algemeen e-mailadres gepubliceerd, alleen een adres voor orderverwerking. Naast het NL-domein bestaat ook een .com-domein.</t>
+          <t>Segment toegekend op basis van een actuele locatiepagina zonder expliciete peildatum. De bron noemt ongeveer 2.000 medewerkers op de locatie; dit ligt eenduidig in het segment 50+. Eerder gevonden afwijkende cijfers veranderen dit niet: circa 1.400 betreft heel Nederland en valt af op meetniveau, circa 2.100 komt uit een C-bron en wijst dezelfde kant op. Geen algemeen e-mailadres gepubliceerd, alleen een adres voor orderverwerking. Naast het NL-domein bestaat ook een .com-domein.</t>
         </is>
       </c>
     </row>
@@ -834,10 +832,8 @@
           <t>nog niet gecontroleerd</t>
         </is>
       </c>
-      <c r="Y3" s="3" t="inlineStr">
-        <is>
-          <t>15-09-2026</t>
-        </is>
+      <c r="Y3" s="3" t="n">
+        <v>46280</v>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
@@ -956,10 +952,8 @@
           <t>nog niet gecontroleerd</t>
         </is>
       </c>
-      <c r="Y4" s="3" t="inlineStr">
-        <is>
-          <t>15-09-2026</t>
-        </is>
+      <c r="Y4" s="3" t="n">
+        <v>46280</v>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
@@ -1078,10 +1072,8 @@
           <t>nog niet gecontroleerd</t>
         </is>
       </c>
-      <c r="Y5" s="3" t="inlineStr">
-        <is>
-          <t>15-09-2026</t>
-        </is>
+      <c r="Y5" s="3" t="n">
+        <v>46280</v>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
@@ -1200,10 +1192,8 @@
           <t>nog niet gecontroleerd</t>
         </is>
       </c>
-      <c r="Y6" s="3" t="inlineStr">
-        <is>
-          <t>15-09-2026</t>
-        </is>
+      <c r="Y6" s="3" t="n">
+        <v>46280</v>
       </c>
       <c r="Z6" t="inlineStr">
         <is>

--- a/data/HAHEBO_leadbestand_pilot.xlsx
+++ b/data/HAHEBO_leadbestand_pilot.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Uitleg" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Leadbestand'!$A$1:$Z$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Leadbestand'!$A$1:$AA$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Uitleg'!$A$1:$B$1</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -438,7 +438,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z500"/>
+  <dimension ref="A1:AA500"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -460,13 +460,14 @@
     <col width="16" customWidth="1" min="17" max="17"/>
     <col width="32" customWidth="1" min="18" max="18"/>
     <col width="16" customWidth="1" min="19" max="19"/>
-    <col width="28" customWidth="1" min="20" max="20"/>
-    <col width="16" customWidth="1" min="21" max="21"/>
-    <col width="20" customWidth="1" min="22" max="22"/>
-    <col width="26" customWidth="1" min="23" max="23"/>
-    <col width="22" customWidth="1" min="24" max="24"/>
-    <col width="16" customWidth="1" min="25" max="25"/>
-    <col width="30" customWidth="1" min="26" max="26"/>
+    <col width="20" customWidth="1" min="20" max="20"/>
+    <col width="28" customWidth="1" min="21" max="21"/>
+    <col width="16" customWidth="1" min="22" max="22"/>
+    <col width="20" customWidth="1" min="23" max="23"/>
+    <col width="26" customWidth="1" min="24" max="24"/>
+    <col width="22" customWidth="1" min="25" max="25"/>
+    <col width="16" customWidth="1" min="26" max="26"/>
+    <col width="30" customWidth="1" min="27" max="27"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -567,35 +568,40 @@
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
+          <t>Doelgroepstatus</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
           <t>Algemeen e-mailadres</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>Telefoonnummer</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>Bron contactgegevens</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>Resultaat vergelijking acquisitielijst</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>Matchwijze acquisitielijst</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>Datum verzameld</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>Opmerkingen</t>
         </is>
@@ -694,28 +700,33 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
+          <t>nog niet te bepalen</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
           <t>Niet gevonden</t>
         </is>
       </c>
-      <c r="U2" s="2" t="inlineStr">
+      <c r="V2" s="2" t="inlineStr">
         <is>
           <t>+31 485 587600</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>https://www.msd-animal-health.nl/contactgegevens/</t>
         </is>
       </c>
-      <c r="W2" t="inlineStr">
+      <c r="X2" t="inlineStr">
         <is>
           <t>nog niet gecontroleerd</t>
         </is>
       </c>
-      <c r="Y2" s="3" t="n">
+      <c r="Z2" s="3" t="n">
         <v>46280</v>
       </c>
-      <c r="Z2" t="inlineStr">
+      <c r="AA2" t="inlineStr">
         <is>
           <t>Segment toegekend op basis van een actuele locatiepagina zonder expliciete peildatum. De bron noemt ongeveer 2.000 medewerkers op de locatie; dit ligt eenduidig in het segment 50+. Eerder gevonden afwijkende cijfers veranderen dit niet: circa 1.400 betreft heel Nederland en valt af op meetniveau, circa 2.100 komt uit een C-bron en wijst dezelfde kant op. Geen algemeen e-mailadres gepubliceerd, alleen een adres voor orderverwerking. Naast het NL-domein bestaat ook een .com-domein.</t>
         </is>
@@ -814,28 +825,33 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
+          <t>nog niet te bepalen</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
           <t>sales@elpress.com</t>
         </is>
       </c>
-      <c r="U3" s="2" t="inlineStr">
+      <c r="V3" s="2" t="inlineStr">
         <is>
           <t>+31 485 51 69 69</t>
         </is>
       </c>
-      <c r="V3" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>https://www.elpress.com/contact</t>
         </is>
       </c>
-      <c r="W3" t="inlineStr">
+      <c r="X3" t="inlineStr">
         <is>
           <t>nog niet gecontroleerd</t>
         </is>
       </c>
-      <c r="Y3" s="3" t="n">
+      <c r="Z3" s="3" t="n">
         <v>46280</v>
       </c>
-      <c r="Z3" t="inlineStr">
+      <c r="AA3" t="inlineStr">
         <is>
           <t>Geen enkel publiek medewerkersgegeven gevonden. Datagat, geen tegenstrijdigheid. KVK-nummer en adres bevestigd op de eigen contactpagina. sales@ is het enige gepubliceerde algemene adres.</t>
         </is>
@@ -934,28 +950,33 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
+          <t>nog niet te bepalen</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
           <t>info@hendrix-genetics.com</t>
         </is>
       </c>
-      <c r="U4" s="2" t="inlineStr">
+      <c r="V4" s="2" t="inlineStr">
         <is>
           <t>+31 485 801 911</t>
         </is>
       </c>
-      <c r="V4" t="inlineStr">
+      <c r="W4" t="inlineStr">
         <is>
           <t>https://www.hendrix-genetics.com/en/about/contact/ en https://dutchpoultrycentre.nl/en/preferred-partners/breeding-hatching/hendrix-genetics</t>
         </is>
       </c>
-      <c r="W4" t="inlineStr">
+      <c r="X4" t="inlineStr">
         <is>
           <t>nog niet gecontroleerd</t>
         </is>
       </c>
-      <c r="Y4" s="3" t="n">
+      <c r="Z4" s="3" t="n">
         <v>46280</v>
       </c>
-      <c r="Z4" t="inlineStr">
+      <c r="AA4" t="inlineStr">
         <is>
           <t>Alleen een C-bron, die bovendien de entiteit betreft en niet de locatie. De klasse 21 tot 50 bevat waarden onder 50 en de waarde 50 zelf, dus ook bij een sterkere bron zou dit een grensgeval blijven. Op hetzelfde adres staan meerdere groepsentiteiten en er is geen bron die het totaal voor de locatie noemt. E-mailadres komt van een derde partij en is niet op de eigen site bevestigd.</t>
         </is>
@@ -1054,28 +1075,33 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
+          <t>nog niet te bepalen</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
           <t>info@paridon-mas.nl</t>
         </is>
       </c>
-      <c r="U5" s="2" t="inlineStr">
+      <c r="V5" s="2" t="inlineStr">
         <is>
           <t>0485 57 83 83</t>
         </is>
       </c>
-      <c r="V5" t="inlineStr">
+      <c r="W5" t="inlineStr">
         <is>
           <t>http://www.paridon-mas.nl/contact.html</t>
         </is>
       </c>
-      <c r="W5" t="inlineStr">
+      <c r="X5" t="inlineStr">
         <is>
           <t>nog niet gecontroleerd</t>
         </is>
       </c>
-      <c r="Y5" s="3" t="n">
+      <c r="Z5" s="3" t="n">
         <v>46280</v>
       </c>
-      <c r="Z5" t="inlineStr">
+      <c r="AA5" t="inlineStr">
         <is>
           <t>Alleen een C-bron. Dezelfde bron noemt zowel 10 werknemers als de klasse 10 tot 19, beide volledig in het bereik 49 of minder, dus geen tegenstrijdigheid. Bij een A- of B-bron zou dit direct tot nog te bepalen leiden. Het bronniveau is hier het knelpunt, niet de grens.</t>
         </is>
@@ -1174,28 +1200,33 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
+          <t>nog niet te bepalen</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
           <t>info@instalplan.nl</t>
         </is>
       </c>
-      <c r="U6" s="2" t="inlineStr">
+      <c r="V6" s="2" t="inlineStr">
         <is>
           <t>+31 6 831 95 313</t>
         </is>
       </c>
-      <c r="V6" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>https://www.instalplan.nl/</t>
         </is>
       </c>
-      <c r="W6" t="inlineStr">
+      <c r="X6" t="inlineStr">
         <is>
           <t>nog niet gecontroleerd</t>
         </is>
       </c>
-      <c r="Y6" s="3" t="n">
+      <c r="Z6" s="3" t="n">
         <v>46280</v>
       </c>
-      <c r="Z6" t="inlineStr">
+      <c r="AA6" t="inlineStr">
         <is>
           <t>Geen KVK-nummer en geen medewerkersgegeven gevonden. Contactgegevens komen rechtstreeks van de eigen website. Telefoonnummer is een mobiel nummer, maar staat als zakelijk contactnummer op de site.</t>
         </is>
@@ -1206,3960 +1237,3960 @@
       <c r="C7" s="2" t="n"/>
       <c r="G7" s="2" t="n"/>
       <c r="M7" s="3" t="n"/>
-      <c r="U7" s="2" t="n"/>
-      <c r="Y7" s="3" t="n"/>
+      <c r="V7" s="2" t="n"/>
+      <c r="Z7" s="3" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n"/>
       <c r="C8" s="2" t="n"/>
       <c r="G8" s="2" t="n"/>
       <c r="M8" s="3" t="n"/>
-      <c r="U8" s="2" t="n"/>
-      <c r="Y8" s="3" t="n"/>
+      <c r="V8" s="2" t="n"/>
+      <c r="Z8" s="3" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n"/>
       <c r="C9" s="2" t="n"/>
       <c r="G9" s="2" t="n"/>
       <c r="M9" s="3" t="n"/>
-      <c r="U9" s="2" t="n"/>
-      <c r="Y9" s="3" t="n"/>
+      <c r="V9" s="2" t="n"/>
+      <c r="Z9" s="3" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n"/>
       <c r="C10" s="2" t="n"/>
       <c r="G10" s="2" t="n"/>
       <c r="M10" s="3" t="n"/>
-      <c r="U10" s="2" t="n"/>
-      <c r="Y10" s="3" t="n"/>
+      <c r="V10" s="2" t="n"/>
+      <c r="Z10" s="3" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n"/>
       <c r="C11" s="2" t="n"/>
       <c r="G11" s="2" t="n"/>
       <c r="M11" s="3" t="n"/>
-      <c r="U11" s="2" t="n"/>
-      <c r="Y11" s="3" t="n"/>
+      <c r="V11" s="2" t="n"/>
+      <c r="Z11" s="3" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n"/>
       <c r="C12" s="2" t="n"/>
       <c r="G12" s="2" t="n"/>
       <c r="M12" s="3" t="n"/>
-      <c r="U12" s="2" t="n"/>
-      <c r="Y12" s="3" t="n"/>
+      <c r="V12" s="2" t="n"/>
+      <c r="Z12" s="3" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n"/>
       <c r="C13" s="2" t="n"/>
       <c r="G13" s="2" t="n"/>
       <c r="M13" s="3" t="n"/>
-      <c r="U13" s="2" t="n"/>
-      <c r="Y13" s="3" t="n"/>
+      <c r="V13" s="2" t="n"/>
+      <c r="Z13" s="3" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n"/>
       <c r="C14" s="2" t="n"/>
       <c r="G14" s="2" t="n"/>
       <c r="M14" s="3" t="n"/>
-      <c r="U14" s="2" t="n"/>
-      <c r="Y14" s="3" t="n"/>
+      <c r="V14" s="2" t="n"/>
+      <c r="Z14" s="3" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n"/>
       <c r="C15" s="2" t="n"/>
       <c r="G15" s="2" t="n"/>
       <c r="M15" s="3" t="n"/>
-      <c r="U15" s="2" t="n"/>
-      <c r="Y15" s="3" t="n"/>
+      <c r="V15" s="2" t="n"/>
+      <c r="Z15" s="3" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n"/>
       <c r="C16" s="2" t="n"/>
       <c r="G16" s="2" t="n"/>
       <c r="M16" s="3" t="n"/>
-      <c r="U16" s="2" t="n"/>
-      <c r="Y16" s="3" t="n"/>
+      <c r="V16" s="2" t="n"/>
+      <c r="Z16" s="3" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n"/>
       <c r="C17" s="2" t="n"/>
       <c r="G17" s="2" t="n"/>
       <c r="M17" s="3" t="n"/>
-      <c r="U17" s="2" t="n"/>
-      <c r="Y17" s="3" t="n"/>
+      <c r="V17" s="2" t="n"/>
+      <c r="Z17" s="3" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n"/>
       <c r="C18" s="2" t="n"/>
       <c r="G18" s="2" t="n"/>
       <c r="M18" s="3" t="n"/>
-      <c r="U18" s="2" t="n"/>
-      <c r="Y18" s="3" t="n"/>
+      <c r="V18" s="2" t="n"/>
+      <c r="Z18" s="3" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n"/>
       <c r="C19" s="2" t="n"/>
       <c r="G19" s="2" t="n"/>
       <c r="M19" s="3" t="n"/>
-      <c r="U19" s="2" t="n"/>
-      <c r="Y19" s="3" t="n"/>
+      <c r="V19" s="2" t="n"/>
+      <c r="Z19" s="3" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n"/>
       <c r="C20" s="2" t="n"/>
       <c r="G20" s="2" t="n"/>
       <c r="M20" s="3" t="n"/>
-      <c r="U20" s="2" t="n"/>
-      <c r="Y20" s="3" t="n"/>
+      <c r="V20" s="2" t="n"/>
+      <c r="Z20" s="3" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="2" t="n"/>
       <c r="C21" s="2" t="n"/>
       <c r="G21" s="2" t="n"/>
       <c r="M21" s="3" t="n"/>
-      <c r="U21" s="2" t="n"/>
-      <c r="Y21" s="3" t="n"/>
+      <c r="V21" s="2" t="n"/>
+      <c r="Z21" s="3" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n"/>
       <c r="C22" s="2" t="n"/>
       <c r="G22" s="2" t="n"/>
       <c r="M22" s="3" t="n"/>
-      <c r="U22" s="2" t="n"/>
-      <c r="Y22" s="3" t="n"/>
+      <c r="V22" s="2" t="n"/>
+      <c r="Z22" s="3" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="2" t="n"/>
       <c r="C23" s="2" t="n"/>
       <c r="G23" s="2" t="n"/>
       <c r="M23" s="3" t="n"/>
-      <c r="U23" s="2" t="n"/>
-      <c r="Y23" s="3" t="n"/>
+      <c r="V23" s="2" t="n"/>
+      <c r="Z23" s="3" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n"/>
       <c r="C24" s="2" t="n"/>
       <c r="G24" s="2" t="n"/>
       <c r="M24" s="3" t="n"/>
-      <c r="U24" s="2" t="n"/>
-      <c r="Y24" s="3" t="n"/>
+      <c r="V24" s="2" t="n"/>
+      <c r="Z24" s="3" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="2" t="n"/>
       <c r="C25" s="2" t="n"/>
       <c r="G25" s="2" t="n"/>
       <c r="M25" s="3" t="n"/>
-      <c r="U25" s="2" t="n"/>
-      <c r="Y25" s="3" t="n"/>
+      <c r="V25" s="2" t="n"/>
+      <c r="Z25" s="3" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n"/>
       <c r="C26" s="2" t="n"/>
       <c r="G26" s="2" t="n"/>
       <c r="M26" s="3" t="n"/>
-      <c r="U26" s="2" t="n"/>
-      <c r="Y26" s="3" t="n"/>
+      <c r="V26" s="2" t="n"/>
+      <c r="Z26" s="3" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="2" t="n"/>
       <c r="C27" s="2" t="n"/>
       <c r="G27" s="2" t="n"/>
       <c r="M27" s="3" t="n"/>
-      <c r="U27" s="2" t="n"/>
-      <c r="Y27" s="3" t="n"/>
+      <c r="V27" s="2" t="n"/>
+      <c r="Z27" s="3" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n"/>
       <c r="C28" s="2" t="n"/>
       <c r="G28" s="2" t="n"/>
       <c r="M28" s="3" t="n"/>
-      <c r="U28" s="2" t="n"/>
-      <c r="Y28" s="3" t="n"/>
+      <c r="V28" s="2" t="n"/>
+      <c r="Z28" s="3" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="2" t="n"/>
       <c r="C29" s="2" t="n"/>
       <c r="G29" s="2" t="n"/>
       <c r="M29" s="3" t="n"/>
-      <c r="U29" s="2" t="n"/>
-      <c r="Y29" s="3" t="n"/>
+      <c r="V29" s="2" t="n"/>
+      <c r="Z29" s="3" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n"/>
       <c r="C30" s="2" t="n"/>
       <c r="G30" s="2" t="n"/>
       <c r="M30" s="3" t="n"/>
-      <c r="U30" s="2" t="n"/>
-      <c r="Y30" s="3" t="n"/>
+      <c r="V30" s="2" t="n"/>
+      <c r="Z30" s="3" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="2" t="n"/>
       <c r="C31" s="2" t="n"/>
       <c r="G31" s="2" t="n"/>
       <c r="M31" s="3" t="n"/>
-      <c r="U31" s="2" t="n"/>
-      <c r="Y31" s="3" t="n"/>
+      <c r="V31" s="2" t="n"/>
+      <c r="Z31" s="3" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n"/>
       <c r="C32" s="2" t="n"/>
       <c r="G32" s="2" t="n"/>
       <c r="M32" s="3" t="n"/>
-      <c r="U32" s="2" t="n"/>
-      <c r="Y32" s="3" t="n"/>
+      <c r="V32" s="2" t="n"/>
+      <c r="Z32" s="3" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="2" t="n"/>
       <c r="C33" s="2" t="n"/>
       <c r="G33" s="2" t="n"/>
       <c r="M33" s="3" t="n"/>
-      <c r="U33" s="2" t="n"/>
-      <c r="Y33" s="3" t="n"/>
+      <c r="V33" s="2" t="n"/>
+      <c r="Z33" s="3" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="2" t="n"/>
       <c r="C34" s="2" t="n"/>
       <c r="G34" s="2" t="n"/>
       <c r="M34" s="3" t="n"/>
-      <c r="U34" s="2" t="n"/>
-      <c r="Y34" s="3" t="n"/>
+      <c r="V34" s="2" t="n"/>
+      <c r="Z34" s="3" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="2" t="n"/>
       <c r="C35" s="2" t="n"/>
       <c r="G35" s="2" t="n"/>
       <c r="M35" s="3" t="n"/>
-      <c r="U35" s="2" t="n"/>
-      <c r="Y35" s="3" t="n"/>
+      <c r="V35" s="2" t="n"/>
+      <c r="Z35" s="3" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="2" t="n"/>
       <c r="C36" s="2" t="n"/>
       <c r="G36" s="2" t="n"/>
       <c r="M36" s="3" t="n"/>
-      <c r="U36" s="2" t="n"/>
-      <c r="Y36" s="3" t="n"/>
+      <c r="V36" s="2" t="n"/>
+      <c r="Z36" s="3" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="2" t="n"/>
       <c r="C37" s="2" t="n"/>
       <c r="G37" s="2" t="n"/>
       <c r="M37" s="3" t="n"/>
-      <c r="U37" s="2" t="n"/>
-      <c r="Y37" s="3" t="n"/>
+      <c r="V37" s="2" t="n"/>
+      <c r="Z37" s="3" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="2" t="n"/>
       <c r="C38" s="2" t="n"/>
       <c r="G38" s="2" t="n"/>
       <c r="M38" s="3" t="n"/>
-      <c r="U38" s="2" t="n"/>
-      <c r="Y38" s="3" t="n"/>
+      <c r="V38" s="2" t="n"/>
+      <c r="Z38" s="3" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="2" t="n"/>
       <c r="C39" s="2" t="n"/>
       <c r="G39" s="2" t="n"/>
       <c r="M39" s="3" t="n"/>
-      <c r="U39" s="2" t="n"/>
-      <c r="Y39" s="3" t="n"/>
+      <c r="V39" s="2" t="n"/>
+      <c r="Z39" s="3" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="2" t="n"/>
       <c r="C40" s="2" t="n"/>
       <c r="G40" s="2" t="n"/>
       <c r="M40" s="3" t="n"/>
-      <c r="U40" s="2" t="n"/>
-      <c r="Y40" s="3" t="n"/>
+      <c r="V40" s="2" t="n"/>
+      <c r="Z40" s="3" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="2" t="n"/>
       <c r="C41" s="2" t="n"/>
       <c r="G41" s="2" t="n"/>
       <c r="M41" s="3" t="n"/>
-      <c r="U41" s="2" t="n"/>
-      <c r="Y41" s="3" t="n"/>
+      <c r="V41" s="2" t="n"/>
+      <c r="Z41" s="3" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="2" t="n"/>
       <c r="C42" s="2" t="n"/>
       <c r="G42" s="2" t="n"/>
       <c r="M42" s="3" t="n"/>
-      <c r="U42" s="2" t="n"/>
-      <c r="Y42" s="3" t="n"/>
+      <c r="V42" s="2" t="n"/>
+      <c r="Z42" s="3" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="2" t="n"/>
       <c r="C43" s="2" t="n"/>
       <c r="G43" s="2" t="n"/>
       <c r="M43" s="3" t="n"/>
-      <c r="U43" s="2" t="n"/>
-      <c r="Y43" s="3" t="n"/>
+      <c r="V43" s="2" t="n"/>
+      <c r="Z43" s="3" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="2" t="n"/>
       <c r="C44" s="2" t="n"/>
       <c r="G44" s="2" t="n"/>
       <c r="M44" s="3" t="n"/>
-      <c r="U44" s="2" t="n"/>
-      <c r="Y44" s="3" t="n"/>
+      <c r="V44" s="2" t="n"/>
+      <c r="Z44" s="3" t="n"/>
     </row>
     <row r="45">
       <c r="A45" s="2" t="n"/>
       <c r="C45" s="2" t="n"/>
       <c r="G45" s="2" t="n"/>
       <c r="M45" s="3" t="n"/>
-      <c r="U45" s="2" t="n"/>
-      <c r="Y45" s="3" t="n"/>
+      <c r="V45" s="2" t="n"/>
+      <c r="Z45" s="3" t="n"/>
     </row>
     <row r="46">
       <c r="A46" s="2" t="n"/>
       <c r="C46" s="2" t="n"/>
       <c r="G46" s="2" t="n"/>
       <c r="M46" s="3" t="n"/>
-      <c r="U46" s="2" t="n"/>
-      <c r="Y46" s="3" t="n"/>
+      <c r="V46" s="2" t="n"/>
+      <c r="Z46" s="3" t="n"/>
     </row>
     <row r="47">
       <c r="A47" s="2" t="n"/>
       <c r="C47" s="2" t="n"/>
       <c r="G47" s="2" t="n"/>
       <c r="M47" s="3" t="n"/>
-      <c r="U47" s="2" t="n"/>
-      <c r="Y47" s="3" t="n"/>
+      <c r="V47" s="2" t="n"/>
+      <c r="Z47" s="3" t="n"/>
     </row>
     <row r="48">
       <c r="A48" s="2" t="n"/>
       <c r="C48" s="2" t="n"/>
       <c r="G48" s="2" t="n"/>
       <c r="M48" s="3" t="n"/>
-      <c r="U48" s="2" t="n"/>
-      <c r="Y48" s="3" t="n"/>
+      <c r="V48" s="2" t="n"/>
+      <c r="Z48" s="3" t="n"/>
     </row>
     <row r="49">
       <c r="A49" s="2" t="n"/>
       <c r="C49" s="2" t="n"/>
       <c r="G49" s="2" t="n"/>
       <c r="M49" s="3" t="n"/>
-      <c r="U49" s="2" t="n"/>
-      <c r="Y49" s="3" t="n"/>
+      <c r="V49" s="2" t="n"/>
+      <c r="Z49" s="3" t="n"/>
     </row>
     <row r="50">
       <c r="A50" s="2" t="n"/>
       <c r="C50" s="2" t="n"/>
       <c r="G50" s="2" t="n"/>
       <c r="M50" s="3" t="n"/>
-      <c r="U50" s="2" t="n"/>
-      <c r="Y50" s="3" t="n"/>
+      <c r="V50" s="2" t="n"/>
+      <c r="Z50" s="3" t="n"/>
     </row>
     <row r="51">
       <c r="A51" s="2" t="n"/>
       <c r="C51" s="2" t="n"/>
       <c r="G51" s="2" t="n"/>
       <c r="M51" s="3" t="n"/>
-      <c r="U51" s="2" t="n"/>
-      <c r="Y51" s="3" t="n"/>
+      <c r="V51" s="2" t="n"/>
+      <c r="Z51" s="3" t="n"/>
     </row>
     <row r="52">
       <c r="A52" s="2" t="n"/>
       <c r="C52" s="2" t="n"/>
       <c r="G52" s="2" t="n"/>
       <c r="M52" s="3" t="n"/>
-      <c r="U52" s="2" t="n"/>
-      <c r="Y52" s="3" t="n"/>
+      <c r="V52" s="2" t="n"/>
+      <c r="Z52" s="3" t="n"/>
     </row>
     <row r="53">
       <c r="A53" s="2" t="n"/>
       <c r="C53" s="2" t="n"/>
       <c r="G53" s="2" t="n"/>
       <c r="M53" s="3" t="n"/>
-      <c r="U53" s="2" t="n"/>
-      <c r="Y53" s="3" t="n"/>
+      <c r="V53" s="2" t="n"/>
+      <c r="Z53" s="3" t="n"/>
     </row>
     <row r="54">
       <c r="A54" s="2" t="n"/>
       <c r="C54" s="2" t="n"/>
       <c r="G54" s="2" t="n"/>
       <c r="M54" s="3" t="n"/>
-      <c r="U54" s="2" t="n"/>
-      <c r="Y54" s="3" t="n"/>
+      <c r="V54" s="2" t="n"/>
+      <c r="Z54" s="3" t="n"/>
     </row>
     <row r="55">
       <c r="A55" s="2" t="n"/>
       <c r="C55" s="2" t="n"/>
       <c r="G55" s="2" t="n"/>
       <c r="M55" s="3" t="n"/>
-      <c r="U55" s="2" t="n"/>
-      <c r="Y55" s="3" t="n"/>
+      <c r="V55" s="2" t="n"/>
+      <c r="Z55" s="3" t="n"/>
     </row>
     <row r="56">
       <c r="A56" s="2" t="n"/>
       <c r="C56" s="2" t="n"/>
       <c r="G56" s="2" t="n"/>
       <c r="M56" s="3" t="n"/>
-      <c r="U56" s="2" t="n"/>
-      <c r="Y56" s="3" t="n"/>
+      <c r="V56" s="2" t="n"/>
+      <c r="Z56" s="3" t="n"/>
     </row>
     <row r="57">
       <c r="A57" s="2" t="n"/>
       <c r="C57" s="2" t="n"/>
       <c r="G57" s="2" t="n"/>
       <c r="M57" s="3" t="n"/>
-      <c r="U57" s="2" t="n"/>
-      <c r="Y57" s="3" t="n"/>
+      <c r="V57" s="2" t="n"/>
+      <c r="Z57" s="3" t="n"/>
     </row>
     <row r="58">
       <c r="A58" s="2" t="n"/>
       <c r="C58" s="2" t="n"/>
       <c r="G58" s="2" t="n"/>
       <c r="M58" s="3" t="n"/>
-      <c r="U58" s="2" t="n"/>
-      <c r="Y58" s="3" t="n"/>
+      <c r="V58" s="2" t="n"/>
+      <c r="Z58" s="3" t="n"/>
     </row>
     <row r="59">
       <c r="A59" s="2" t="n"/>
       <c r="C59" s="2" t="n"/>
       <c r="G59" s="2" t="n"/>
       <c r="M59" s="3" t="n"/>
-      <c r="U59" s="2" t="n"/>
-      <c r="Y59" s="3" t="n"/>
+      <c r="V59" s="2" t="n"/>
+      <c r="Z59" s="3" t="n"/>
     </row>
     <row r="60">
       <c r="A60" s="2" t="n"/>
       <c r="C60" s="2" t="n"/>
       <c r="G60" s="2" t="n"/>
       <c r="M60" s="3" t="n"/>
-      <c r="U60" s="2" t="n"/>
-      <c r="Y60" s="3" t="n"/>
+      <c r="V60" s="2" t="n"/>
+      <c r="Z60" s="3" t="n"/>
     </row>
     <row r="61">
       <c r="A61" s="2" t="n"/>
       <c r="C61" s="2" t="n"/>
       <c r="G61" s="2" t="n"/>
       <c r="M61" s="3" t="n"/>
-      <c r="U61" s="2" t="n"/>
-      <c r="Y61" s="3" t="n"/>
+      <c r="V61" s="2" t="n"/>
+      <c r="Z61" s="3" t="n"/>
     </row>
     <row r="62">
       <c r="A62" s="2" t="n"/>
       <c r="C62" s="2" t="n"/>
       <c r="G62" s="2" t="n"/>
       <c r="M62" s="3" t="n"/>
-      <c r="U62" s="2" t="n"/>
-      <c r="Y62" s="3" t="n"/>
+      <c r="V62" s="2" t="n"/>
+      <c r="Z62" s="3" t="n"/>
     </row>
     <row r="63">
       <c r="A63" s="2" t="n"/>
       <c r="C63" s="2" t="n"/>
       <c r="G63" s="2" t="n"/>
       <c r="M63" s="3" t="n"/>
-      <c r="U63" s="2" t="n"/>
-      <c r="Y63" s="3" t="n"/>
+      <c r="V63" s="2" t="n"/>
+      <c r="Z63" s="3" t="n"/>
     </row>
     <row r="64">
       <c r="A64" s="2" t="n"/>
       <c r="C64" s="2" t="n"/>
       <c r="G64" s="2" t="n"/>
       <c r="M64" s="3" t="n"/>
-      <c r="U64" s="2" t="n"/>
-      <c r="Y64" s="3" t="n"/>
+      <c r="V64" s="2" t="n"/>
+      <c r="Z64" s="3" t="n"/>
     </row>
     <row r="65">
       <c r="A65" s="2" t="n"/>
       <c r="C65" s="2" t="n"/>
       <c r="G65" s="2" t="n"/>
       <c r="M65" s="3" t="n"/>
-      <c r="U65" s="2" t="n"/>
-      <c r="Y65" s="3" t="n"/>
+      <c r="V65" s="2" t="n"/>
+      <c r="Z65" s="3" t="n"/>
     </row>
     <row r="66">
       <c r="A66" s="2" t="n"/>
       <c r="C66" s="2" t="n"/>
       <c r="G66" s="2" t="n"/>
       <c r="M66" s="3" t="n"/>
-      <c r="U66" s="2" t="n"/>
-      <c r="Y66" s="3" t="n"/>
+      <c r="V66" s="2" t="n"/>
+      <c r="Z66" s="3" t="n"/>
     </row>
     <row r="67">
       <c r="A67" s="2" t="n"/>
       <c r="C67" s="2" t="n"/>
       <c r="G67" s="2" t="n"/>
       <c r="M67" s="3" t="n"/>
-      <c r="U67" s="2" t="n"/>
-      <c r="Y67" s="3" t="n"/>
+      <c r="V67" s="2" t="n"/>
+      <c r="Z67" s="3" t="n"/>
     </row>
     <row r="68">
       <c r="A68" s="2" t="n"/>
       <c r="C68" s="2" t="n"/>
       <c r="G68" s="2" t="n"/>
       <c r="M68" s="3" t="n"/>
-      <c r="U68" s="2" t="n"/>
-      <c r="Y68" s="3" t="n"/>
+      <c r="V68" s="2" t="n"/>
+      <c r="Z68" s="3" t="n"/>
     </row>
     <row r="69">
       <c r="A69" s="2" t="n"/>
       <c r="C69" s="2" t="n"/>
       <c r="G69" s="2" t="n"/>
       <c r="M69" s="3" t="n"/>
-      <c r="U69" s="2" t="n"/>
-      <c r="Y69" s="3" t="n"/>
+      <c r="V69" s="2" t="n"/>
+      <c r="Z69" s="3" t="n"/>
     </row>
     <row r="70">
       <c r="A70" s="2" t="n"/>
       <c r="C70" s="2" t="n"/>
       <c r="G70" s="2" t="n"/>
       <c r="M70" s="3" t="n"/>
-      <c r="U70" s="2" t="n"/>
-      <c r="Y70" s="3" t="n"/>
+      <c r="V70" s="2" t="n"/>
+      <c r="Z70" s="3" t="n"/>
     </row>
     <row r="71">
       <c r="A71" s="2" t="n"/>
       <c r="C71" s="2" t="n"/>
       <c r="G71" s="2" t="n"/>
       <c r="M71" s="3" t="n"/>
-      <c r="U71" s="2" t="n"/>
-      <c r="Y71" s="3" t="n"/>
+      <c r="V71" s="2" t="n"/>
+      <c r="Z71" s="3" t="n"/>
     </row>
     <row r="72">
       <c r="A72" s="2" t="n"/>
       <c r="C72" s="2" t="n"/>
       <c r="G72" s="2" t="n"/>
       <c r="M72" s="3" t="n"/>
-      <c r="U72" s="2" t="n"/>
-      <c r="Y72" s="3" t="n"/>
+      <c r="V72" s="2" t="n"/>
+      <c r="Z72" s="3" t="n"/>
     </row>
     <row r="73">
       <c r="A73" s="2" t="n"/>
       <c r="C73" s="2" t="n"/>
       <c r="G73" s="2" t="n"/>
       <c r="M73" s="3" t="n"/>
-      <c r="U73" s="2" t="n"/>
-      <c r="Y73" s="3" t="n"/>
+      <c r="V73" s="2" t="n"/>
+      <c r="Z73" s="3" t="n"/>
     </row>
     <row r="74">
       <c r="A74" s="2" t="n"/>
       <c r="C74" s="2" t="n"/>
       <c r="G74" s="2" t="n"/>
       <c r="M74" s="3" t="n"/>
-      <c r="U74" s="2" t="n"/>
-      <c r="Y74" s="3" t="n"/>
+      <c r="V74" s="2" t="n"/>
+      <c r="Z74" s="3" t="n"/>
     </row>
     <row r="75">
       <c r="A75" s="2" t="n"/>
       <c r="C75" s="2" t="n"/>
       <c r="G75" s="2" t="n"/>
       <c r="M75" s="3" t="n"/>
-      <c r="U75" s="2" t="n"/>
-      <c r="Y75" s="3" t="n"/>
+      <c r="V75" s="2" t="n"/>
+      <c r="Z75" s="3" t="n"/>
     </row>
     <row r="76">
       <c r="A76" s="2" t="n"/>
       <c r="C76" s="2" t="n"/>
       <c r="G76" s="2" t="n"/>
       <c r="M76" s="3" t="n"/>
-      <c r="U76" s="2" t="n"/>
-      <c r="Y76" s="3" t="n"/>
+      <c r="V76" s="2" t="n"/>
+      <c r="Z76" s="3" t="n"/>
     </row>
     <row r="77">
       <c r="A77" s="2" t="n"/>
       <c r="C77" s="2" t="n"/>
       <c r="G77" s="2" t="n"/>
       <c r="M77" s="3" t="n"/>
-      <c r="U77" s="2" t="n"/>
-      <c r="Y77" s="3" t="n"/>
+      <c r="V77" s="2" t="n"/>
+      <c r="Z77" s="3" t="n"/>
     </row>
     <row r="78">
       <c r="A78" s="2" t="n"/>
       <c r="C78" s="2" t="n"/>
       <c r="G78" s="2" t="n"/>
       <c r="M78" s="3" t="n"/>
-      <c r="U78" s="2" t="n"/>
-      <c r="Y78" s="3" t="n"/>
+      <c r="V78" s="2" t="n"/>
+      <c r="Z78" s="3" t="n"/>
     </row>
     <row r="79">
       <c r="A79" s="2" t="n"/>
       <c r="C79" s="2" t="n"/>
       <c r="G79" s="2" t="n"/>
       <c r="M79" s="3" t="n"/>
-      <c r="U79" s="2" t="n"/>
-      <c r="Y79" s="3" t="n"/>
+      <c r="V79" s="2" t="n"/>
+      <c r="Z79" s="3" t="n"/>
     </row>
     <row r="80">
       <c r="A80" s="2" t="n"/>
       <c r="C80" s="2" t="n"/>
       <c r="G80" s="2" t="n"/>
       <c r="M80" s="3" t="n"/>
-      <c r="U80" s="2" t="n"/>
-      <c r="Y80" s="3" t="n"/>
+      <c r="V80" s="2" t="n"/>
+      <c r="Z80" s="3" t="n"/>
     </row>
     <row r="81">
       <c r="A81" s="2" t="n"/>
       <c r="C81" s="2" t="n"/>
       <c r="G81" s="2" t="n"/>
       <c r="M81" s="3" t="n"/>
-      <c r="U81" s="2" t="n"/>
-      <c r="Y81" s="3" t="n"/>
+      <c r="V81" s="2" t="n"/>
+      <c r="Z81" s="3" t="n"/>
     </row>
     <row r="82">
       <c r="A82" s="2" t="n"/>
       <c r="C82" s="2" t="n"/>
       <c r="G82" s="2" t="n"/>
       <c r="M82" s="3" t="n"/>
-      <c r="U82" s="2" t="n"/>
-      <c r="Y82" s="3" t="n"/>
+      <c r="V82" s="2" t="n"/>
+      <c r="Z82" s="3" t="n"/>
     </row>
     <row r="83">
       <c r="A83" s="2" t="n"/>
       <c r="C83" s="2" t="n"/>
       <c r="G83" s="2" t="n"/>
       <c r="M83" s="3" t="n"/>
-      <c r="U83" s="2" t="n"/>
-      <c r="Y83" s="3" t="n"/>
+      <c r="V83" s="2" t="n"/>
+      <c r="Z83" s="3" t="n"/>
     </row>
     <row r="84">
       <c r="A84" s="2" t="n"/>
       <c r="C84" s="2" t="n"/>
       <c r="G84" s="2" t="n"/>
       <c r="M84" s="3" t="n"/>
-      <c r="U84" s="2" t="n"/>
-      <c r="Y84" s="3" t="n"/>
+      <c r="V84" s="2" t="n"/>
+      <c r="Z84" s="3" t="n"/>
     </row>
     <row r="85">
       <c r="A85" s="2" t="n"/>
       <c r="C85" s="2" t="n"/>
       <c r="G85" s="2" t="n"/>
       <c r="M85" s="3" t="n"/>
-      <c r="U85" s="2" t="n"/>
-      <c r="Y85" s="3" t="n"/>
+      <c r="V85" s="2" t="n"/>
+      <c r="Z85" s="3" t="n"/>
     </row>
     <row r="86">
       <c r="A86" s="2" t="n"/>
       <c r="C86" s="2" t="n"/>
       <c r="G86" s="2" t="n"/>
       <c r="M86" s="3" t="n"/>
-      <c r="U86" s="2" t="n"/>
-      <c r="Y86" s="3" t="n"/>
+      <c r="V86" s="2" t="n"/>
+      <c r="Z86" s="3" t="n"/>
     </row>
     <row r="87">
       <c r="A87" s="2" t="n"/>
       <c r="C87" s="2" t="n"/>
       <c r="G87" s="2" t="n"/>
       <c r="M87" s="3" t="n"/>
-      <c r="U87" s="2" t="n"/>
-      <c r="Y87" s="3" t="n"/>
+      <c r="V87" s="2" t="n"/>
+      <c r="Z87" s="3" t="n"/>
     </row>
     <row r="88">
       <c r="A88" s="2" t="n"/>
       <c r="C88" s="2" t="n"/>
       <c r="G88" s="2" t="n"/>
       <c r="M88" s="3" t="n"/>
-      <c r="U88" s="2" t="n"/>
-      <c r="Y88" s="3" t="n"/>
+      <c r="V88" s="2" t="n"/>
+      <c r="Z88" s="3" t="n"/>
     </row>
     <row r="89">
       <c r="A89" s="2" t="n"/>
       <c r="C89" s="2" t="n"/>
       <c r="G89" s="2" t="n"/>
       <c r="M89" s="3" t="n"/>
-      <c r="U89" s="2" t="n"/>
-      <c r="Y89" s="3" t="n"/>
+      <c r="V89" s="2" t="n"/>
+      <c r="Z89" s="3" t="n"/>
     </row>
     <row r="90">
       <c r="A90" s="2" t="n"/>
       <c r="C90" s="2" t="n"/>
       <c r="G90" s="2" t="n"/>
       <c r="M90" s="3" t="n"/>
-      <c r="U90" s="2" t="n"/>
-      <c r="Y90" s="3" t="n"/>
+      <c r="V90" s="2" t="n"/>
+      <c r="Z90" s="3" t="n"/>
     </row>
     <row r="91">
       <c r="A91" s="2" t="n"/>
       <c r="C91" s="2" t="n"/>
       <c r="G91" s="2" t="n"/>
       <c r="M91" s="3" t="n"/>
-      <c r="U91" s="2" t="n"/>
-      <c r="Y91" s="3" t="n"/>
+      <c r="V91" s="2" t="n"/>
+      <c r="Z91" s="3" t="n"/>
     </row>
     <row r="92">
       <c r="A92" s="2" t="n"/>
       <c r="C92" s="2" t="n"/>
       <c r="G92" s="2" t="n"/>
       <c r="M92" s="3" t="n"/>
-      <c r="U92" s="2" t="n"/>
-      <c r="Y92" s="3" t="n"/>
+      <c r="V92" s="2" t="n"/>
+      <c r="Z92" s="3" t="n"/>
     </row>
     <row r="93">
       <c r="A93" s="2" t="n"/>
       <c r="C93" s="2" t="n"/>
       <c r="G93" s="2" t="n"/>
       <c r="M93" s="3" t="n"/>
-      <c r="U93" s="2" t="n"/>
-      <c r="Y93" s="3" t="n"/>
+      <c r="V93" s="2" t="n"/>
+      <c r="Z93" s="3" t="n"/>
     </row>
     <row r="94">
       <c r="A94" s="2" t="n"/>
       <c r="C94" s="2" t="n"/>
       <c r="G94" s="2" t="n"/>
       <c r="M94" s="3" t="n"/>
-      <c r="U94" s="2" t="n"/>
-      <c r="Y94" s="3" t="n"/>
+      <c r="V94" s="2" t="n"/>
+      <c r="Z94" s="3" t="n"/>
     </row>
     <row r="95">
       <c r="A95" s="2" t="n"/>
       <c r="C95" s="2" t="n"/>
       <c r="G95" s="2" t="n"/>
       <c r="M95" s="3" t="n"/>
-      <c r="U95" s="2" t="n"/>
-      <c r="Y95" s="3" t="n"/>
+      <c r="V95" s="2" t="n"/>
+      <c r="Z95" s="3" t="n"/>
     </row>
     <row r="96">
       <c r="A96" s="2" t="n"/>
       <c r="C96" s="2" t="n"/>
       <c r="G96" s="2" t="n"/>
       <c r="M96" s="3" t="n"/>
-      <c r="U96" s="2" t="n"/>
-      <c r="Y96" s="3" t="n"/>
+      <c r="V96" s="2" t="n"/>
+      <c r="Z96" s="3" t="n"/>
     </row>
     <row r="97">
       <c r="A97" s="2" t="n"/>
       <c r="C97" s="2" t="n"/>
       <c r="G97" s="2" t="n"/>
       <c r="M97" s="3" t="n"/>
-      <c r="U97" s="2" t="n"/>
-      <c r="Y97" s="3" t="n"/>
+      <c r="V97" s="2" t="n"/>
+      <c r="Z97" s="3" t="n"/>
     </row>
     <row r="98">
       <c r="A98" s="2" t="n"/>
       <c r="C98" s="2" t="n"/>
       <c r="G98" s="2" t="n"/>
       <c r="M98" s="3" t="n"/>
-      <c r="U98" s="2" t="n"/>
-      <c r="Y98" s="3" t="n"/>
+      <c r="V98" s="2" t="n"/>
+      <c r="Z98" s="3" t="n"/>
     </row>
     <row r="99">
       <c r="A99" s="2" t="n"/>
       <c r="C99" s="2" t="n"/>
       <c r="G99" s="2" t="n"/>
       <c r="M99" s="3" t="n"/>
-      <c r="U99" s="2" t="n"/>
-      <c r="Y99" s="3" t="n"/>
+      <c r="V99" s="2" t="n"/>
+      <c r="Z99" s="3" t="n"/>
     </row>
     <row r="100">
       <c r="A100" s="2" t="n"/>
       <c r="C100" s="2" t="n"/>
       <c r="G100" s="2" t="n"/>
       <c r="M100" s="3" t="n"/>
-      <c r="U100" s="2" t="n"/>
-      <c r="Y100" s="3" t="n"/>
+      <c r="V100" s="2" t="n"/>
+      <c r="Z100" s="3" t="n"/>
     </row>
     <row r="101">
       <c r="A101" s="2" t="n"/>
       <c r="C101" s="2" t="n"/>
       <c r="G101" s="2" t="n"/>
       <c r="M101" s="3" t="n"/>
-      <c r="U101" s="2" t="n"/>
-      <c r="Y101" s="3" t="n"/>
+      <c r="V101" s="2" t="n"/>
+      <c r="Z101" s="3" t="n"/>
     </row>
     <row r="102">
       <c r="A102" s="2" t="n"/>
       <c r="C102" s="2" t="n"/>
       <c r="G102" s="2" t="n"/>
       <c r="M102" s="3" t="n"/>
-      <c r="U102" s="2" t="n"/>
-      <c r="Y102" s="3" t="n"/>
+      <c r="V102" s="2" t="n"/>
+      <c r="Z102" s="3" t="n"/>
     </row>
     <row r="103">
       <c r="A103" s="2" t="n"/>
       <c r="C103" s="2" t="n"/>
       <c r="G103" s="2" t="n"/>
       <c r="M103" s="3" t="n"/>
-      <c r="U103" s="2" t="n"/>
-      <c r="Y103" s="3" t="n"/>
+      <c r="V103" s="2" t="n"/>
+      <c r="Z103" s="3" t="n"/>
     </row>
     <row r="104">
       <c r="A104" s="2" t="n"/>
       <c r="C104" s="2" t="n"/>
       <c r="G104" s="2" t="n"/>
       <c r="M104" s="3" t="n"/>
-      <c r="U104" s="2" t="n"/>
-      <c r="Y104" s="3" t="n"/>
+      <c r="V104" s="2" t="n"/>
+      <c r="Z104" s="3" t="n"/>
     </row>
     <row r="105">
       <c r="A105" s="2" t="n"/>
       <c r="C105" s="2" t="n"/>
       <c r="G105" s="2" t="n"/>
       <c r="M105" s="3" t="n"/>
-      <c r="U105" s="2" t="n"/>
-      <c r="Y105" s="3" t="n"/>
+      <c r="V105" s="2" t="n"/>
+      <c r="Z105" s="3" t="n"/>
     </row>
     <row r="106">
       <c r="A106" s="2" t="n"/>
       <c r="C106" s="2" t="n"/>
       <c r="G106" s="2" t="n"/>
       <c r="M106" s="3" t="n"/>
-      <c r="U106" s="2" t="n"/>
-      <c r="Y106" s="3" t="n"/>
+      <c r="V106" s="2" t="n"/>
+      <c r="Z106" s="3" t="n"/>
     </row>
     <row r="107">
       <c r="A107" s="2" t="n"/>
       <c r="C107" s="2" t="n"/>
       <c r="G107" s="2" t="n"/>
       <c r="M107" s="3" t="n"/>
-      <c r="U107" s="2" t="n"/>
-      <c r="Y107" s="3" t="n"/>
+      <c r="V107" s="2" t="n"/>
+      <c r="Z107" s="3" t="n"/>
     </row>
     <row r="108">
       <c r="A108" s="2" t="n"/>
       <c r="C108" s="2" t="n"/>
       <c r="G108" s="2" t="n"/>
       <c r="M108" s="3" t="n"/>
-      <c r="U108" s="2" t="n"/>
-      <c r="Y108" s="3" t="n"/>
+      <c r="V108" s="2" t="n"/>
+      <c r="Z108" s="3" t="n"/>
     </row>
     <row r="109">
       <c r="A109" s="2" t="n"/>
       <c r="C109" s="2" t="n"/>
       <c r="G109" s="2" t="n"/>
       <c r="M109" s="3" t="n"/>
-      <c r="U109" s="2" t="n"/>
-      <c r="Y109" s="3" t="n"/>
+      <c r="V109" s="2" t="n"/>
+      <c r="Z109" s="3" t="n"/>
     </row>
     <row r="110">
       <c r="A110" s="2" t="n"/>
       <c r="C110" s="2" t="n"/>
       <c r="G110" s="2" t="n"/>
       <c r="M110" s="3" t="n"/>
-      <c r="U110" s="2" t="n"/>
-      <c r="Y110" s="3" t="n"/>
+      <c r="V110" s="2" t="n"/>
+      <c r="Z110" s="3" t="n"/>
     </row>
     <row r="111">
       <c r="A111" s="2" t="n"/>
       <c r="C111" s="2" t="n"/>
       <c r="G111" s="2" t="n"/>
       <c r="M111" s="3" t="n"/>
-      <c r="U111" s="2" t="n"/>
-      <c r="Y111" s="3" t="n"/>
+      <c r="V111" s="2" t="n"/>
+      <c r="Z111" s="3" t="n"/>
     </row>
     <row r="112">
       <c r="A112" s="2" t="n"/>
       <c r="C112" s="2" t="n"/>
       <c r="G112" s="2" t="n"/>
       <c r="M112" s="3" t="n"/>
-      <c r="U112" s="2" t="n"/>
-      <c r="Y112" s="3" t="n"/>
+      <c r="V112" s="2" t="n"/>
+      <c r="Z112" s="3" t="n"/>
     </row>
     <row r="113">
       <c r="A113" s="2" t="n"/>
       <c r="C113" s="2" t="n"/>
       <c r="G113" s="2" t="n"/>
       <c r="M113" s="3" t="n"/>
-      <c r="U113" s="2" t="n"/>
-      <c r="Y113" s="3" t="n"/>
+      <c r="V113" s="2" t="n"/>
+      <c r="Z113" s="3" t="n"/>
     </row>
     <row r="114">
       <c r="A114" s="2" t="n"/>
       <c r="C114" s="2" t="n"/>
       <c r="G114" s="2" t="n"/>
       <c r="M114" s="3" t="n"/>
-      <c r="U114" s="2" t="n"/>
-      <c r="Y114" s="3" t="n"/>
+      <c r="V114" s="2" t="n"/>
+      <c r="Z114" s="3" t="n"/>
     </row>
     <row r="115">
       <c r="A115" s="2" t="n"/>
       <c r="C115" s="2" t="n"/>
       <c r="G115" s="2" t="n"/>
       <c r="M115" s="3" t="n"/>
-      <c r="U115" s="2" t="n"/>
-      <c r="Y115" s="3" t="n"/>
+      <c r="V115" s="2" t="n"/>
+      <c r="Z115" s="3" t="n"/>
     </row>
     <row r="116">
       <c r="A116" s="2" t="n"/>
       <c r="C116" s="2" t="n"/>
       <c r="G116" s="2" t="n"/>
       <c r="M116" s="3" t="n"/>
-      <c r="U116" s="2" t="n"/>
-      <c r="Y116" s="3" t="n"/>
+      <c r="V116" s="2" t="n"/>
+      <c r="Z116" s="3" t="n"/>
     </row>
     <row r="117">
       <c r="A117" s="2" t="n"/>
       <c r="C117" s="2" t="n"/>
       <c r="G117" s="2" t="n"/>
       <c r="M117" s="3" t="n"/>
-      <c r="U117" s="2" t="n"/>
-      <c r="Y117" s="3" t="n"/>
+      <c r="V117" s="2" t="n"/>
+      <c r="Z117" s="3" t="n"/>
     </row>
     <row r="118">
       <c r="A118" s="2" t="n"/>
       <c r="C118" s="2" t="n"/>
       <c r="G118" s="2" t="n"/>
       <c r="M118" s="3" t="n"/>
-      <c r="U118" s="2" t="n"/>
-      <c r="Y118" s="3" t="n"/>
+      <c r="V118" s="2" t="n"/>
+      <c r="Z118" s="3" t="n"/>
     </row>
     <row r="119">
       <c r="A119" s="2" t="n"/>
       <c r="C119" s="2" t="n"/>
       <c r="G119" s="2" t="n"/>
       <c r="M119" s="3" t="n"/>
-      <c r="U119" s="2" t="n"/>
-      <c r="Y119" s="3" t="n"/>
+      <c r="V119" s="2" t="n"/>
+      <c r="Z119" s="3" t="n"/>
     </row>
     <row r="120">
       <c r="A120" s="2" t="n"/>
       <c r="C120" s="2" t="n"/>
       <c r="G120" s="2" t="n"/>
       <c r="M120" s="3" t="n"/>
-      <c r="U120" s="2" t="n"/>
-      <c r="Y120" s="3" t="n"/>
+      <c r="V120" s="2" t="n"/>
+      <c r="Z120" s="3" t="n"/>
     </row>
     <row r="121">
       <c r="A121" s="2" t="n"/>
       <c r="C121" s="2" t="n"/>
       <c r="G121" s="2" t="n"/>
       <c r="M121" s="3" t="n"/>
-      <c r="U121" s="2" t="n"/>
-      <c r="Y121" s="3" t="n"/>
+      <c r="V121" s="2" t="n"/>
+      <c r="Z121" s="3" t="n"/>
     </row>
     <row r="122">
       <c r="A122" s="2" t="n"/>
       <c r="C122" s="2" t="n"/>
       <c r="G122" s="2" t="n"/>
       <c r="M122" s="3" t="n"/>
-      <c r="U122" s="2" t="n"/>
-      <c r="Y122" s="3" t="n"/>
+      <c r="V122" s="2" t="n"/>
+      <c r="Z122" s="3" t="n"/>
     </row>
     <row r="123">
       <c r="A123" s="2" t="n"/>
       <c r="C123" s="2" t="n"/>
       <c r="G123" s="2" t="n"/>
       <c r="M123" s="3" t="n"/>
-      <c r="U123" s="2" t="n"/>
-      <c r="Y123" s="3" t="n"/>
+      <c r="V123" s="2" t="n"/>
+      <c r="Z123" s="3" t="n"/>
     </row>
     <row r="124">
       <c r="A124" s="2" t="n"/>
       <c r="C124" s="2" t="n"/>
       <c r="G124" s="2" t="n"/>
       <c r="M124" s="3" t="n"/>
-      <c r="U124" s="2" t="n"/>
-      <c r="Y124" s="3" t="n"/>
+      <c r="V124" s="2" t="n"/>
+      <c r="Z124" s="3" t="n"/>
     </row>
     <row r="125">
       <c r="A125" s="2" t="n"/>
       <c r="C125" s="2" t="n"/>
       <c r="G125" s="2" t="n"/>
       <c r="M125" s="3" t="n"/>
-      <c r="U125" s="2" t="n"/>
-      <c r="Y125" s="3" t="n"/>
+      <c r="V125" s="2" t="n"/>
+      <c r="Z125" s="3" t="n"/>
     </row>
     <row r="126">
       <c r="A126" s="2" t="n"/>
       <c r="C126" s="2" t="n"/>
       <c r="G126" s="2" t="n"/>
       <c r="M126" s="3" t="n"/>
-      <c r="U126" s="2" t="n"/>
-      <c r="Y126" s="3" t="n"/>
+      <c r="V126" s="2" t="n"/>
+      <c r="Z126" s="3" t="n"/>
     </row>
     <row r="127">
       <c r="A127" s="2" t="n"/>
       <c r="C127" s="2" t="n"/>
       <c r="G127" s="2" t="n"/>
       <c r="M127" s="3" t="n"/>
-      <c r="U127" s="2" t="n"/>
-      <c r="Y127" s="3" t="n"/>
+      <c r="V127" s="2" t="n"/>
+      <c r="Z127" s="3" t="n"/>
     </row>
     <row r="128">
       <c r="A128" s="2" t="n"/>
       <c r="C128" s="2" t="n"/>
       <c r="G128" s="2" t="n"/>
       <c r="M128" s="3" t="n"/>
-      <c r="U128" s="2" t="n"/>
-      <c r="Y128" s="3" t="n"/>
+      <c r="V128" s="2" t="n"/>
+      <c r="Z128" s="3" t="n"/>
     </row>
     <row r="129">
       <c r="A129" s="2" t="n"/>
       <c r="C129" s="2" t="n"/>
       <c r="G129" s="2" t="n"/>
       <c r="M129" s="3" t="n"/>
-      <c r="U129" s="2" t="n"/>
-      <c r="Y129" s="3" t="n"/>
+      <c r="V129" s="2" t="n"/>
+      <c r="Z129" s="3" t="n"/>
     </row>
     <row r="130">
       <c r="A130" s="2" t="n"/>
       <c r="C130" s="2" t="n"/>
       <c r="G130" s="2" t="n"/>
       <c r="M130" s="3" t="n"/>
-      <c r="U130" s="2" t="n"/>
-      <c r="Y130" s="3" t="n"/>
+      <c r="V130" s="2" t="n"/>
+      <c r="Z130" s="3" t="n"/>
     </row>
     <row r="131">
       <c r="A131" s="2" t="n"/>
       <c r="C131" s="2" t="n"/>
       <c r="G131" s="2" t="n"/>
       <c r="M131" s="3" t="n"/>
-      <c r="U131" s="2" t="n"/>
-      <c r="Y131" s="3" t="n"/>
+      <c r="V131" s="2" t="n"/>
+      <c r="Z131" s="3" t="n"/>
     </row>
     <row r="132">
       <c r="A132" s="2" t="n"/>
       <c r="C132" s="2" t="n"/>
       <c r="G132" s="2" t="n"/>
       <c r="M132" s="3" t="n"/>
-      <c r="U132" s="2" t="n"/>
-      <c r="Y132" s="3" t="n"/>
+      <c r="V132" s="2" t="n"/>
+      <c r="Z132" s="3" t="n"/>
     </row>
     <row r="133">
       <c r="A133" s="2" t="n"/>
       <c r="C133" s="2" t="n"/>
       <c r="G133" s="2" t="n"/>
       <c r="M133" s="3" t="n"/>
-      <c r="U133" s="2" t="n"/>
-      <c r="Y133" s="3" t="n"/>
+      <c r="V133" s="2" t="n"/>
+      <c r="Z133" s="3" t="n"/>
     </row>
     <row r="134">
       <c r="A134" s="2" t="n"/>
       <c r="C134" s="2" t="n"/>
       <c r="G134" s="2" t="n"/>
       <c r="M134" s="3" t="n"/>
-      <c r="U134" s="2" t="n"/>
-      <c r="Y134" s="3" t="n"/>
+      <c r="V134" s="2" t="n"/>
+      <c r="Z134" s="3" t="n"/>
     </row>
     <row r="135">
       <c r="A135" s="2" t="n"/>
       <c r="C135" s="2" t="n"/>
       <c r="G135" s="2" t="n"/>
       <c r="M135" s="3" t="n"/>
-      <c r="U135" s="2" t="n"/>
-      <c r="Y135" s="3" t="n"/>
+      <c r="V135" s="2" t="n"/>
+      <c r="Z135" s="3" t="n"/>
     </row>
     <row r="136">
       <c r="A136" s="2" t="n"/>
       <c r="C136" s="2" t="n"/>
       <c r="G136" s="2" t="n"/>
       <c r="M136" s="3" t="n"/>
-      <c r="U136" s="2" t="n"/>
-      <c r="Y136" s="3" t="n"/>
+      <c r="V136" s="2" t="n"/>
+      <c r="Z136" s="3" t="n"/>
     </row>
     <row r="137">
       <c r="A137" s="2" t="n"/>
       <c r="C137" s="2" t="n"/>
       <c r="G137" s="2" t="n"/>
       <c r="M137" s="3" t="n"/>
-      <c r="U137" s="2" t="n"/>
-      <c r="Y137" s="3" t="n"/>
+      <c r="V137" s="2" t="n"/>
+      <c r="Z137" s="3" t="n"/>
     </row>
     <row r="138">
       <c r="A138" s="2" t="n"/>
       <c r="C138" s="2" t="n"/>
       <c r="G138" s="2" t="n"/>
       <c r="M138" s="3" t="n"/>
-      <c r="U138" s="2" t="n"/>
-      <c r="Y138" s="3" t="n"/>
+      <c r="V138" s="2" t="n"/>
+      <c r="Z138" s="3" t="n"/>
     </row>
     <row r="139">
       <c r="A139" s="2" t="n"/>
       <c r="C139" s="2" t="n"/>
       <c r="G139" s="2" t="n"/>
       <c r="M139" s="3" t="n"/>
-      <c r="U139" s="2" t="n"/>
-      <c r="Y139" s="3" t="n"/>
+      <c r="V139" s="2" t="n"/>
+      <c r="Z139" s="3" t="n"/>
     </row>
     <row r="140">
       <c r="A140" s="2" t="n"/>
       <c r="C140" s="2" t="n"/>
       <c r="G140" s="2" t="n"/>
       <c r="M140" s="3" t="n"/>
-      <c r="U140" s="2" t="n"/>
-      <c r="Y140" s="3" t="n"/>
+      <c r="V140" s="2" t="n"/>
+      <c r="Z140" s="3" t="n"/>
     </row>
     <row r="141">
       <c r="A141" s="2" t="n"/>
       <c r="C141" s="2" t="n"/>
       <c r="G141" s="2" t="n"/>
       <c r="M141" s="3" t="n"/>
-      <c r="U141" s="2" t="n"/>
-      <c r="Y141" s="3" t="n"/>
+      <c r="V141" s="2" t="n"/>
+      <c r="Z141" s="3" t="n"/>
     </row>
     <row r="142">
       <c r="A142" s="2" t="n"/>
       <c r="C142" s="2" t="n"/>
       <c r="G142" s="2" t="n"/>
       <c r="M142" s="3" t="n"/>
-      <c r="U142" s="2" t="n"/>
-      <c r="Y142" s="3" t="n"/>
+      <c r="V142" s="2" t="n"/>
+      <c r="Z142" s="3" t="n"/>
     </row>
     <row r="143">
       <c r="A143" s="2" t="n"/>
       <c r="C143" s="2" t="n"/>
       <c r="G143" s="2" t="n"/>
       <c r="M143" s="3" t="n"/>
-      <c r="U143" s="2" t="n"/>
-      <c r="Y143" s="3" t="n"/>
+      <c r="V143" s="2" t="n"/>
+      <c r="Z143" s="3" t="n"/>
     </row>
     <row r="144">
       <c r="A144" s="2" t="n"/>
       <c r="C144" s="2" t="n"/>
       <c r="G144" s="2" t="n"/>
       <c r="M144" s="3" t="n"/>
-      <c r="U144" s="2" t="n"/>
-      <c r="Y144" s="3" t="n"/>
+      <c r="V144" s="2" t="n"/>
+      <c r="Z144" s="3" t="n"/>
     </row>
     <row r="145">
       <c r="A145" s="2" t="n"/>
       <c r="C145" s="2" t="n"/>
       <c r="G145" s="2" t="n"/>
       <c r="M145" s="3" t="n"/>
-      <c r="U145" s="2" t="n"/>
-      <c r="Y145" s="3" t="n"/>
+      <c r="V145" s="2" t="n"/>
+      <c r="Z145" s="3" t="n"/>
     </row>
     <row r="146">
       <c r="A146" s="2" t="n"/>
       <c r="C146" s="2" t="n"/>
       <c r="G146" s="2" t="n"/>
       <c r="M146" s="3" t="n"/>
-      <c r="U146" s="2" t="n"/>
-      <c r="Y146" s="3" t="n"/>
+      <c r="V146" s="2" t="n"/>
+      <c r="Z146" s="3" t="n"/>
     </row>
     <row r="147">
       <c r="A147" s="2" t="n"/>
       <c r="C147" s="2" t="n"/>
       <c r="G147" s="2" t="n"/>
       <c r="M147" s="3" t="n"/>
-      <c r="U147" s="2" t="n"/>
-      <c r="Y147" s="3" t="n"/>
+      <c r="V147" s="2" t="n"/>
+      <c r="Z147" s="3" t="n"/>
     </row>
     <row r="148">
       <c r="A148" s="2" t="n"/>
       <c r="C148" s="2" t="n"/>
       <c r="G148" s="2" t="n"/>
       <c r="M148" s="3" t="n"/>
-      <c r="U148" s="2" t="n"/>
-      <c r="Y148" s="3" t="n"/>
+      <c r="V148" s="2" t="n"/>
+      <c r="Z148" s="3" t="n"/>
     </row>
     <row r="149">
       <c r="A149" s="2" t="n"/>
       <c r="C149" s="2" t="n"/>
       <c r="G149" s="2" t="n"/>
       <c r="M149" s="3" t="n"/>
-      <c r="U149" s="2" t="n"/>
-      <c r="Y149" s="3" t="n"/>
+      <c r="V149" s="2" t="n"/>
+      <c r="Z149" s="3" t="n"/>
     </row>
     <row r="150">
       <c r="A150" s="2" t="n"/>
       <c r="C150" s="2" t="n"/>
       <c r="G150" s="2" t="n"/>
       <c r="M150" s="3" t="n"/>
-      <c r="U150" s="2" t="n"/>
-      <c r="Y150" s="3" t="n"/>
+      <c r="V150" s="2" t="n"/>
+      <c r="Z150" s="3" t="n"/>
     </row>
     <row r="151">
       <c r="A151" s="2" t="n"/>
       <c r="C151" s="2" t="n"/>
       <c r="G151" s="2" t="n"/>
       <c r="M151" s="3" t="n"/>
-      <c r="U151" s="2" t="n"/>
-      <c r="Y151" s="3" t="n"/>
+      <c r="V151" s="2" t="n"/>
+      <c r="Z151" s="3" t="n"/>
     </row>
     <row r="152">
       <c r="A152" s="2" t="n"/>
       <c r="C152" s="2" t="n"/>
       <c r="G152" s="2" t="n"/>
       <c r="M152" s="3" t="n"/>
-      <c r="U152" s="2" t="n"/>
-      <c r="Y152" s="3" t="n"/>
+      <c r="V152" s="2" t="n"/>
+      <c r="Z152" s="3" t="n"/>
     </row>
     <row r="153">
       <c r="A153" s="2" t="n"/>
       <c r="C153" s="2" t="n"/>
       <c r="G153" s="2" t="n"/>
       <c r="M153" s="3" t="n"/>
-      <c r="U153" s="2" t="n"/>
-      <c r="Y153" s="3" t="n"/>
+      <c r="V153" s="2" t="n"/>
+      <c r="Z153" s="3" t="n"/>
     </row>
     <row r="154">
       <c r="A154" s="2" t="n"/>
       <c r="C154" s="2" t="n"/>
       <c r="G154" s="2" t="n"/>
       <c r="M154" s="3" t="n"/>
-      <c r="U154" s="2" t="n"/>
-      <c r="Y154" s="3" t="n"/>
+      <c r="V154" s="2" t="n"/>
+      <c r="Z154" s="3" t="n"/>
     </row>
     <row r="155">
       <c r="A155" s="2" t="n"/>
       <c r="C155" s="2" t="n"/>
       <c r="G155" s="2" t="n"/>
       <c r="M155" s="3" t="n"/>
-      <c r="U155" s="2" t="n"/>
-      <c r="Y155" s="3" t="n"/>
+      <c r="V155" s="2" t="n"/>
+      <c r="Z155" s="3" t="n"/>
     </row>
     <row r="156">
       <c r="A156" s="2" t="n"/>
       <c r="C156" s="2" t="n"/>
       <c r="G156" s="2" t="n"/>
       <c r="M156" s="3" t="n"/>
-      <c r="U156" s="2" t="n"/>
-      <c r="Y156" s="3" t="n"/>
+      <c r="V156" s="2" t="n"/>
+      <c r="Z156" s="3" t="n"/>
     </row>
     <row r="157">
       <c r="A157" s="2" t="n"/>
       <c r="C157" s="2" t="n"/>
       <c r="G157" s="2" t="n"/>
       <c r="M157" s="3" t="n"/>
-      <c r="U157" s="2" t="n"/>
-      <c r="Y157" s="3" t="n"/>
+      <c r="V157" s="2" t="n"/>
+      <c r="Z157" s="3" t="n"/>
     </row>
     <row r="158">
       <c r="A158" s="2" t="n"/>
       <c r="C158" s="2" t="n"/>
       <c r="G158" s="2" t="n"/>
       <c r="M158" s="3" t="n"/>
-      <c r="U158" s="2" t="n"/>
-      <c r="Y158" s="3" t="n"/>
+      <c r="V158" s="2" t="n"/>
+      <c r="Z158" s="3" t="n"/>
     </row>
     <row r="159">
       <c r="A159" s="2" t="n"/>
       <c r="C159" s="2" t="n"/>
       <c r="G159" s="2" t="n"/>
       <c r="M159" s="3" t="n"/>
-      <c r="U159" s="2" t="n"/>
-      <c r="Y159" s="3" t="n"/>
+      <c r="V159" s="2" t="n"/>
+      <c r="Z159" s="3" t="n"/>
     </row>
     <row r="160">
       <c r="A160" s="2" t="n"/>
       <c r="C160" s="2" t="n"/>
       <c r="G160" s="2" t="n"/>
       <c r="M160" s="3" t="n"/>
-      <c r="U160" s="2" t="n"/>
-      <c r="Y160" s="3" t="n"/>
+      <c r="V160" s="2" t="n"/>
+      <c r="Z160" s="3" t="n"/>
     </row>
     <row r="161">
       <c r="A161" s="2" t="n"/>
       <c r="C161" s="2" t="n"/>
       <c r="G161" s="2" t="n"/>
       <c r="M161" s="3" t="n"/>
-      <c r="U161" s="2" t="n"/>
-      <c r="Y161" s="3" t="n"/>
+      <c r="V161" s="2" t="n"/>
+      <c r="Z161" s="3" t="n"/>
     </row>
     <row r="162">
       <c r="A162" s="2" t="n"/>
       <c r="C162" s="2" t="n"/>
       <c r="G162" s="2" t="n"/>
       <c r="M162" s="3" t="n"/>
-      <c r="U162" s="2" t="n"/>
-      <c r="Y162" s="3" t="n"/>
+      <c r="V162" s="2" t="n"/>
+      <c r="Z162" s="3" t="n"/>
     </row>
     <row r="163">
       <c r="A163" s="2" t="n"/>
       <c r="C163" s="2" t="n"/>
       <c r="G163" s="2" t="n"/>
       <c r="M163" s="3" t="n"/>
-      <c r="U163" s="2" t="n"/>
-      <c r="Y163" s="3" t="n"/>
+      <c r="V163" s="2" t="n"/>
+      <c r="Z163" s="3" t="n"/>
     </row>
     <row r="164">
       <c r="A164" s="2" t="n"/>
       <c r="C164" s="2" t="n"/>
       <c r="G164" s="2" t="n"/>
       <c r="M164" s="3" t="n"/>
-      <c r="U164" s="2" t="n"/>
-      <c r="Y164" s="3" t="n"/>
+      <c r="V164" s="2" t="n"/>
+      <c r="Z164" s="3" t="n"/>
     </row>
     <row r="165">
       <c r="A165" s="2" t="n"/>
       <c r="C165" s="2" t="n"/>
       <c r="G165" s="2" t="n"/>
       <c r="M165" s="3" t="n"/>
-      <c r="U165" s="2" t="n"/>
-      <c r="Y165" s="3" t="n"/>
+      <c r="V165" s="2" t="n"/>
+      <c r="Z165" s="3" t="n"/>
     </row>
     <row r="166">
       <c r="A166" s="2" t="n"/>
       <c r="C166" s="2" t="n"/>
       <c r="G166" s="2" t="n"/>
       <c r="M166" s="3" t="n"/>
-      <c r="U166" s="2" t="n"/>
-      <c r="Y166" s="3" t="n"/>
+      <c r="V166" s="2" t="n"/>
+      <c r="Z166" s="3" t="n"/>
     </row>
     <row r="167">
       <c r="A167" s="2" t="n"/>
       <c r="C167" s="2" t="n"/>
       <c r="G167" s="2" t="n"/>
       <c r="M167" s="3" t="n"/>
-      <c r="U167" s="2" t="n"/>
-      <c r="Y167" s="3" t="n"/>
+      <c r="V167" s="2" t="n"/>
+      <c r="Z167" s="3" t="n"/>
     </row>
     <row r="168">
       <c r="A168" s="2" t="n"/>
       <c r="C168" s="2" t="n"/>
       <c r="G168" s="2" t="n"/>
       <c r="M168" s="3" t="n"/>
-      <c r="U168" s="2" t="n"/>
-      <c r="Y168" s="3" t="n"/>
+      <c r="V168" s="2" t="n"/>
+      <c r="Z168" s="3" t="n"/>
     </row>
     <row r="169">
       <c r="A169" s="2" t="n"/>
       <c r="C169" s="2" t="n"/>
       <c r="G169" s="2" t="n"/>
       <c r="M169" s="3" t="n"/>
-      <c r="U169" s="2" t="n"/>
-      <c r="Y169" s="3" t="n"/>
+      <c r="V169" s="2" t="n"/>
+      <c r="Z169" s="3" t="n"/>
     </row>
     <row r="170">
       <c r="A170" s="2" t="n"/>
       <c r="C170" s="2" t="n"/>
       <c r="G170" s="2" t="n"/>
       <c r="M170" s="3" t="n"/>
-      <c r="U170" s="2" t="n"/>
-      <c r="Y170" s="3" t="n"/>
+      <c r="V170" s="2" t="n"/>
+      <c r="Z170" s="3" t="n"/>
     </row>
     <row r="171">
       <c r="A171" s="2" t="n"/>
       <c r="C171" s="2" t="n"/>
       <c r="G171" s="2" t="n"/>
       <c r="M171" s="3" t="n"/>
-      <c r="U171" s="2" t="n"/>
-      <c r="Y171" s="3" t="n"/>
+      <c r="V171" s="2" t="n"/>
+      <c r="Z171" s="3" t="n"/>
     </row>
     <row r="172">
       <c r="A172" s="2" t="n"/>
       <c r="C172" s="2" t="n"/>
       <c r="G172" s="2" t="n"/>
       <c r="M172" s="3" t="n"/>
-      <c r="U172" s="2" t="n"/>
-      <c r="Y172" s="3" t="n"/>
+      <c r="V172" s="2" t="n"/>
+      <c r="Z172" s="3" t="n"/>
     </row>
     <row r="173">
       <c r="A173" s="2" t="n"/>
       <c r="C173" s="2" t="n"/>
       <c r="G173" s="2" t="n"/>
       <c r="M173" s="3" t="n"/>
-      <c r="U173" s="2" t="n"/>
-      <c r="Y173" s="3" t="n"/>
+      <c r="V173" s="2" t="n"/>
+      <c r="Z173" s="3" t="n"/>
     </row>
     <row r="174">
       <c r="A174" s="2" t="n"/>
       <c r="C174" s="2" t="n"/>
       <c r="G174" s="2" t="n"/>
       <c r="M174" s="3" t="n"/>
-      <c r="U174" s="2" t="n"/>
-      <c r="Y174" s="3" t="n"/>
+      <c r="V174" s="2" t="n"/>
+      <c r="Z174" s="3" t="n"/>
     </row>
     <row r="175">
       <c r="A175" s="2" t="n"/>
       <c r="C175" s="2" t="n"/>
       <c r="G175" s="2" t="n"/>
       <c r="M175" s="3" t="n"/>
-      <c r="U175" s="2" t="n"/>
-      <c r="Y175" s="3" t="n"/>
+      <c r="V175" s="2" t="n"/>
+      <c r="Z175" s="3" t="n"/>
     </row>
     <row r="176">
       <c r="A176" s="2" t="n"/>
       <c r="C176" s="2" t="n"/>
       <c r="G176" s="2" t="n"/>
       <c r="M176" s="3" t="n"/>
-      <c r="U176" s="2" t="n"/>
-      <c r="Y176" s="3" t="n"/>
+      <c r="V176" s="2" t="n"/>
+      <c r="Z176" s="3" t="n"/>
     </row>
     <row r="177">
       <c r="A177" s="2" t="n"/>
       <c r="C177" s="2" t="n"/>
       <c r="G177" s="2" t="n"/>
       <c r="M177" s="3" t="n"/>
-      <c r="U177" s="2" t="n"/>
-      <c r="Y177" s="3" t="n"/>
+      <c r="V177" s="2" t="n"/>
+      <c r="Z177" s="3" t="n"/>
     </row>
     <row r="178">
       <c r="A178" s="2" t="n"/>
       <c r="C178" s="2" t="n"/>
       <c r="G178" s="2" t="n"/>
       <c r="M178" s="3" t="n"/>
-      <c r="U178" s="2" t="n"/>
-      <c r="Y178" s="3" t="n"/>
+      <c r="V178" s="2" t="n"/>
+      <c r="Z178" s="3" t="n"/>
     </row>
     <row r="179">
       <c r="A179" s="2" t="n"/>
       <c r="C179" s="2" t="n"/>
       <c r="G179" s="2" t="n"/>
       <c r="M179" s="3" t="n"/>
-      <c r="U179" s="2" t="n"/>
-      <c r="Y179" s="3" t="n"/>
+      <c r="V179" s="2" t="n"/>
+      <c r="Z179" s="3" t="n"/>
     </row>
     <row r="180">
       <c r="A180" s="2" t="n"/>
       <c r="C180" s="2" t="n"/>
       <c r="G180" s="2" t="n"/>
       <c r="M180" s="3" t="n"/>
-      <c r="U180" s="2" t="n"/>
-      <c r="Y180" s="3" t="n"/>
+      <c r="V180" s="2" t="n"/>
+      <c r="Z180" s="3" t="n"/>
     </row>
     <row r="181">
       <c r="A181" s="2" t="n"/>
       <c r="C181" s="2" t="n"/>
       <c r="G181" s="2" t="n"/>
       <c r="M181" s="3" t="n"/>
-      <c r="U181" s="2" t="n"/>
-      <c r="Y181" s="3" t="n"/>
+      <c r="V181" s="2" t="n"/>
+      <c r="Z181" s="3" t="n"/>
     </row>
     <row r="182">
       <c r="A182" s="2" t="n"/>
       <c r="C182" s="2" t="n"/>
       <c r="G182" s="2" t="n"/>
       <c r="M182" s="3" t="n"/>
-      <c r="U182" s="2" t="n"/>
-      <c r="Y182" s="3" t="n"/>
+      <c r="V182" s="2" t="n"/>
+      <c r="Z182" s="3" t="n"/>
     </row>
     <row r="183">
       <c r="A183" s="2" t="n"/>
       <c r="C183" s="2" t="n"/>
       <c r="G183" s="2" t="n"/>
       <c r="M183" s="3" t="n"/>
-      <c r="U183" s="2" t="n"/>
-      <c r="Y183" s="3" t="n"/>
+      <c r="V183" s="2" t="n"/>
+      <c r="Z183" s="3" t="n"/>
     </row>
     <row r="184">
       <c r="A184" s="2" t="n"/>
       <c r="C184" s="2" t="n"/>
       <c r="G184" s="2" t="n"/>
       <c r="M184" s="3" t="n"/>
-      <c r="U184" s="2" t="n"/>
-      <c r="Y184" s="3" t="n"/>
+      <c r="V184" s="2" t="n"/>
+      <c r="Z184" s="3" t="n"/>
     </row>
     <row r="185">
       <c r="A185" s="2" t="n"/>
       <c r="C185" s="2" t="n"/>
       <c r="G185" s="2" t="n"/>
       <c r="M185" s="3" t="n"/>
-      <c r="U185" s="2" t="n"/>
-      <c r="Y185" s="3" t="n"/>
+      <c r="V185" s="2" t="n"/>
+      <c r="Z185" s="3" t="n"/>
     </row>
     <row r="186">
       <c r="A186" s="2" t="n"/>
       <c r="C186" s="2" t="n"/>
       <c r="G186" s="2" t="n"/>
       <c r="M186" s="3" t="n"/>
-      <c r="U186" s="2" t="n"/>
-      <c r="Y186" s="3" t="n"/>
+      <c r="V186" s="2" t="n"/>
+      <c r="Z186" s="3" t="n"/>
     </row>
     <row r="187">
       <c r="A187" s="2" t="n"/>
       <c r="C187" s="2" t="n"/>
       <c r="G187" s="2" t="n"/>
       <c r="M187" s="3" t="n"/>
-      <c r="U187" s="2" t="n"/>
-      <c r="Y187" s="3" t="n"/>
+      <c r="V187" s="2" t="n"/>
+      <c r="Z187" s="3" t="n"/>
     </row>
     <row r="188">
       <c r="A188" s="2" t="n"/>
       <c r="C188" s="2" t="n"/>
       <c r="G188" s="2" t="n"/>
       <c r="M188" s="3" t="n"/>
-      <c r="U188" s="2" t="n"/>
-      <c r="Y188" s="3" t="n"/>
+      <c r="V188" s="2" t="n"/>
+      <c r="Z188" s="3" t="n"/>
     </row>
     <row r="189">
       <c r="A189" s="2" t="n"/>
       <c r="C189" s="2" t="n"/>
       <c r="G189" s="2" t="n"/>
       <c r="M189" s="3" t="n"/>
-      <c r="U189" s="2" t="n"/>
-      <c r="Y189" s="3" t="n"/>
+      <c r="V189" s="2" t="n"/>
+      <c r="Z189" s="3" t="n"/>
     </row>
     <row r="190">
       <c r="A190" s="2" t="n"/>
       <c r="C190" s="2" t="n"/>
       <c r="G190" s="2" t="n"/>
       <c r="M190" s="3" t="n"/>
-      <c r="U190" s="2" t="n"/>
-      <c r="Y190" s="3" t="n"/>
+      <c r="V190" s="2" t="n"/>
+      <c r="Z190" s="3" t="n"/>
     </row>
     <row r="191">
       <c r="A191" s="2" t="n"/>
       <c r="C191" s="2" t="n"/>
       <c r="G191" s="2" t="n"/>
       <c r="M191" s="3" t="n"/>
-      <c r="U191" s="2" t="n"/>
-      <c r="Y191" s="3" t="n"/>
+      <c r="V191" s="2" t="n"/>
+      <c r="Z191" s="3" t="n"/>
     </row>
     <row r="192">
       <c r="A192" s="2" t="n"/>
       <c r="C192" s="2" t="n"/>
       <c r="G192" s="2" t="n"/>
       <c r="M192" s="3" t="n"/>
-      <c r="U192" s="2" t="n"/>
-      <c r="Y192" s="3" t="n"/>
+      <c r="V192" s="2" t="n"/>
+      <c r="Z192" s="3" t="n"/>
     </row>
     <row r="193">
       <c r="A193" s="2" t="n"/>
       <c r="C193" s="2" t="n"/>
       <c r="G193" s="2" t="n"/>
       <c r="M193" s="3" t="n"/>
-      <c r="U193" s="2" t="n"/>
-      <c r="Y193" s="3" t="n"/>
+      <c r="V193" s="2" t="n"/>
+      <c r="Z193" s="3" t="n"/>
     </row>
     <row r="194">
       <c r="A194" s="2" t="n"/>
       <c r="C194" s="2" t="n"/>
       <c r="G194" s="2" t="n"/>
       <c r="M194" s="3" t="n"/>
-      <c r="U194" s="2" t="n"/>
-      <c r="Y194" s="3" t="n"/>
+      <c r="V194" s="2" t="n"/>
+      <c r="Z194" s="3" t="n"/>
     </row>
     <row r="195">
       <c r="A195" s="2" t="n"/>
       <c r="C195" s="2" t="n"/>
       <c r="G195" s="2" t="n"/>
       <c r="M195" s="3" t="n"/>
-      <c r="U195" s="2" t="n"/>
-      <c r="Y195" s="3" t="n"/>
+      <c r="V195" s="2" t="n"/>
+      <c r="Z195" s="3" t="n"/>
     </row>
     <row r="196">
       <c r="A196" s="2" t="n"/>
       <c r="C196" s="2" t="n"/>
       <c r="G196" s="2" t="n"/>
       <c r="M196" s="3" t="n"/>
-      <c r="U196" s="2" t="n"/>
-      <c r="Y196" s="3" t="n"/>
+      <c r="V196" s="2" t="n"/>
+      <c r="Z196" s="3" t="n"/>
     </row>
     <row r="197">
       <c r="A197" s="2" t="n"/>
       <c r="C197" s="2" t="n"/>
       <c r="G197" s="2" t="n"/>
       <c r="M197" s="3" t="n"/>
-      <c r="U197" s="2" t="n"/>
-      <c r="Y197" s="3" t="n"/>
+      <c r="V197" s="2" t="n"/>
+      <c r="Z197" s="3" t="n"/>
     </row>
     <row r="198">
       <c r="A198" s="2" t="n"/>
       <c r="C198" s="2" t="n"/>
       <c r="G198" s="2" t="n"/>
       <c r="M198" s="3" t="n"/>
-      <c r="U198" s="2" t="n"/>
-      <c r="Y198" s="3" t="n"/>
+      <c r="V198" s="2" t="n"/>
+      <c r="Z198" s="3" t="n"/>
     </row>
     <row r="199">
       <c r="A199" s="2" t="n"/>
       <c r="C199" s="2" t="n"/>
       <c r="G199" s="2" t="n"/>
       <c r="M199" s="3" t="n"/>
-      <c r="U199" s="2" t="n"/>
-      <c r="Y199" s="3" t="n"/>
+      <c r="V199" s="2" t="n"/>
+      <c r="Z199" s="3" t="n"/>
     </row>
     <row r="200">
       <c r="A200" s="2" t="n"/>
       <c r="C200" s="2" t="n"/>
       <c r="G200" s="2" t="n"/>
       <c r="M200" s="3" t="n"/>
-      <c r="U200" s="2" t="n"/>
-      <c r="Y200" s="3" t="n"/>
+      <c r="V200" s="2" t="n"/>
+      <c r="Z200" s="3" t="n"/>
     </row>
     <row r="201">
       <c r="A201" s="2" t="n"/>
       <c r="C201" s="2" t="n"/>
       <c r="G201" s="2" t="n"/>
       <c r="M201" s="3" t="n"/>
-      <c r="U201" s="2" t="n"/>
-      <c r="Y201" s="3" t="n"/>
+      <c r="V201" s="2" t="n"/>
+      <c r="Z201" s="3" t="n"/>
     </row>
     <row r="202">
       <c r="A202" s="2" t="n"/>
       <c r="C202" s="2" t="n"/>
       <c r="G202" s="2" t="n"/>
       <c r="M202" s="3" t="n"/>
-      <c r="U202" s="2" t="n"/>
-      <c r="Y202" s="3" t="n"/>
+      <c r="V202" s="2" t="n"/>
+      <c r="Z202" s="3" t="n"/>
     </row>
     <row r="203">
       <c r="A203" s="2" t="n"/>
       <c r="C203" s="2" t="n"/>
       <c r="G203" s="2" t="n"/>
       <c r="M203" s="3" t="n"/>
-      <c r="U203" s="2" t="n"/>
-      <c r="Y203" s="3" t="n"/>
+      <c r="V203" s="2" t="n"/>
+      <c r="Z203" s="3" t="n"/>
     </row>
     <row r="204">
       <c r="A204" s="2" t="n"/>
       <c r="C204" s="2" t="n"/>
       <c r="G204" s="2" t="n"/>
       <c r="M204" s="3" t="n"/>
-      <c r="U204" s="2" t="n"/>
-      <c r="Y204" s="3" t="n"/>
+      <c r="V204" s="2" t="n"/>
+      <c r="Z204" s="3" t="n"/>
     </row>
     <row r="205">
       <c r="A205" s="2" t="n"/>
       <c r="C205" s="2" t="n"/>
       <c r="G205" s="2" t="n"/>
       <c r="M205" s="3" t="n"/>
-      <c r="U205" s="2" t="n"/>
-      <c r="Y205" s="3" t="n"/>
+      <c r="V205" s="2" t="n"/>
+      <c r="Z205" s="3" t="n"/>
     </row>
     <row r="206">
       <c r="A206" s="2" t="n"/>
       <c r="C206" s="2" t="n"/>
       <c r="G206" s="2" t="n"/>
       <c r="M206" s="3" t="n"/>
-      <c r="U206" s="2" t="n"/>
-      <c r="Y206" s="3" t="n"/>
+      <c r="V206" s="2" t="n"/>
+      <c r="Z206" s="3" t="n"/>
     </row>
     <row r="207">
       <c r="A207" s="2" t="n"/>
       <c r="C207" s="2" t="n"/>
       <c r="G207" s="2" t="n"/>
       <c r="M207" s="3" t="n"/>
-      <c r="U207" s="2" t="n"/>
-      <c r="Y207" s="3" t="n"/>
+      <c r="V207" s="2" t="n"/>
+      <c r="Z207" s="3" t="n"/>
     </row>
     <row r="208">
       <c r="A208" s="2" t="n"/>
       <c r="C208" s="2" t="n"/>
       <c r="G208" s="2" t="n"/>
       <c r="M208" s="3" t="n"/>
-      <c r="U208" s="2" t="n"/>
-      <c r="Y208" s="3" t="n"/>
+      <c r="V208" s="2" t="n"/>
+      <c r="Z208" s="3" t="n"/>
     </row>
     <row r="209">
       <c r="A209" s="2" t="n"/>
       <c r="C209" s="2" t="n"/>
       <c r="G209" s="2" t="n"/>
       <c r="M209" s="3" t="n"/>
-      <c r="U209" s="2" t="n"/>
-      <c r="Y209" s="3" t="n"/>
+      <c r="V209" s="2" t="n"/>
+      <c r="Z209" s="3" t="n"/>
     </row>
     <row r="210">
       <c r="A210" s="2" t="n"/>
       <c r="C210" s="2" t="n"/>
       <c r="G210" s="2" t="n"/>
       <c r="M210" s="3" t="n"/>
-      <c r="U210" s="2" t="n"/>
-      <c r="Y210" s="3" t="n"/>
+      <c r="V210" s="2" t="n"/>
+      <c r="Z210" s="3" t="n"/>
     </row>
     <row r="211">
       <c r="A211" s="2" t="n"/>
       <c r="C211" s="2" t="n"/>
       <c r="G211" s="2" t="n"/>
       <c r="M211" s="3" t="n"/>
-      <c r="U211" s="2" t="n"/>
-      <c r="Y211" s="3" t="n"/>
+      <c r="V211" s="2" t="n"/>
+      <c r="Z211" s="3" t="n"/>
     </row>
     <row r="212">
       <c r="A212" s="2" t="n"/>
       <c r="C212" s="2" t="n"/>
       <c r="G212" s="2" t="n"/>
       <c r="M212" s="3" t="n"/>
-      <c r="U212" s="2" t="n"/>
-      <c r="Y212" s="3" t="n"/>
+      <c r="V212" s="2" t="n"/>
+      <c r="Z212" s="3" t="n"/>
     </row>
     <row r="213">
       <c r="A213" s="2" t="n"/>
       <c r="C213" s="2" t="n"/>
       <c r="G213" s="2" t="n"/>
       <c r="M213" s="3" t="n"/>
-      <c r="U213" s="2" t="n"/>
-      <c r="Y213" s="3" t="n"/>
+      <c r="V213" s="2" t="n"/>
+      <c r="Z213" s="3" t="n"/>
     </row>
     <row r="214">
       <c r="A214" s="2" t="n"/>
       <c r="C214" s="2" t="n"/>
       <c r="G214" s="2" t="n"/>
       <c r="M214" s="3" t="n"/>
-      <c r="U214" s="2" t="n"/>
-      <c r="Y214" s="3" t="n"/>
+      <c r="V214" s="2" t="n"/>
+      <c r="Z214" s="3" t="n"/>
     </row>
     <row r="215">
       <c r="A215" s="2" t="n"/>
       <c r="C215" s="2" t="n"/>
       <c r="G215" s="2" t="n"/>
       <c r="M215" s="3" t="n"/>
-      <c r="U215" s="2" t="n"/>
-      <c r="Y215" s="3" t="n"/>
+      <c r="V215" s="2" t="n"/>
+      <c r="Z215" s="3" t="n"/>
     </row>
     <row r="216">
       <c r="A216" s="2" t="n"/>
       <c r="C216" s="2" t="n"/>
       <c r="G216" s="2" t="n"/>
       <c r="M216" s="3" t="n"/>
-      <c r="U216" s="2" t="n"/>
-      <c r="Y216" s="3" t="n"/>
+      <c r="V216" s="2" t="n"/>
+      <c r="Z216" s="3" t="n"/>
     </row>
     <row r="217">
       <c r="A217" s="2" t="n"/>
       <c r="C217" s="2" t="n"/>
       <c r="G217" s="2" t="n"/>
       <c r="M217" s="3" t="n"/>
-      <c r="U217" s="2" t="n"/>
-      <c r="Y217" s="3" t="n"/>
+      <c r="V217" s="2" t="n"/>
+      <c r="Z217" s="3" t="n"/>
     </row>
     <row r="218">
       <c r="A218" s="2" t="n"/>
       <c r="C218" s="2" t="n"/>
       <c r="G218" s="2" t="n"/>
       <c r="M218" s="3" t="n"/>
-      <c r="U218" s="2" t="n"/>
-      <c r="Y218" s="3" t="n"/>
+      <c r="V218" s="2" t="n"/>
+      <c r="Z218" s="3" t="n"/>
     </row>
     <row r="219">
       <c r="A219" s="2" t="n"/>
       <c r="C219" s="2" t="n"/>
       <c r="G219" s="2" t="n"/>
       <c r="M219" s="3" t="n"/>
-      <c r="U219" s="2" t="n"/>
-      <c r="Y219" s="3" t="n"/>
+      <c r="V219" s="2" t="n"/>
+      <c r="Z219" s="3" t="n"/>
     </row>
     <row r="220">
       <c r="A220" s="2" t="n"/>
       <c r="C220" s="2" t="n"/>
       <c r="G220" s="2" t="n"/>
       <c r="M220" s="3" t="n"/>
-      <c r="U220" s="2" t="n"/>
-      <c r="Y220" s="3" t="n"/>
+      <c r="V220" s="2" t="n"/>
+      <c r="Z220" s="3" t="n"/>
     </row>
     <row r="221">
       <c r="A221" s="2" t="n"/>
       <c r="C221" s="2" t="n"/>
       <c r="G221" s="2" t="n"/>
       <c r="M221" s="3" t="n"/>
-      <c r="U221" s="2" t="n"/>
-      <c r="Y221" s="3" t="n"/>
+      <c r="V221" s="2" t="n"/>
+      <c r="Z221" s="3" t="n"/>
     </row>
     <row r="222">
       <c r="A222" s="2" t="n"/>
       <c r="C222" s="2" t="n"/>
       <c r="G222" s="2" t="n"/>
       <c r="M222" s="3" t="n"/>
-      <c r="U222" s="2" t="n"/>
-      <c r="Y222" s="3" t="n"/>
+      <c r="V222" s="2" t="n"/>
+      <c r="Z222" s="3" t="n"/>
     </row>
     <row r="223">
       <c r="A223" s="2" t="n"/>
       <c r="C223" s="2" t="n"/>
       <c r="G223" s="2" t="n"/>
       <c r="M223" s="3" t="n"/>
-      <c r="U223" s="2" t="n"/>
-      <c r="Y223" s="3" t="n"/>
+      <c r="V223" s="2" t="n"/>
+      <c r="Z223" s="3" t="n"/>
     </row>
     <row r="224">
       <c r="A224" s="2" t="n"/>
       <c r="C224" s="2" t="n"/>
       <c r="G224" s="2" t="n"/>
       <c r="M224" s="3" t="n"/>
-      <c r="U224" s="2" t="n"/>
-      <c r="Y224" s="3" t="n"/>
+      <c r="V224" s="2" t="n"/>
+      <c r="Z224" s="3" t="n"/>
     </row>
     <row r="225">
       <c r="A225" s="2" t="n"/>
       <c r="C225" s="2" t="n"/>
       <c r="G225" s="2" t="n"/>
       <c r="M225" s="3" t="n"/>
-      <c r="U225" s="2" t="n"/>
-      <c r="Y225" s="3" t="n"/>
+      <c r="V225" s="2" t="n"/>
+      <c r="Z225" s="3" t="n"/>
     </row>
     <row r="226">
       <c r="A226" s="2" t="n"/>
       <c r="C226" s="2" t="n"/>
       <c r="G226" s="2" t="n"/>
       <c r="M226" s="3" t="n"/>
-      <c r="U226" s="2" t="n"/>
-      <c r="Y226" s="3" t="n"/>
+      <c r="V226" s="2" t="n"/>
+      <c r="Z226" s="3" t="n"/>
     </row>
     <row r="227">
       <c r="A227" s="2" t="n"/>
       <c r="C227" s="2" t="n"/>
       <c r="G227" s="2" t="n"/>
       <c r="M227" s="3" t="n"/>
-      <c r="U227" s="2" t="n"/>
-      <c r="Y227" s="3" t="n"/>
+      <c r="V227" s="2" t="n"/>
+      <c r="Z227" s="3" t="n"/>
     </row>
     <row r="228">
       <c r="A228" s="2" t="n"/>
       <c r="C228" s="2" t="n"/>
       <c r="G228" s="2" t="n"/>
       <c r="M228" s="3" t="n"/>
-      <c r="U228" s="2" t="n"/>
-      <c r="Y228" s="3" t="n"/>
+      <c r="V228" s="2" t="n"/>
+      <c r="Z228" s="3" t="n"/>
     </row>
     <row r="229">
       <c r="A229" s="2" t="n"/>
       <c r="C229" s="2" t="n"/>
       <c r="G229" s="2" t="n"/>
       <c r="M229" s="3" t="n"/>
-      <c r="U229" s="2" t="n"/>
-      <c r="Y229" s="3" t="n"/>
+      <c r="V229" s="2" t="n"/>
+      <c r="Z229" s="3" t="n"/>
     </row>
     <row r="230">
       <c r="A230" s="2" t="n"/>
       <c r="C230" s="2" t="n"/>
       <c r="G230" s="2" t="n"/>
       <c r="M230" s="3" t="n"/>
-      <c r="U230" s="2" t="n"/>
-      <c r="Y230" s="3" t="n"/>
+      <c r="V230" s="2" t="n"/>
+      <c r="Z230" s="3" t="n"/>
     </row>
     <row r="231">
       <c r="A231" s="2" t="n"/>
       <c r="C231" s="2" t="n"/>
       <c r="G231" s="2" t="n"/>
       <c r="M231" s="3" t="n"/>
-      <c r="U231" s="2" t="n"/>
-      <c r="Y231" s="3" t="n"/>
+      <c r="V231" s="2" t="n"/>
+      <c r="Z231" s="3" t="n"/>
     </row>
     <row r="232">
       <c r="A232" s="2" t="n"/>
       <c r="C232" s="2" t="n"/>
       <c r="G232" s="2" t="n"/>
       <c r="M232" s="3" t="n"/>
-      <c r="U232" s="2" t="n"/>
-      <c r="Y232" s="3" t="n"/>
+      <c r="V232" s="2" t="n"/>
+      <c r="Z232" s="3" t="n"/>
     </row>
     <row r="233">
       <c r="A233" s="2" t="n"/>
       <c r="C233" s="2" t="n"/>
       <c r="G233" s="2" t="n"/>
       <c r="M233" s="3" t="n"/>
-      <c r="U233" s="2" t="n"/>
-      <c r="Y233" s="3" t="n"/>
+      <c r="V233" s="2" t="n"/>
+      <c r="Z233" s="3" t="n"/>
     </row>
     <row r="234">
       <c r="A234" s="2" t="n"/>
       <c r="C234" s="2" t="n"/>
       <c r="G234" s="2" t="n"/>
       <c r="M234" s="3" t="n"/>
-      <c r="U234" s="2" t="n"/>
-      <c r="Y234" s="3" t="n"/>
+      <c r="V234" s="2" t="n"/>
+      <c r="Z234" s="3" t="n"/>
     </row>
     <row r="235">
       <c r="A235" s="2" t="n"/>
       <c r="C235" s="2" t="n"/>
       <c r="G235" s="2" t="n"/>
       <c r="M235" s="3" t="n"/>
-      <c r="U235" s="2" t="n"/>
-      <c r="Y235" s="3" t="n"/>
+      <c r="V235" s="2" t="n"/>
+      <c r="Z235" s="3" t="n"/>
     </row>
     <row r="236">
       <c r="A236" s="2" t="n"/>
       <c r="C236" s="2" t="n"/>
       <c r="G236" s="2" t="n"/>
       <c r="M236" s="3" t="n"/>
-      <c r="U236" s="2" t="n"/>
-      <c r="Y236" s="3" t="n"/>
+      <c r="V236" s="2" t="n"/>
+      <c r="Z236" s="3" t="n"/>
     </row>
     <row r="237">
       <c r="A237" s="2" t="n"/>
       <c r="C237" s="2" t="n"/>
       <c r="G237" s="2" t="n"/>
       <c r="M237" s="3" t="n"/>
-      <c r="U237" s="2" t="n"/>
-      <c r="Y237" s="3" t="n"/>
+      <c r="V237" s="2" t="n"/>
+      <c r="Z237" s="3" t="n"/>
     </row>
     <row r="238">
       <c r="A238" s="2" t="n"/>
       <c r="C238" s="2" t="n"/>
       <c r="G238" s="2" t="n"/>
       <c r="M238" s="3" t="n"/>
-      <c r="U238" s="2" t="n"/>
-      <c r="Y238" s="3" t="n"/>
+      <c r="V238" s="2" t="n"/>
+      <c r="Z238" s="3" t="n"/>
     </row>
     <row r="239">
       <c r="A239" s="2" t="n"/>
       <c r="C239" s="2" t="n"/>
       <c r="G239" s="2" t="n"/>
       <c r="M239" s="3" t="n"/>
-      <c r="U239" s="2" t="n"/>
-      <c r="Y239" s="3" t="n"/>
+      <c r="V239" s="2" t="n"/>
+      <c r="Z239" s="3" t="n"/>
     </row>
     <row r="240">
       <c r="A240" s="2" t="n"/>
       <c r="C240" s="2" t="n"/>
       <c r="G240" s="2" t="n"/>
       <c r="M240" s="3" t="n"/>
-      <c r="U240" s="2" t="n"/>
-      <c r="Y240" s="3" t="n"/>
+      <c r="V240" s="2" t="n"/>
+      <c r="Z240" s="3" t="n"/>
     </row>
     <row r="241">
       <c r="A241" s="2" t="n"/>
       <c r="C241" s="2" t="n"/>
       <c r="G241" s="2" t="n"/>
       <c r="M241" s="3" t="n"/>
-      <c r="U241" s="2" t="n"/>
-      <c r="Y241" s="3" t="n"/>
+      <c r="V241" s="2" t="n"/>
+      <c r="Z241" s="3" t="n"/>
     </row>
     <row r="242">
       <c r="A242" s="2" t="n"/>
       <c r="C242" s="2" t="n"/>
       <c r="G242" s="2" t="n"/>
       <c r="M242" s="3" t="n"/>
-      <c r="U242" s="2" t="n"/>
-      <c r="Y242" s="3" t="n"/>
+      <c r="V242" s="2" t="n"/>
+      <c r="Z242" s="3" t="n"/>
     </row>
     <row r="243">
       <c r="A243" s="2" t="n"/>
       <c r="C243" s="2" t="n"/>
       <c r="G243" s="2" t="n"/>
       <c r="M243" s="3" t="n"/>
-      <c r="U243" s="2" t="n"/>
-      <c r="Y243" s="3" t="n"/>
+      <c r="V243" s="2" t="n"/>
+      <c r="Z243" s="3" t="n"/>
     </row>
     <row r="244">
       <c r="A244" s="2" t="n"/>
       <c r="C244" s="2" t="n"/>
       <c r="G244" s="2" t="n"/>
       <c r="M244" s="3" t="n"/>
-      <c r="U244" s="2" t="n"/>
-      <c r="Y244" s="3" t="n"/>
+      <c r="V244" s="2" t="n"/>
+      <c r="Z244" s="3" t="n"/>
     </row>
     <row r="245">
       <c r="A245" s="2" t="n"/>
       <c r="C245" s="2" t="n"/>
       <c r="G245" s="2" t="n"/>
       <c r="M245" s="3" t="n"/>
-      <c r="U245" s="2" t="n"/>
-      <c r="Y245" s="3" t="n"/>
+      <c r="V245" s="2" t="n"/>
+      <c r="Z245" s="3" t="n"/>
     </row>
     <row r="246">
       <c r="A246" s="2" t="n"/>
       <c r="C246" s="2" t="n"/>
       <c r="G246" s="2" t="n"/>
       <c r="M246" s="3" t="n"/>
-      <c r="U246" s="2" t="n"/>
-      <c r="Y246" s="3" t="n"/>
+      <c r="V246" s="2" t="n"/>
+      <c r="Z246" s="3" t="n"/>
     </row>
     <row r="247">
       <c r="A247" s="2" t="n"/>
       <c r="C247" s="2" t="n"/>
       <c r="G247" s="2" t="n"/>
       <c r="M247" s="3" t="n"/>
-      <c r="U247" s="2" t="n"/>
-      <c r="Y247" s="3" t="n"/>
+      <c r="V247" s="2" t="n"/>
+      <c r="Z247" s="3" t="n"/>
     </row>
     <row r="248">
       <c r="A248" s="2" t="n"/>
       <c r="C248" s="2" t="n"/>
       <c r="G248" s="2" t="n"/>
       <c r="M248" s="3" t="n"/>
-      <c r="U248" s="2" t="n"/>
-      <c r="Y248" s="3" t="n"/>
+      <c r="V248" s="2" t="n"/>
+      <c r="Z248" s="3" t="n"/>
     </row>
     <row r="249">
       <c r="A249" s="2" t="n"/>
       <c r="C249" s="2" t="n"/>
       <c r="G249" s="2" t="n"/>
       <c r="M249" s="3" t="n"/>
-      <c r="U249" s="2" t="n"/>
-      <c r="Y249" s="3" t="n"/>
+      <c r="V249" s="2" t="n"/>
+      <c r="Z249" s="3" t="n"/>
     </row>
     <row r="250">
       <c r="A250" s="2" t="n"/>
       <c r="C250" s="2" t="n"/>
       <c r="G250" s="2" t="n"/>
       <c r="M250" s="3" t="n"/>
-      <c r="U250" s="2" t="n"/>
-      <c r="Y250" s="3" t="n"/>
+      <c r="V250" s="2" t="n"/>
+      <c r="Z250" s="3" t="n"/>
     </row>
     <row r="251">
       <c r="A251" s="2" t="n"/>
       <c r="C251" s="2" t="n"/>
       <c r="G251" s="2" t="n"/>
       <c r="M251" s="3" t="n"/>
-      <c r="U251" s="2" t="n"/>
-      <c r="Y251" s="3" t="n"/>
+      <c r="V251" s="2" t="n"/>
+      <c r="Z251" s="3" t="n"/>
     </row>
     <row r="252">
       <c r="A252" s="2" t="n"/>
       <c r="C252" s="2" t="n"/>
       <c r="G252" s="2" t="n"/>
       <c r="M252" s="3" t="n"/>
-      <c r="U252" s="2" t="n"/>
-      <c r="Y252" s="3" t="n"/>
+      <c r="V252" s="2" t="n"/>
+      <c r="Z252" s="3" t="n"/>
     </row>
     <row r="253">
       <c r="A253" s="2" t="n"/>
       <c r="C253" s="2" t="n"/>
       <c r="G253" s="2" t="n"/>
       <c r="M253" s="3" t="n"/>
-      <c r="U253" s="2" t="n"/>
-      <c r="Y253" s="3" t="n"/>
+      <c r="V253" s="2" t="n"/>
+      <c r="Z253" s="3" t="n"/>
     </row>
     <row r="254">
       <c r="A254" s="2" t="n"/>
       <c r="C254" s="2" t="n"/>
       <c r="G254" s="2" t="n"/>
       <c r="M254" s="3" t="n"/>
-      <c r="U254" s="2" t="n"/>
-      <c r="Y254" s="3" t="n"/>
+      <c r="V254" s="2" t="n"/>
+      <c r="Z254" s="3" t="n"/>
     </row>
     <row r="255">
       <c r="A255" s="2" t="n"/>
       <c r="C255" s="2" t="n"/>
       <c r="G255" s="2" t="n"/>
       <c r="M255" s="3" t="n"/>
-      <c r="U255" s="2" t="n"/>
-      <c r="Y255" s="3" t="n"/>
+      <c r="V255" s="2" t="n"/>
+      <c r="Z255" s="3" t="n"/>
     </row>
     <row r="256">
       <c r="A256" s="2" t="n"/>
       <c r="C256" s="2" t="n"/>
       <c r="G256" s="2" t="n"/>
       <c r="M256" s="3" t="n"/>
-      <c r="U256" s="2" t="n"/>
-      <c r="Y256" s="3" t="n"/>
+      <c r="V256" s="2" t="n"/>
+      <c r="Z256" s="3" t="n"/>
     </row>
     <row r="257">
       <c r="A257" s="2" t="n"/>
       <c r="C257" s="2" t="n"/>
       <c r="G257" s="2" t="n"/>
       <c r="M257" s="3" t="n"/>
-      <c r="U257" s="2" t="n"/>
-      <c r="Y257" s="3" t="n"/>
+      <c r="V257" s="2" t="n"/>
+      <c r="Z257" s="3" t="n"/>
     </row>
     <row r="258">
       <c r="A258" s="2" t="n"/>
       <c r="C258" s="2" t="n"/>
       <c r="G258" s="2" t="n"/>
       <c r="M258" s="3" t="n"/>
-      <c r="U258" s="2" t="n"/>
-      <c r="Y258" s="3" t="n"/>
+      <c r="V258" s="2" t="n"/>
+      <c r="Z258" s="3" t="n"/>
     </row>
     <row r="259">
       <c r="A259" s="2" t="n"/>
       <c r="C259" s="2" t="n"/>
       <c r="G259" s="2" t="n"/>
       <c r="M259" s="3" t="n"/>
-      <c r="U259" s="2" t="n"/>
-      <c r="Y259" s="3" t="n"/>
+      <c r="V259" s="2" t="n"/>
+      <c r="Z259" s="3" t="n"/>
     </row>
     <row r="260">
       <c r="A260" s="2" t="n"/>
       <c r="C260" s="2" t="n"/>
       <c r="G260" s="2" t="n"/>
       <c r="M260" s="3" t="n"/>
-      <c r="U260" s="2" t="n"/>
-      <c r="Y260" s="3" t="n"/>
+      <c r="V260" s="2" t="n"/>
+      <c r="Z260" s="3" t="n"/>
     </row>
     <row r="261">
       <c r="A261" s="2" t="n"/>
       <c r="C261" s="2" t="n"/>
       <c r="G261" s="2" t="n"/>
       <c r="M261" s="3" t="n"/>
-      <c r="U261" s="2" t="n"/>
-      <c r="Y261" s="3" t="n"/>
+      <c r="V261" s="2" t="n"/>
+      <c r="Z261" s="3" t="n"/>
     </row>
     <row r="262">
       <c r="A262" s="2" t="n"/>
       <c r="C262" s="2" t="n"/>
       <c r="G262" s="2" t="n"/>
       <c r="M262" s="3" t="n"/>
-      <c r="U262" s="2" t="n"/>
-      <c r="Y262" s="3" t="n"/>
+      <c r="V262" s="2" t="n"/>
+      <c r="Z262" s="3" t="n"/>
     </row>
     <row r="263">
       <c r="A263" s="2" t="n"/>
       <c r="C263" s="2" t="n"/>
       <c r="G263" s="2" t="n"/>
       <c r="M263" s="3" t="n"/>
-      <c r="U263" s="2" t="n"/>
-      <c r="Y263" s="3" t="n"/>
+      <c r="V263" s="2" t="n"/>
+      <c r="Z263" s="3" t="n"/>
     </row>
     <row r="264">
       <c r="A264" s="2" t="n"/>
       <c r="C264" s="2" t="n"/>
       <c r="G264" s="2" t="n"/>
       <c r="M264" s="3" t="n"/>
-      <c r="U264" s="2" t="n"/>
-      <c r="Y264" s="3" t="n"/>
+      <c r="V264" s="2" t="n"/>
+      <c r="Z264" s="3" t="n"/>
     </row>
     <row r="265">
       <c r="A265" s="2" t="n"/>
       <c r="C265" s="2" t="n"/>
       <c r="G265" s="2" t="n"/>
       <c r="M265" s="3" t="n"/>
-      <c r="U265" s="2" t="n"/>
-      <c r="Y265" s="3" t="n"/>
+      <c r="V265" s="2" t="n"/>
+      <c r="Z265" s="3" t="n"/>
     </row>
     <row r="266">
       <c r="A266" s="2" t="n"/>
       <c r="C266" s="2" t="n"/>
       <c r="G266" s="2" t="n"/>
       <c r="M266" s="3" t="n"/>
-      <c r="U266" s="2" t="n"/>
-      <c r="Y266" s="3" t="n"/>
+      <c r="V266" s="2" t="n"/>
+      <c r="Z266" s="3" t="n"/>
     </row>
     <row r="267">
       <c r="A267" s="2" t="n"/>
       <c r="C267" s="2" t="n"/>
       <c r="G267" s="2" t="n"/>
       <c r="M267" s="3" t="n"/>
-      <c r="U267" s="2" t="n"/>
-      <c r="Y267" s="3" t="n"/>
+      <c r="V267" s="2" t="n"/>
+      <c r="Z267" s="3" t="n"/>
     </row>
     <row r="268">
       <c r="A268" s="2" t="n"/>
       <c r="C268" s="2" t="n"/>
       <c r="G268" s="2" t="n"/>
       <c r="M268" s="3" t="n"/>
-      <c r="U268" s="2" t="n"/>
-      <c r="Y268" s="3" t="n"/>
+      <c r="V268" s="2" t="n"/>
+      <c r="Z268" s="3" t="n"/>
     </row>
     <row r="269">
       <c r="A269" s="2" t="n"/>
       <c r="C269" s="2" t="n"/>
       <c r="G269" s="2" t="n"/>
       <c r="M269" s="3" t="n"/>
-      <c r="U269" s="2" t="n"/>
-      <c r="Y269" s="3" t="n"/>
+      <c r="V269" s="2" t="n"/>
+      <c r="Z269" s="3" t="n"/>
     </row>
     <row r="270">
       <c r="A270" s="2" t="n"/>
       <c r="C270" s="2" t="n"/>
       <c r="G270" s="2" t="n"/>
       <c r="M270" s="3" t="n"/>
-      <c r="U270" s="2" t="n"/>
-      <c r="Y270" s="3" t="n"/>
+      <c r="V270" s="2" t="n"/>
+      <c r="Z270" s="3" t="n"/>
     </row>
     <row r="271">
       <c r="A271" s="2" t="n"/>
       <c r="C271" s="2" t="n"/>
       <c r="G271" s="2" t="n"/>
       <c r="M271" s="3" t="n"/>
-      <c r="U271" s="2" t="n"/>
-      <c r="Y271" s="3" t="n"/>
+      <c r="V271" s="2" t="n"/>
+      <c r="Z271" s="3" t="n"/>
     </row>
     <row r="272">
       <c r="A272" s="2" t="n"/>
       <c r="C272" s="2" t="n"/>
       <c r="G272" s="2" t="n"/>
       <c r="M272" s="3" t="n"/>
-      <c r="U272" s="2" t="n"/>
-      <c r="Y272" s="3" t="n"/>
+      <c r="V272" s="2" t="n"/>
+      <c r="Z272" s="3" t="n"/>
     </row>
     <row r="273">
       <c r="A273" s="2" t="n"/>
       <c r="C273" s="2" t="n"/>
       <c r="G273" s="2" t="n"/>
       <c r="M273" s="3" t="n"/>
-      <c r="U273" s="2" t="n"/>
-      <c r="Y273" s="3" t="n"/>
+      <c r="V273" s="2" t="n"/>
+      <c r="Z273" s="3" t="n"/>
     </row>
     <row r="274">
       <c r="A274" s="2" t="n"/>
       <c r="C274" s="2" t="n"/>
       <c r="G274" s="2" t="n"/>
       <c r="M274" s="3" t="n"/>
-      <c r="U274" s="2" t="n"/>
-      <c r="Y274" s="3" t="n"/>
+      <c r="V274" s="2" t="n"/>
+      <c r="Z274" s="3" t="n"/>
     </row>
     <row r="275">
       <c r="A275" s="2" t="n"/>
       <c r="C275" s="2" t="n"/>
       <c r="G275" s="2" t="n"/>
       <c r="M275" s="3" t="n"/>
-      <c r="U275" s="2" t="n"/>
-      <c r="Y275" s="3" t="n"/>
+      <c r="V275" s="2" t="n"/>
+      <c r="Z275" s="3" t="n"/>
     </row>
     <row r="276">
       <c r="A276" s="2" t="n"/>
       <c r="C276" s="2" t="n"/>
       <c r="G276" s="2" t="n"/>
       <c r="M276" s="3" t="n"/>
-      <c r="U276" s="2" t="n"/>
-      <c r="Y276" s="3" t="n"/>
+      <c r="V276" s="2" t="n"/>
+      <c r="Z276" s="3" t="n"/>
     </row>
     <row r="277">
       <c r="A277" s="2" t="n"/>
       <c r="C277" s="2" t="n"/>
       <c r="G277" s="2" t="n"/>
       <c r="M277" s="3" t="n"/>
-      <c r="U277" s="2" t="n"/>
-      <c r="Y277" s="3" t="n"/>
+      <c r="V277" s="2" t="n"/>
+      <c r="Z277" s="3" t="n"/>
     </row>
     <row r="278">
       <c r="A278" s="2" t="n"/>
       <c r="C278" s="2" t="n"/>
       <c r="G278" s="2" t="n"/>
       <c r="M278" s="3" t="n"/>
-      <c r="U278" s="2" t="n"/>
-      <c r="Y278" s="3" t="n"/>
+      <c r="V278" s="2" t="n"/>
+      <c r="Z278" s="3" t="n"/>
     </row>
     <row r="279">
       <c r="A279" s="2" t="n"/>
       <c r="C279" s="2" t="n"/>
       <c r="G279" s="2" t="n"/>
       <c r="M279" s="3" t="n"/>
-      <c r="U279" s="2" t="n"/>
-      <c r="Y279" s="3" t="n"/>
+      <c r="V279" s="2" t="n"/>
+      <c r="Z279" s="3" t="n"/>
     </row>
     <row r="280">
       <c r="A280" s="2" t="n"/>
       <c r="C280" s="2" t="n"/>
       <c r="G280" s="2" t="n"/>
       <c r="M280" s="3" t="n"/>
-      <c r="U280" s="2" t="n"/>
-      <c r="Y280" s="3" t="n"/>
+      <c r="V280" s="2" t="n"/>
+      <c r="Z280" s="3" t="n"/>
     </row>
     <row r="281">
       <c r="A281" s="2" t="n"/>
       <c r="C281" s="2" t="n"/>
       <c r="G281" s="2" t="n"/>
       <c r="M281" s="3" t="n"/>
-      <c r="U281" s="2" t="n"/>
-      <c r="Y281" s="3" t="n"/>
+      <c r="V281" s="2" t="n"/>
+      <c r="Z281" s="3" t="n"/>
     </row>
     <row r="282">
       <c r="A282" s="2" t="n"/>
       <c r="C282" s="2" t="n"/>
       <c r="G282" s="2" t="n"/>
       <c r="M282" s="3" t="n"/>
-      <c r="U282" s="2" t="n"/>
-      <c r="Y282" s="3" t="n"/>
+      <c r="V282" s="2" t="n"/>
+      <c r="Z282" s="3" t="n"/>
     </row>
     <row r="283">
       <c r="A283" s="2" t="n"/>
       <c r="C283" s="2" t="n"/>
       <c r="G283" s="2" t="n"/>
       <c r="M283" s="3" t="n"/>
-      <c r="U283" s="2" t="n"/>
-      <c r="Y283" s="3" t="n"/>
+      <c r="V283" s="2" t="n"/>
+      <c r="Z283" s="3" t="n"/>
     </row>
     <row r="284">
       <c r="A284" s="2" t="n"/>
       <c r="C284" s="2" t="n"/>
       <c r="G284" s="2" t="n"/>
       <c r="M284" s="3" t="n"/>
-      <c r="U284" s="2" t="n"/>
-      <c r="Y284" s="3" t="n"/>
+      <c r="V284" s="2" t="n"/>
+      <c r="Z284" s="3" t="n"/>
     </row>
     <row r="285">
       <c r="A285" s="2" t="n"/>
       <c r="C285" s="2" t="n"/>
       <c r="G285" s="2" t="n"/>
       <c r="M285" s="3" t="n"/>
-      <c r="U285" s="2" t="n"/>
-      <c r="Y285" s="3" t="n"/>
+      <c r="V285" s="2" t="n"/>
+      <c r="Z285" s="3" t="n"/>
     </row>
     <row r="286">
       <c r="A286" s="2" t="n"/>
       <c r="C286" s="2" t="n"/>
       <c r="G286" s="2" t="n"/>
       <c r="M286" s="3" t="n"/>
-      <c r="U286" s="2" t="n"/>
-      <c r="Y286" s="3" t="n"/>
+      <c r="V286" s="2" t="n"/>
+      <c r="Z286" s="3" t="n"/>
     </row>
     <row r="287">
       <c r="A287" s="2" t="n"/>
       <c r="C287" s="2" t="n"/>
       <c r="G287" s="2" t="n"/>
       <c r="M287" s="3" t="n"/>
-      <c r="U287" s="2" t="n"/>
-      <c r="Y287" s="3" t="n"/>
+      <c r="V287" s="2" t="n"/>
+      <c r="Z287" s="3" t="n"/>
     </row>
     <row r="288">
       <c r="A288" s="2" t="n"/>
       <c r="C288" s="2" t="n"/>
       <c r="G288" s="2" t="n"/>
       <c r="M288" s="3" t="n"/>
-      <c r="U288" s="2" t="n"/>
-      <c r="Y288" s="3" t="n"/>
+      <c r="V288" s="2" t="n"/>
+      <c r="Z288" s="3" t="n"/>
     </row>
     <row r="289">
       <c r="A289" s="2" t="n"/>
       <c r="C289" s="2" t="n"/>
       <c r="G289" s="2" t="n"/>
       <c r="M289" s="3" t="n"/>
-      <c r="U289" s="2" t="n"/>
-      <c r="Y289" s="3" t="n"/>
+      <c r="V289" s="2" t="n"/>
+      <c r="Z289" s="3" t="n"/>
     </row>
     <row r="290">
       <c r="A290" s="2" t="n"/>
       <c r="C290" s="2" t="n"/>
       <c r="G290" s="2" t="n"/>
       <c r="M290" s="3" t="n"/>
-      <c r="U290" s="2" t="n"/>
-      <c r="Y290" s="3" t="n"/>
+      <c r="V290" s="2" t="n"/>
+      <c r="Z290" s="3" t="n"/>
     </row>
     <row r="291">
       <c r="A291" s="2" t="n"/>
       <c r="C291" s="2" t="n"/>
       <c r="G291" s="2" t="n"/>
       <c r="M291" s="3" t="n"/>
-      <c r="U291" s="2" t="n"/>
-      <c r="Y291" s="3" t="n"/>
+      <c r="V291" s="2" t="n"/>
+      <c r="Z291" s="3" t="n"/>
     </row>
     <row r="292">
       <c r="A292" s="2" t="n"/>
       <c r="C292" s="2" t="n"/>
       <c r="G292" s="2" t="n"/>
       <c r="M292" s="3" t="n"/>
-      <c r="U292" s="2" t="n"/>
-      <c r="Y292" s="3" t="n"/>
+      <c r="V292" s="2" t="n"/>
+      <c r="Z292" s="3" t="n"/>
     </row>
     <row r="293">
       <c r="A293" s="2" t="n"/>
       <c r="C293" s="2" t="n"/>
       <c r="G293" s="2" t="n"/>
       <c r="M293" s="3" t="n"/>
-      <c r="U293" s="2" t="n"/>
-      <c r="Y293" s="3" t="n"/>
+      <c r="V293" s="2" t="n"/>
+      <c r="Z293" s="3" t="n"/>
     </row>
     <row r="294">
       <c r="A294" s="2" t="n"/>
       <c r="C294" s="2" t="n"/>
       <c r="G294" s="2" t="n"/>
       <c r="M294" s="3" t="n"/>
-      <c r="U294" s="2" t="n"/>
-      <c r="Y294" s="3" t="n"/>
+      <c r="V294" s="2" t="n"/>
+      <c r="Z294" s="3" t="n"/>
     </row>
     <row r="295">
       <c r="A295" s="2" t="n"/>
       <c r="C295" s="2" t="n"/>
       <c r="G295" s="2" t="n"/>
       <c r="M295" s="3" t="n"/>
-      <c r="U295" s="2" t="n"/>
-      <c r="Y295" s="3" t="n"/>
+      <c r="V295" s="2" t="n"/>
+      <c r="Z295" s="3" t="n"/>
     </row>
     <row r="296">
       <c r="A296" s="2" t="n"/>
       <c r="C296" s="2" t="n"/>
       <c r="G296" s="2" t="n"/>
       <c r="M296" s="3" t="n"/>
-      <c r="U296" s="2" t="n"/>
-      <c r="Y296" s="3" t="n"/>
+      <c r="V296" s="2" t="n"/>
+      <c r="Z296" s="3" t="n"/>
     </row>
     <row r="297">
       <c r="A297" s="2" t="n"/>
       <c r="C297" s="2" t="n"/>
       <c r="G297" s="2" t="n"/>
       <c r="M297" s="3" t="n"/>
-      <c r="U297" s="2" t="n"/>
-      <c r="Y297" s="3" t="n"/>
+      <c r="V297" s="2" t="n"/>
+      <c r="Z297" s="3" t="n"/>
     </row>
     <row r="298">
       <c r="A298" s="2" t="n"/>
       <c r="C298" s="2" t="n"/>
       <c r="G298" s="2" t="n"/>
       <c r="M298" s="3" t="n"/>
-      <c r="U298" s="2" t="n"/>
-      <c r="Y298" s="3" t="n"/>
+      <c r="V298" s="2" t="n"/>
+      <c r="Z298" s="3" t="n"/>
     </row>
     <row r="299">
       <c r="A299" s="2" t="n"/>
       <c r="C299" s="2" t="n"/>
       <c r="G299" s="2" t="n"/>
       <c r="M299" s="3" t="n"/>
-      <c r="U299" s="2" t="n"/>
-      <c r="Y299" s="3" t="n"/>
+      <c r="V299" s="2" t="n"/>
+      <c r="Z299" s="3" t="n"/>
     </row>
     <row r="300">
       <c r="A300" s="2" t="n"/>
       <c r="C300" s="2" t="n"/>
       <c r="G300" s="2" t="n"/>
       <c r="M300" s="3" t="n"/>
-      <c r="U300" s="2" t="n"/>
-      <c r="Y300" s="3" t="n"/>
+      <c r="V300" s="2" t="n"/>
+      <c r="Z300" s="3" t="n"/>
     </row>
     <row r="301">
       <c r="A301" s="2" t="n"/>
       <c r="C301" s="2" t="n"/>
       <c r="G301" s="2" t="n"/>
       <c r="M301" s="3" t="n"/>
-      <c r="U301" s="2" t="n"/>
-      <c r="Y301" s="3" t="n"/>
+      <c r="V301" s="2" t="n"/>
+      <c r="Z301" s="3" t="n"/>
     </row>
     <row r="302">
       <c r="A302" s="2" t="n"/>
       <c r="C302" s="2" t="n"/>
       <c r="G302" s="2" t="n"/>
       <c r="M302" s="3" t="n"/>
-      <c r="U302" s="2" t="n"/>
-      <c r="Y302" s="3" t="n"/>
+      <c r="V302" s="2" t="n"/>
+      <c r="Z302" s="3" t="n"/>
     </row>
     <row r="303">
       <c r="A303" s="2" t="n"/>
       <c r="C303" s="2" t="n"/>
       <c r="G303" s="2" t="n"/>
       <c r="M303" s="3" t="n"/>
-      <c r="U303" s="2" t="n"/>
-      <c r="Y303" s="3" t="n"/>
+      <c r="V303" s="2" t="n"/>
+      <c r="Z303" s="3" t="n"/>
     </row>
     <row r="304">
       <c r="A304" s="2" t="n"/>
       <c r="C304" s="2" t="n"/>
       <c r="G304" s="2" t="n"/>
       <c r="M304" s="3" t="n"/>
-      <c r="U304" s="2" t="n"/>
-      <c r="Y304" s="3" t="n"/>
+      <c r="V304" s="2" t="n"/>
+      <c r="Z304" s="3" t="n"/>
     </row>
     <row r="305">
       <c r="A305" s="2" t="n"/>
       <c r="C305" s="2" t="n"/>
       <c r="G305" s="2" t="n"/>
       <c r="M305" s="3" t="n"/>
-      <c r="U305" s="2" t="n"/>
-      <c r="Y305" s="3" t="n"/>
+      <c r="V305" s="2" t="n"/>
+      <c r="Z305" s="3" t="n"/>
     </row>
     <row r="306">
       <c r="A306" s="2" t="n"/>
       <c r="C306" s="2" t="n"/>
       <c r="G306" s="2" t="n"/>
       <c r="M306" s="3" t="n"/>
-      <c r="U306" s="2" t="n"/>
-      <c r="Y306" s="3" t="n"/>
+      <c r="V306" s="2" t="n"/>
+      <c r="Z306" s="3" t="n"/>
     </row>
     <row r="307">
       <c r="A307" s="2" t="n"/>
       <c r="C307" s="2" t="n"/>
       <c r="G307" s="2" t="n"/>
       <c r="M307" s="3" t="n"/>
-      <c r="U307" s="2" t="n"/>
-      <c r="Y307" s="3" t="n"/>
+      <c r="V307" s="2" t="n"/>
+      <c r="Z307" s="3" t="n"/>
     </row>
     <row r="308">
       <c r="A308" s="2" t="n"/>
       <c r="C308" s="2" t="n"/>
       <c r="G308" s="2" t="n"/>
       <c r="M308" s="3" t="n"/>
-      <c r="U308" s="2" t="n"/>
-      <c r="Y308" s="3" t="n"/>
+      <c r="V308" s="2" t="n"/>
+      <c r="Z308" s="3" t="n"/>
     </row>
     <row r="309">
       <c r="A309" s="2" t="n"/>
       <c r="C309" s="2" t="n"/>
       <c r="G309" s="2" t="n"/>
       <c r="M309" s="3" t="n"/>
-      <c r="U309" s="2" t="n"/>
-      <c r="Y309" s="3" t="n"/>
+      <c r="V309" s="2" t="n"/>
+      <c r="Z309" s="3" t="n"/>
     </row>
     <row r="310">
       <c r="A310" s="2" t="n"/>
       <c r="C310" s="2" t="n"/>
       <c r="G310" s="2" t="n"/>
       <c r="M310" s="3" t="n"/>
-      <c r="U310" s="2" t="n"/>
-      <c r="Y310" s="3" t="n"/>
+      <c r="V310" s="2" t="n"/>
+      <c r="Z310" s="3" t="n"/>
     </row>
     <row r="311">
       <c r="A311" s="2" t="n"/>
       <c r="C311" s="2" t="n"/>
       <c r="G311" s="2" t="n"/>
       <c r="M311" s="3" t="n"/>
-      <c r="U311" s="2" t="n"/>
-      <c r="Y311" s="3" t="n"/>
+      <c r="V311" s="2" t="n"/>
+      <c r="Z311" s="3" t="n"/>
     </row>
     <row r="312">
       <c r="A312" s="2" t="n"/>
       <c r="C312" s="2" t="n"/>
       <c r="G312" s="2" t="n"/>
       <c r="M312" s="3" t="n"/>
-      <c r="U312" s="2" t="n"/>
-      <c r="Y312" s="3" t="n"/>
+      <c r="V312" s="2" t="n"/>
+      <c r="Z312" s="3" t="n"/>
     </row>
     <row r="313">
       <c r="A313" s="2" t="n"/>
       <c r="C313" s="2" t="n"/>
       <c r="G313" s="2" t="n"/>
       <c r="M313" s="3" t="n"/>
-      <c r="U313" s="2" t="n"/>
-      <c r="Y313" s="3" t="n"/>
+      <c r="V313" s="2" t="n"/>
+      <c r="Z313" s="3" t="n"/>
     </row>
     <row r="314">
       <c r="A314" s="2" t="n"/>
       <c r="C314" s="2" t="n"/>
       <c r="G314" s="2" t="n"/>
       <c r="M314" s="3" t="n"/>
-      <c r="U314" s="2" t="n"/>
-      <c r="Y314" s="3" t="n"/>
+      <c r="V314" s="2" t="n"/>
+      <c r="Z314" s="3" t="n"/>
     </row>
     <row r="315">
       <c r="A315" s="2" t="n"/>
       <c r="C315" s="2" t="n"/>
       <c r="G315" s="2" t="n"/>
       <c r="M315" s="3" t="n"/>
-      <c r="U315" s="2" t="n"/>
-      <c r="Y315" s="3" t="n"/>
+      <c r="V315" s="2" t="n"/>
+      <c r="Z315" s="3" t="n"/>
     </row>
     <row r="316">
       <c r="A316" s="2" t="n"/>
       <c r="C316" s="2" t="n"/>
       <c r="G316" s="2" t="n"/>
       <c r="M316" s="3" t="n"/>
-      <c r="U316" s="2" t="n"/>
-      <c r="Y316" s="3" t="n"/>
+      <c r="V316" s="2" t="n"/>
+      <c r="Z316" s="3" t="n"/>
     </row>
     <row r="317">
       <c r="A317" s="2" t="n"/>
       <c r="C317" s="2" t="n"/>
       <c r="G317" s="2" t="n"/>
       <c r="M317" s="3" t="n"/>
-      <c r="U317" s="2" t="n"/>
-      <c r="Y317" s="3" t="n"/>
+      <c r="V317" s="2" t="n"/>
+      <c r="Z317" s="3" t="n"/>
     </row>
     <row r="318">
       <c r="A318" s="2" t="n"/>
       <c r="C318" s="2" t="n"/>
       <c r="G318" s="2" t="n"/>
       <c r="M318" s="3" t="n"/>
-      <c r="U318" s="2" t="n"/>
-      <c r="Y318" s="3" t="n"/>
+      <c r="V318" s="2" t="n"/>
+      <c r="Z318" s="3" t="n"/>
     </row>
     <row r="319">
       <c r="A319" s="2" t="n"/>
       <c r="C319" s="2" t="n"/>
       <c r="G319" s="2" t="n"/>
       <c r="M319" s="3" t="n"/>
-      <c r="U319" s="2" t="n"/>
-      <c r="Y319" s="3" t="n"/>
+      <c r="V319" s="2" t="n"/>
+      <c r="Z319" s="3" t="n"/>
     </row>
     <row r="320">
       <c r="A320" s="2" t="n"/>
       <c r="C320" s="2" t="n"/>
       <c r="G320" s="2" t="n"/>
       <c r="M320" s="3" t="n"/>
-      <c r="U320" s="2" t="n"/>
-      <c r="Y320" s="3" t="n"/>
+      <c r="V320" s="2" t="n"/>
+      <c r="Z320" s="3" t="n"/>
     </row>
     <row r="321">
       <c r="A321" s="2" t="n"/>
       <c r="C321" s="2" t="n"/>
       <c r="G321" s="2" t="n"/>
       <c r="M321" s="3" t="n"/>
-      <c r="U321" s="2" t="n"/>
-      <c r="Y321" s="3" t="n"/>
+      <c r="V321" s="2" t="n"/>
+      <c r="Z321" s="3" t="n"/>
     </row>
     <row r="322">
       <c r="A322" s="2" t="n"/>
       <c r="C322" s="2" t="n"/>
       <c r="G322" s="2" t="n"/>
       <c r="M322" s="3" t="n"/>
-      <c r="U322" s="2" t="n"/>
-      <c r="Y322" s="3" t="n"/>
+      <c r="V322" s="2" t="n"/>
+      <c r="Z322" s="3" t="n"/>
     </row>
     <row r="323">
       <c r="A323" s="2" t="n"/>
       <c r="C323" s="2" t="n"/>
       <c r="G323" s="2" t="n"/>
       <c r="M323" s="3" t="n"/>
-      <c r="U323" s="2" t="n"/>
-      <c r="Y323" s="3" t="n"/>
+      <c r="V323" s="2" t="n"/>
+      <c r="Z323" s="3" t="n"/>
     </row>
     <row r="324">
       <c r="A324" s="2" t="n"/>
       <c r="C324" s="2" t="n"/>
       <c r="G324" s="2" t="n"/>
       <c r="M324" s="3" t="n"/>
-      <c r="U324" s="2" t="n"/>
-      <c r="Y324" s="3" t="n"/>
+      <c r="V324" s="2" t="n"/>
+      <c r="Z324" s="3" t="n"/>
     </row>
     <row r="325">
       <c r="A325" s="2" t="n"/>
       <c r="C325" s="2" t="n"/>
       <c r="G325" s="2" t="n"/>
       <c r="M325" s="3" t="n"/>
-      <c r="U325" s="2" t="n"/>
-      <c r="Y325" s="3" t="n"/>
+      <c r="V325" s="2" t="n"/>
+      <c r="Z325" s="3" t="n"/>
     </row>
     <row r="326">
       <c r="A326" s="2" t="n"/>
       <c r="C326" s="2" t="n"/>
       <c r="G326" s="2" t="n"/>
       <c r="M326" s="3" t="n"/>
-      <c r="U326" s="2" t="n"/>
-      <c r="Y326" s="3" t="n"/>
+      <c r="V326" s="2" t="n"/>
+      <c r="Z326" s="3" t="n"/>
     </row>
     <row r="327">
       <c r="A327" s="2" t="n"/>
       <c r="C327" s="2" t="n"/>
       <c r="G327" s="2" t="n"/>
       <c r="M327" s="3" t="n"/>
-      <c r="U327" s="2" t="n"/>
-      <c r="Y327" s="3" t="n"/>
+      <c r="V327" s="2" t="n"/>
+      <c r="Z327" s="3" t="n"/>
     </row>
     <row r="328">
       <c r="A328" s="2" t="n"/>
       <c r="C328" s="2" t="n"/>
       <c r="G328" s="2" t="n"/>
       <c r="M328" s="3" t="n"/>
-      <c r="U328" s="2" t="n"/>
-      <c r="Y328" s="3" t="n"/>
+      <c r="V328" s="2" t="n"/>
+      <c r="Z328" s="3" t="n"/>
     </row>
     <row r="329">
       <c r="A329" s="2" t="n"/>
       <c r="C329" s="2" t="n"/>
       <c r="G329" s="2" t="n"/>
       <c r="M329" s="3" t="n"/>
-      <c r="U329" s="2" t="n"/>
-      <c r="Y329" s="3" t="n"/>
+      <c r="V329" s="2" t="n"/>
+      <c r="Z329" s="3" t="n"/>
     </row>
     <row r="330">
       <c r="A330" s="2" t="n"/>
       <c r="C330" s="2" t="n"/>
       <c r="G330" s="2" t="n"/>
       <c r="M330" s="3" t="n"/>
-      <c r="U330" s="2" t="n"/>
-      <c r="Y330" s="3" t="n"/>
+      <c r="V330" s="2" t="n"/>
+      <c r="Z330" s="3" t="n"/>
     </row>
     <row r="331">
       <c r="A331" s="2" t="n"/>
       <c r="C331" s="2" t="n"/>
       <c r="G331" s="2" t="n"/>
       <c r="M331" s="3" t="n"/>
-      <c r="U331" s="2" t="n"/>
-      <c r="Y331" s="3" t="n"/>
+      <c r="V331" s="2" t="n"/>
+      <c r="Z331" s="3" t="n"/>
     </row>
     <row r="332">
       <c r="A332" s="2" t="n"/>
       <c r="C332" s="2" t="n"/>
       <c r="G332" s="2" t="n"/>
       <c r="M332" s="3" t="n"/>
-      <c r="U332" s="2" t="n"/>
-      <c r="Y332" s="3" t="n"/>
+      <c r="V332" s="2" t="n"/>
+      <c r="Z332" s="3" t="n"/>
     </row>
     <row r="333">
       <c r="A333" s="2" t="n"/>
       <c r="C333" s="2" t="n"/>
       <c r="G333" s="2" t="n"/>
       <c r="M333" s="3" t="n"/>
-      <c r="U333" s="2" t="n"/>
-      <c r="Y333" s="3" t="n"/>
+      <c r="V333" s="2" t="n"/>
+      <c r="Z333" s="3" t="n"/>
     </row>
     <row r="334">
       <c r="A334" s="2" t="n"/>
       <c r="C334" s="2" t="n"/>
       <c r="G334" s="2" t="n"/>
       <c r="M334" s="3" t="n"/>
-      <c r="U334" s="2" t="n"/>
-      <c r="Y334" s="3" t="n"/>
+      <c r="V334" s="2" t="n"/>
+      <c r="Z334" s="3" t="n"/>
     </row>
     <row r="335">
       <c r="A335" s="2" t="n"/>
       <c r="C335" s="2" t="n"/>
       <c r="G335" s="2" t="n"/>
       <c r="M335" s="3" t="n"/>
-      <c r="U335" s="2" t="n"/>
-      <c r="Y335" s="3" t="n"/>
+      <c r="V335" s="2" t="n"/>
+      <c r="Z335" s="3" t="n"/>
     </row>
     <row r="336">
       <c r="A336" s="2" t="n"/>
       <c r="C336" s="2" t="n"/>
       <c r="G336" s="2" t="n"/>
       <c r="M336" s="3" t="n"/>
-      <c r="U336" s="2" t="n"/>
-      <c r="Y336" s="3" t="n"/>
+      <c r="V336" s="2" t="n"/>
+      <c r="Z336" s="3" t="n"/>
     </row>
     <row r="337">
       <c r="A337" s="2" t="n"/>
       <c r="C337" s="2" t="n"/>
       <c r="G337" s="2" t="n"/>
       <c r="M337" s="3" t="n"/>
-      <c r="U337" s="2" t="n"/>
-      <c r="Y337" s="3" t="n"/>
+      <c r="V337" s="2" t="n"/>
+      <c r="Z337" s="3" t="n"/>
     </row>
     <row r="338">
       <c r="A338" s="2" t="n"/>
       <c r="C338" s="2" t="n"/>
       <c r="G338" s="2" t="n"/>
       <c r="M338" s="3" t="n"/>
-      <c r="U338" s="2" t="n"/>
-      <c r="Y338" s="3" t="n"/>
+      <c r="V338" s="2" t="n"/>
+      <c r="Z338" s="3" t="n"/>
     </row>
     <row r="339">
       <c r="A339" s="2" t="n"/>
       <c r="C339" s="2" t="n"/>
       <c r="G339" s="2" t="n"/>
       <c r="M339" s="3" t="n"/>
-      <c r="U339" s="2" t="n"/>
-      <c r="Y339" s="3" t="n"/>
+      <c r="V339" s="2" t="n"/>
+      <c r="Z339" s="3" t="n"/>
     </row>
     <row r="340">
       <c r="A340" s="2" t="n"/>
       <c r="C340" s="2" t="n"/>
       <c r="G340" s="2" t="n"/>
       <c r="M340" s="3" t="n"/>
-      <c r="U340" s="2" t="n"/>
-      <c r="Y340" s="3" t="n"/>
+      <c r="V340" s="2" t="n"/>
+      <c r="Z340" s="3" t="n"/>
     </row>
     <row r="341">
       <c r="A341" s="2" t="n"/>
       <c r="C341" s="2" t="n"/>
       <c r="G341" s="2" t="n"/>
       <c r="M341" s="3" t="n"/>
-      <c r="U341" s="2" t="n"/>
-      <c r="Y341" s="3" t="n"/>
+      <c r="V341" s="2" t="n"/>
+      <c r="Z341" s="3" t="n"/>
     </row>
     <row r="342">
       <c r="A342" s="2" t="n"/>
       <c r="C342" s="2" t="n"/>
       <c r="G342" s="2" t="n"/>
       <c r="M342" s="3" t="n"/>
-      <c r="U342" s="2" t="n"/>
-      <c r="Y342" s="3" t="n"/>
+      <c r="V342" s="2" t="n"/>
+      <c r="Z342" s="3" t="n"/>
     </row>
     <row r="343">
       <c r="A343" s="2" t="n"/>
       <c r="C343" s="2" t="n"/>
       <c r="G343" s="2" t="n"/>
       <c r="M343" s="3" t="n"/>
-      <c r="U343" s="2" t="n"/>
-      <c r="Y343" s="3" t="n"/>
+      <c r="V343" s="2" t="n"/>
+      <c r="Z343" s="3" t="n"/>
     </row>
     <row r="344">
       <c r="A344" s="2" t="n"/>
       <c r="C344" s="2" t="n"/>
       <c r="G344" s="2" t="n"/>
       <c r="M344" s="3" t="n"/>
-      <c r="U344" s="2" t="n"/>
-      <c r="Y344" s="3" t="n"/>
+      <c r="V344" s="2" t="n"/>
+      <c r="Z344" s="3" t="n"/>
     </row>
     <row r="345">
       <c r="A345" s="2" t="n"/>
       <c r="C345" s="2" t="n"/>
       <c r="G345" s="2" t="n"/>
       <c r="M345" s="3" t="n"/>
-      <c r="U345" s="2" t="n"/>
-      <c r="Y345" s="3" t="n"/>
+      <c r="V345" s="2" t="n"/>
+      <c r="Z345" s="3" t="n"/>
     </row>
     <row r="346">
       <c r="A346" s="2" t="n"/>
       <c r="C346" s="2" t="n"/>
       <c r="G346" s="2" t="n"/>
       <c r="M346" s="3" t="n"/>
-      <c r="U346" s="2" t="n"/>
-      <c r="Y346" s="3" t="n"/>
+      <c r="V346" s="2" t="n"/>
+      <c r="Z346" s="3" t="n"/>
     </row>
     <row r="347">
       <c r="A347" s="2" t="n"/>
       <c r="C347" s="2" t="n"/>
       <c r="G347" s="2" t="n"/>
       <c r="M347" s="3" t="n"/>
-      <c r="U347" s="2" t="n"/>
-      <c r="Y347" s="3" t="n"/>
+      <c r="V347" s="2" t="n"/>
+      <c r="Z347" s="3" t="n"/>
     </row>
     <row r="348">
       <c r="A348" s="2" t="n"/>
       <c r="C348" s="2" t="n"/>
       <c r="G348" s="2" t="n"/>
       <c r="M348" s="3" t="n"/>
-      <c r="U348" s="2" t="n"/>
-      <c r="Y348" s="3" t="n"/>
+      <c r="V348" s="2" t="n"/>
+      <c r="Z348" s="3" t="n"/>
     </row>
     <row r="349">
       <c r="A349" s="2" t="n"/>
       <c r="C349" s="2" t="n"/>
       <c r="G349" s="2" t="n"/>
       <c r="M349" s="3" t="n"/>
-      <c r="U349" s="2" t="n"/>
-      <c r="Y349" s="3" t="n"/>
+      <c r="V349" s="2" t="n"/>
+      <c r="Z349" s="3" t="n"/>
     </row>
     <row r="350">
       <c r="A350" s="2" t="n"/>
       <c r="C350" s="2" t="n"/>
       <c r="G350" s="2" t="n"/>
       <c r="M350" s="3" t="n"/>
-      <c r="U350" s="2" t="n"/>
-      <c r="Y350" s="3" t="n"/>
+      <c r="V350" s="2" t="n"/>
+      <c r="Z350" s="3" t="n"/>
     </row>
     <row r="351">
       <c r="A351" s="2" t="n"/>
       <c r="C351" s="2" t="n"/>
       <c r="G351" s="2" t="n"/>
       <c r="M351" s="3" t="n"/>
-      <c r="U351" s="2" t="n"/>
-      <c r="Y351" s="3" t="n"/>
+      <c r="V351" s="2" t="n"/>
+      <c r="Z351" s="3" t="n"/>
     </row>
     <row r="352">
       <c r="A352" s="2" t="n"/>
       <c r="C352" s="2" t="n"/>
       <c r="G352" s="2" t="n"/>
       <c r="M352" s="3" t="n"/>
-      <c r="U352" s="2" t="n"/>
-      <c r="Y352" s="3" t="n"/>
+      <c r="V352" s="2" t="n"/>
+      <c r="Z352" s="3" t="n"/>
     </row>
     <row r="353">
       <c r="A353" s="2" t="n"/>
       <c r="C353" s="2" t="n"/>
       <c r="G353" s="2" t="n"/>
       <c r="M353" s="3" t="n"/>
-      <c r="U353" s="2" t="n"/>
-      <c r="Y353" s="3" t="n"/>
+      <c r="V353" s="2" t="n"/>
+      <c r="Z353" s="3" t="n"/>
     </row>
     <row r="354">
       <c r="A354" s="2" t="n"/>
       <c r="C354" s="2" t="n"/>
       <c r="G354" s="2" t="n"/>
       <c r="M354" s="3" t="n"/>
-      <c r="U354" s="2" t="n"/>
-      <c r="Y354" s="3" t="n"/>
+      <c r="V354" s="2" t="n"/>
+      <c r="Z354" s="3" t="n"/>
     </row>
     <row r="355">
       <c r="A355" s="2" t="n"/>
       <c r="C355" s="2" t="n"/>
       <c r="G355" s="2" t="n"/>
       <c r="M355" s="3" t="n"/>
-      <c r="U355" s="2" t="n"/>
-      <c r="Y355" s="3" t="n"/>
+      <c r="V355" s="2" t="n"/>
+      <c r="Z355" s="3" t="n"/>
     </row>
     <row r="356">
       <c r="A356" s="2" t="n"/>
       <c r="C356" s="2" t="n"/>
       <c r="G356" s="2" t="n"/>
       <c r="M356" s="3" t="n"/>
-      <c r="U356" s="2" t="n"/>
-      <c r="Y356" s="3" t="n"/>
+      <c r="V356" s="2" t="n"/>
+      <c r="Z356" s="3" t="n"/>
     </row>
     <row r="357">
       <c r="A357" s="2" t="n"/>
       <c r="C357" s="2" t="n"/>
       <c r="G357" s="2" t="n"/>
       <c r="M357" s="3" t="n"/>
-      <c r="U357" s="2" t="n"/>
-      <c r="Y357" s="3" t="n"/>
+      <c r="V357" s="2" t="n"/>
+      <c r="Z357" s="3" t="n"/>
     </row>
     <row r="358">
       <c r="A358" s="2" t="n"/>
       <c r="C358" s="2" t="n"/>
       <c r="G358" s="2" t="n"/>
       <c r="M358" s="3" t="n"/>
-      <c r="U358" s="2" t="n"/>
-      <c r="Y358" s="3" t="n"/>
+      <c r="V358" s="2" t="n"/>
+      <c r="Z358" s="3" t="n"/>
     </row>
     <row r="359">
       <c r="A359" s="2" t="n"/>
       <c r="C359" s="2" t="n"/>
       <c r="G359" s="2" t="n"/>
       <c r="M359" s="3" t="n"/>
-      <c r="U359" s="2" t="n"/>
-      <c r="Y359" s="3" t="n"/>
+      <c r="V359" s="2" t="n"/>
+      <c r="Z359" s="3" t="n"/>
     </row>
     <row r="360">
       <c r="A360" s="2" t="n"/>
       <c r="C360" s="2" t="n"/>
       <c r="G360" s="2" t="n"/>
       <c r="M360" s="3" t="n"/>
-      <c r="U360" s="2" t="n"/>
-      <c r="Y360" s="3" t="n"/>
+      <c r="V360" s="2" t="n"/>
+      <c r="Z360" s="3" t="n"/>
     </row>
     <row r="361">
       <c r="A361" s="2" t="n"/>
       <c r="C361" s="2" t="n"/>
       <c r="G361" s="2" t="n"/>
       <c r="M361" s="3" t="n"/>
-      <c r="U361" s="2" t="n"/>
-      <c r="Y361" s="3" t="n"/>
+      <c r="V361" s="2" t="n"/>
+      <c r="Z361" s="3" t="n"/>
     </row>
     <row r="362">
       <c r="A362" s="2" t="n"/>
       <c r="C362" s="2" t="n"/>
       <c r="G362" s="2" t="n"/>
       <c r="M362" s="3" t="n"/>
-      <c r="U362" s="2" t="n"/>
-      <c r="Y362" s="3" t="n"/>
+      <c r="V362" s="2" t="n"/>
+      <c r="Z362" s="3" t="n"/>
     </row>
     <row r="363">
       <c r="A363" s="2" t="n"/>
       <c r="C363" s="2" t="n"/>
       <c r="G363" s="2" t="n"/>
       <c r="M363" s="3" t="n"/>
-      <c r="U363" s="2" t="n"/>
-      <c r="Y363" s="3" t="n"/>
+      <c r="V363" s="2" t="n"/>
+      <c r="Z363" s="3" t="n"/>
     </row>
     <row r="364">
       <c r="A364" s="2" t="n"/>
       <c r="C364" s="2" t="n"/>
       <c r="G364" s="2" t="n"/>
       <c r="M364" s="3" t="n"/>
-      <c r="U364" s="2" t="n"/>
-      <c r="Y364" s="3" t="n"/>
+      <c r="V364" s="2" t="n"/>
+      <c r="Z364" s="3" t="n"/>
     </row>
     <row r="365">
       <c r="A365" s="2" t="n"/>
       <c r="C365" s="2" t="n"/>
       <c r="G365" s="2" t="n"/>
       <c r="M365" s="3" t="n"/>
-      <c r="U365" s="2" t="n"/>
-      <c r="Y365" s="3" t="n"/>
+      <c r="V365" s="2" t="n"/>
+      <c r="Z365" s="3" t="n"/>
     </row>
     <row r="366">
       <c r="A366" s="2" t="n"/>
       <c r="C366" s="2" t="n"/>
       <c r="G366" s="2" t="n"/>
       <c r="M366" s="3" t="n"/>
-      <c r="U366" s="2" t="n"/>
-      <c r="Y366" s="3" t="n"/>
+      <c r="V366" s="2" t="n"/>
+      <c r="Z366" s="3" t="n"/>
     </row>
     <row r="367">
       <c r="A367" s="2" t="n"/>
       <c r="C367" s="2" t="n"/>
       <c r="G367" s="2" t="n"/>
       <c r="M367" s="3" t="n"/>
-      <c r="U367" s="2" t="n"/>
-      <c r="Y367" s="3" t="n"/>
+      <c r="V367" s="2" t="n"/>
+      <c r="Z367" s="3" t="n"/>
     </row>
     <row r="368">
       <c r="A368" s="2" t="n"/>
       <c r="C368" s="2" t="n"/>
       <c r="G368" s="2" t="n"/>
       <c r="M368" s="3" t="n"/>
-      <c r="U368" s="2" t="n"/>
-      <c r="Y368" s="3" t="n"/>
+      <c r="V368" s="2" t="n"/>
+      <c r="Z368" s="3" t="n"/>
     </row>
     <row r="369">
       <c r="A369" s="2" t="n"/>
       <c r="C369" s="2" t="n"/>
       <c r="G369" s="2" t="n"/>
       <c r="M369" s="3" t="n"/>
-      <c r="U369" s="2" t="n"/>
-      <c r="Y369" s="3" t="n"/>
+      <c r="V369" s="2" t="n"/>
+      <c r="Z369" s="3" t="n"/>
     </row>
     <row r="370">
       <c r="A370" s="2" t="n"/>
       <c r="C370" s="2" t="n"/>
       <c r="G370" s="2" t="n"/>
       <c r="M370" s="3" t="n"/>
-      <c r="U370" s="2" t="n"/>
-      <c r="Y370" s="3" t="n"/>
+      <c r="V370" s="2" t="n"/>
+      <c r="Z370" s="3" t="n"/>
     </row>
     <row r="371">
       <c r="A371" s="2" t="n"/>
       <c r="C371" s="2" t="n"/>
       <c r="G371" s="2" t="n"/>
       <c r="M371" s="3" t="n"/>
-      <c r="U371" s="2" t="n"/>
-      <c r="Y371" s="3" t="n"/>
+      <c r="V371" s="2" t="n"/>
+      <c r="Z371" s="3" t="n"/>
     </row>
     <row r="372">
       <c r="A372" s="2" t="n"/>
       <c r="C372" s="2" t="n"/>
       <c r="G372" s="2" t="n"/>
       <c r="M372" s="3" t="n"/>
-      <c r="U372" s="2" t="n"/>
-      <c r="Y372" s="3" t="n"/>
+      <c r="V372" s="2" t="n"/>
+      <c r="Z372" s="3" t="n"/>
     </row>
     <row r="373">
       <c r="A373" s="2" t="n"/>
       <c r="C373" s="2" t="n"/>
       <c r="G373" s="2" t="n"/>
       <c r="M373" s="3" t="n"/>
-      <c r="U373" s="2" t="n"/>
-      <c r="Y373" s="3" t="n"/>
+      <c r="V373" s="2" t="n"/>
+      <c r="Z373" s="3" t="n"/>
     </row>
     <row r="374">
       <c r="A374" s="2" t="n"/>
       <c r="C374" s="2" t="n"/>
       <c r="G374" s="2" t="n"/>
       <c r="M374" s="3" t="n"/>
-      <c r="U374" s="2" t="n"/>
-      <c r="Y374" s="3" t="n"/>
+      <c r="V374" s="2" t="n"/>
+      <c r="Z374" s="3" t="n"/>
     </row>
     <row r="375">
       <c r="A375" s="2" t="n"/>
       <c r="C375" s="2" t="n"/>
       <c r="G375" s="2" t="n"/>
       <c r="M375" s="3" t="n"/>
-      <c r="U375" s="2" t="n"/>
-      <c r="Y375" s="3" t="n"/>
+      <c r="V375" s="2" t="n"/>
+      <c r="Z375" s="3" t="n"/>
     </row>
     <row r="376">
       <c r="A376" s="2" t="n"/>
       <c r="C376" s="2" t="n"/>
       <c r="G376" s="2" t="n"/>
       <c r="M376" s="3" t="n"/>
-      <c r="U376" s="2" t="n"/>
-      <c r="Y376" s="3" t="n"/>
+      <c r="V376" s="2" t="n"/>
+      <c r="Z376" s="3" t="n"/>
     </row>
     <row r="377">
       <c r="A377" s="2" t="n"/>
       <c r="C377" s="2" t="n"/>
       <c r="G377" s="2" t="n"/>
       <c r="M377" s="3" t="n"/>
-      <c r="U377" s="2" t="n"/>
-      <c r="Y377" s="3" t="n"/>
+      <c r="V377" s="2" t="n"/>
+      <c r="Z377" s="3" t="n"/>
     </row>
     <row r="378">
       <c r="A378" s="2" t="n"/>
       <c r="C378" s="2" t="n"/>
       <c r="G378" s="2" t="n"/>
       <c r="M378" s="3" t="n"/>
-      <c r="U378" s="2" t="n"/>
-      <c r="Y378" s="3" t="n"/>
+      <c r="V378" s="2" t="n"/>
+      <c r="Z378" s="3" t="n"/>
     </row>
     <row r="379">
       <c r="A379" s="2" t="n"/>
       <c r="C379" s="2" t="n"/>
       <c r="G379" s="2" t="n"/>
       <c r="M379" s="3" t="n"/>
-      <c r="U379" s="2" t="n"/>
-      <c r="Y379" s="3" t="n"/>
+      <c r="V379" s="2" t="n"/>
+      <c r="Z379" s="3" t="n"/>
     </row>
     <row r="380">
       <c r="A380" s="2" t="n"/>
       <c r="C380" s="2" t="n"/>
       <c r="G380" s="2" t="n"/>
       <c r="M380" s="3" t="n"/>
-      <c r="U380" s="2" t="n"/>
-      <c r="Y380" s="3" t="n"/>
+      <c r="V380" s="2" t="n"/>
+      <c r="Z380" s="3" t="n"/>
     </row>
     <row r="381">
       <c r="A381" s="2" t="n"/>
       <c r="C381" s="2" t="n"/>
       <c r="G381" s="2" t="n"/>
       <c r="M381" s="3" t="n"/>
-      <c r="U381" s="2" t="n"/>
-      <c r="Y381" s="3" t="n"/>
+      <c r="V381" s="2" t="n"/>
+      <c r="Z381" s="3" t="n"/>
     </row>
     <row r="382">
       <c r="A382" s="2" t="n"/>
       <c r="C382" s="2" t="n"/>
       <c r="G382" s="2" t="n"/>
       <c r="M382" s="3" t="n"/>
-      <c r="U382" s="2" t="n"/>
-      <c r="Y382" s="3" t="n"/>
+      <c r="V382" s="2" t="n"/>
+      <c r="Z382" s="3" t="n"/>
     </row>
     <row r="383">
       <c r="A383" s="2" t="n"/>
       <c r="C383" s="2" t="n"/>
       <c r="G383" s="2" t="n"/>
       <c r="M383" s="3" t="n"/>
-      <c r="U383" s="2" t="n"/>
-      <c r="Y383" s="3" t="n"/>
+      <c r="V383" s="2" t="n"/>
+      <c r="Z383" s="3" t="n"/>
     </row>
     <row r="384">
       <c r="A384" s="2" t="n"/>
       <c r="C384" s="2" t="n"/>
       <c r="G384" s="2" t="n"/>
       <c r="M384" s="3" t="n"/>
-      <c r="U384" s="2" t="n"/>
-      <c r="Y384" s="3" t="n"/>
+      <c r="V384" s="2" t="n"/>
+      <c r="Z384" s="3" t="n"/>
     </row>
     <row r="385">
       <c r="A385" s="2" t="n"/>
       <c r="C385" s="2" t="n"/>
       <c r="G385" s="2" t="n"/>
       <c r="M385" s="3" t="n"/>
-      <c r="U385" s="2" t="n"/>
-      <c r="Y385" s="3" t="n"/>
+      <c r="V385" s="2" t="n"/>
+      <c r="Z385" s="3" t="n"/>
     </row>
     <row r="386">
       <c r="A386" s="2" t="n"/>
       <c r="C386" s="2" t="n"/>
       <c r="G386" s="2" t="n"/>
       <c r="M386" s="3" t="n"/>
-      <c r="U386" s="2" t="n"/>
-      <c r="Y386" s="3" t="n"/>
+      <c r="V386" s="2" t="n"/>
+      <c r="Z386" s="3" t="n"/>
     </row>
     <row r="387">
       <c r="A387" s="2" t="n"/>
       <c r="C387" s="2" t="n"/>
       <c r="G387" s="2" t="n"/>
       <c r="M387" s="3" t="n"/>
-      <c r="U387" s="2" t="n"/>
-      <c r="Y387" s="3" t="n"/>
+      <c r="V387" s="2" t="n"/>
+      <c r="Z387" s="3" t="n"/>
     </row>
     <row r="388">
       <c r="A388" s="2" t="n"/>
       <c r="C388" s="2" t="n"/>
       <c r="G388" s="2" t="n"/>
       <c r="M388" s="3" t="n"/>
-      <c r="U388" s="2" t="n"/>
-      <c r="Y388" s="3" t="n"/>
+      <c r="V388" s="2" t="n"/>
+      <c r="Z388" s="3" t="n"/>
     </row>
     <row r="389">
       <c r="A389" s="2" t="n"/>
       <c r="C389" s="2" t="n"/>
       <c r="G389" s="2" t="n"/>
       <c r="M389" s="3" t="n"/>
-      <c r="U389" s="2" t="n"/>
-      <c r="Y389" s="3" t="n"/>
+      <c r="V389" s="2" t="n"/>
+      <c r="Z389" s="3" t="n"/>
     </row>
     <row r="390">
       <c r="A390" s="2" t="n"/>
       <c r="C390" s="2" t="n"/>
       <c r="G390" s="2" t="n"/>
       <c r="M390" s="3" t="n"/>
-      <c r="U390" s="2" t="n"/>
-      <c r="Y390" s="3" t="n"/>
+      <c r="V390" s="2" t="n"/>
+      <c r="Z390" s="3" t="n"/>
     </row>
     <row r="391">
       <c r="A391" s="2" t="n"/>
       <c r="C391" s="2" t="n"/>
       <c r="G391" s="2" t="n"/>
       <c r="M391" s="3" t="n"/>
-      <c r="U391" s="2" t="n"/>
-      <c r="Y391" s="3" t="n"/>
+      <c r="V391" s="2" t="n"/>
+      <c r="Z391" s="3" t="n"/>
     </row>
     <row r="392">
       <c r="A392" s="2" t="n"/>
       <c r="C392" s="2" t="n"/>
       <c r="G392" s="2" t="n"/>
       <c r="M392" s="3" t="n"/>
-      <c r="U392" s="2" t="n"/>
-      <c r="Y392" s="3" t="n"/>
+      <c r="V392" s="2" t="n"/>
+      <c r="Z392" s="3" t="n"/>
     </row>
     <row r="393">
       <c r="A393" s="2" t="n"/>
       <c r="C393" s="2" t="n"/>
       <c r="G393" s="2" t="n"/>
       <c r="M393" s="3" t="n"/>
-      <c r="U393" s="2" t="n"/>
-      <c r="Y393" s="3" t="n"/>
+      <c r="V393" s="2" t="n"/>
+      <c r="Z393" s="3" t="n"/>
     </row>
     <row r="394">
       <c r="A394" s="2" t="n"/>
       <c r="C394" s="2" t="n"/>
       <c r="G394" s="2" t="n"/>
       <c r="M394" s="3" t="n"/>
-      <c r="U394" s="2" t="n"/>
-      <c r="Y394" s="3" t="n"/>
+      <c r="V394" s="2" t="n"/>
+      <c r="Z394" s="3" t="n"/>
     </row>
     <row r="395">
       <c r="A395" s="2" t="n"/>
       <c r="C395" s="2" t="n"/>
       <c r="G395" s="2" t="n"/>
       <c r="M395" s="3" t="n"/>
-      <c r="U395" s="2" t="n"/>
-      <c r="Y395" s="3" t="n"/>
+      <c r="V395" s="2" t="n"/>
+      <c r="Z395" s="3" t="n"/>
     </row>
     <row r="396">
       <c r="A396" s="2" t="n"/>
       <c r="C396" s="2" t="n"/>
       <c r="G396" s="2" t="n"/>
       <c r="M396" s="3" t="n"/>
-      <c r="U396" s="2" t="n"/>
-      <c r="Y396" s="3" t="n"/>
+      <c r="V396" s="2" t="n"/>
+      <c r="Z396" s="3" t="n"/>
     </row>
     <row r="397">
       <c r="A397" s="2" t="n"/>
       <c r="C397" s="2" t="n"/>
       <c r="G397" s="2" t="n"/>
       <c r="M397" s="3" t="n"/>
-      <c r="U397" s="2" t="n"/>
-      <c r="Y397" s="3" t="n"/>
+      <c r="V397" s="2" t="n"/>
+      <c r="Z397" s="3" t="n"/>
     </row>
     <row r="398">
       <c r="A398" s="2" t="n"/>
       <c r="C398" s="2" t="n"/>
       <c r="G398" s="2" t="n"/>
       <c r="M398" s="3" t="n"/>
-      <c r="U398" s="2" t="n"/>
-      <c r="Y398" s="3" t="n"/>
+      <c r="V398" s="2" t="n"/>
+      <c r="Z398" s="3" t="n"/>
     </row>
     <row r="399">
       <c r="A399" s="2" t="n"/>
       <c r="C399" s="2" t="n"/>
       <c r="G399" s="2" t="n"/>
       <c r="M399" s="3" t="n"/>
-      <c r="U399" s="2" t="n"/>
-      <c r="Y399" s="3" t="n"/>
+      <c r="V399" s="2" t="n"/>
+      <c r="Z399" s="3" t="n"/>
     </row>
     <row r="400">
       <c r="A400" s="2" t="n"/>
       <c r="C400" s="2" t="n"/>
       <c r="G400" s="2" t="n"/>
       <c r="M400" s="3" t="n"/>
-      <c r="U400" s="2" t="n"/>
-      <c r="Y400" s="3" t="n"/>
+      <c r="V400" s="2" t="n"/>
+      <c r="Z400" s="3" t="n"/>
     </row>
     <row r="401">
       <c r="A401" s="2" t="n"/>
       <c r="C401" s="2" t="n"/>
       <c r="G401" s="2" t="n"/>
       <c r="M401" s="3" t="n"/>
-      <c r="U401" s="2" t="n"/>
-      <c r="Y401" s="3" t="n"/>
+      <c r="V401" s="2" t="n"/>
+      <c r="Z401" s="3" t="n"/>
     </row>
     <row r="402">
       <c r="A402" s="2" t="n"/>
       <c r="C402" s="2" t="n"/>
       <c r="G402" s="2" t="n"/>
       <c r="M402" s="3" t="n"/>
-      <c r="U402" s="2" t="n"/>
-      <c r="Y402" s="3" t="n"/>
+      <c r="V402" s="2" t="n"/>
+      <c r="Z402" s="3" t="n"/>
     </row>
     <row r="403">
       <c r="A403" s="2" t="n"/>
       <c r="C403" s="2" t="n"/>
       <c r="G403" s="2" t="n"/>
       <c r="M403" s="3" t="n"/>
-      <c r="U403" s="2" t="n"/>
-      <c r="Y403" s="3" t="n"/>
+      <c r="V403" s="2" t="n"/>
+      <c r="Z403" s="3" t="n"/>
     </row>
     <row r="404">
       <c r="A404" s="2" t="n"/>
       <c r="C404" s="2" t="n"/>
       <c r="G404" s="2" t="n"/>
       <c r="M404" s="3" t="n"/>
-      <c r="U404" s="2" t="n"/>
-      <c r="Y404" s="3" t="n"/>
+      <c r="V404" s="2" t="n"/>
+      <c r="Z404" s="3" t="n"/>
     </row>
     <row r="405">
       <c r="A405" s="2" t="n"/>
       <c r="C405" s="2" t="n"/>
       <c r="G405" s="2" t="n"/>
       <c r="M405" s="3" t="n"/>
-      <c r="U405" s="2" t="n"/>
-      <c r="Y405" s="3" t="n"/>
+      <c r="V405" s="2" t="n"/>
+      <c r="Z405" s="3" t="n"/>
     </row>
     <row r="406">
       <c r="A406" s="2" t="n"/>
       <c r="C406" s="2" t="n"/>
       <c r="G406" s="2" t="n"/>
       <c r="M406" s="3" t="n"/>
-      <c r="U406" s="2" t="n"/>
-      <c r="Y406" s="3" t="n"/>
+      <c r="V406" s="2" t="n"/>
+      <c r="Z406" s="3" t="n"/>
     </row>
     <row r="407">
       <c r="A407" s="2" t="n"/>
       <c r="C407" s="2" t="n"/>
       <c r="G407" s="2" t="n"/>
       <c r="M407" s="3" t="n"/>
-      <c r="U407" s="2" t="n"/>
-      <c r="Y407" s="3" t="n"/>
+      <c r="V407" s="2" t="n"/>
+      <c r="Z407" s="3" t="n"/>
     </row>
     <row r="408">
       <c r="A408" s="2" t="n"/>
       <c r="C408" s="2" t="n"/>
       <c r="G408" s="2" t="n"/>
       <c r="M408" s="3" t="n"/>
-      <c r="U408" s="2" t="n"/>
-      <c r="Y408" s="3" t="n"/>
+      <c r="V408" s="2" t="n"/>
+      <c r="Z408" s="3" t="n"/>
     </row>
     <row r="409">
       <c r="A409" s="2" t="n"/>
       <c r="C409" s="2" t="n"/>
       <c r="G409" s="2" t="n"/>
       <c r="M409" s="3" t="n"/>
-      <c r="U409" s="2" t="n"/>
-      <c r="Y409" s="3" t="n"/>
+      <c r="V409" s="2" t="n"/>
+      <c r="Z409" s="3" t="n"/>
     </row>
     <row r="410">
       <c r="A410" s="2" t="n"/>
       <c r="C410" s="2" t="n"/>
       <c r="G410" s="2" t="n"/>
       <c r="M410" s="3" t="n"/>
-      <c r="U410" s="2" t="n"/>
-      <c r="Y410" s="3" t="n"/>
+      <c r="V410" s="2" t="n"/>
+      <c r="Z410" s="3" t="n"/>
     </row>
     <row r="411">
       <c r="A411" s="2" t="n"/>
       <c r="C411" s="2" t="n"/>
       <c r="G411" s="2" t="n"/>
       <c r="M411" s="3" t="n"/>
-      <c r="U411" s="2" t="n"/>
-      <c r="Y411" s="3" t="n"/>
+      <c r="V411" s="2" t="n"/>
+      <c r="Z411" s="3" t="n"/>
     </row>
     <row r="412">
       <c r="A412" s="2" t="n"/>
       <c r="C412" s="2" t="n"/>
       <c r="G412" s="2" t="n"/>
       <c r="M412" s="3" t="n"/>
-      <c r="U412" s="2" t="n"/>
-      <c r="Y412" s="3" t="n"/>
+      <c r="V412" s="2" t="n"/>
+      <c r="Z412" s="3" t="n"/>
     </row>
     <row r="413">
       <c r="A413" s="2" t="n"/>
       <c r="C413" s="2" t="n"/>
       <c r="G413" s="2" t="n"/>
       <c r="M413" s="3" t="n"/>
-      <c r="U413" s="2" t="n"/>
-      <c r="Y413" s="3" t="n"/>
+      <c r="V413" s="2" t="n"/>
+      <c r="Z413" s="3" t="n"/>
     </row>
     <row r="414">
       <c r="A414" s="2" t="n"/>
       <c r="C414" s="2" t="n"/>
       <c r="G414" s="2" t="n"/>
       <c r="M414" s="3" t="n"/>
-      <c r="U414" s="2" t="n"/>
-      <c r="Y414" s="3" t="n"/>
+      <c r="V414" s="2" t="n"/>
+      <c r="Z414" s="3" t="n"/>
     </row>
     <row r="415">
       <c r="A415" s="2" t="n"/>
       <c r="C415" s="2" t="n"/>
       <c r="G415" s="2" t="n"/>
       <c r="M415" s="3" t="n"/>
-      <c r="U415" s="2" t="n"/>
-      <c r="Y415" s="3" t="n"/>
+      <c r="V415" s="2" t="n"/>
+      <c r="Z415" s="3" t="n"/>
     </row>
     <row r="416">
       <c r="A416" s="2" t="n"/>
       <c r="C416" s="2" t="n"/>
       <c r="G416" s="2" t="n"/>
       <c r="M416" s="3" t="n"/>
-      <c r="U416" s="2" t="n"/>
-      <c r="Y416" s="3" t="n"/>
+      <c r="V416" s="2" t="n"/>
+      <c r="Z416" s="3" t="n"/>
     </row>
     <row r="417">
       <c r="A417" s="2" t="n"/>
       <c r="C417" s="2" t="n"/>
       <c r="G417" s="2" t="n"/>
       <c r="M417" s="3" t="n"/>
-      <c r="U417" s="2" t="n"/>
-      <c r="Y417" s="3" t="n"/>
+      <c r="V417" s="2" t="n"/>
+      <c r="Z417" s="3" t="n"/>
     </row>
     <row r="418">
       <c r="A418" s="2" t="n"/>
       <c r="C418" s="2" t="n"/>
       <c r="G418" s="2" t="n"/>
       <c r="M418" s="3" t="n"/>
-      <c r="U418" s="2" t="n"/>
-      <c r="Y418" s="3" t="n"/>
+      <c r="V418" s="2" t="n"/>
+      <c r="Z418" s="3" t="n"/>
     </row>
     <row r="419">
       <c r="A419" s="2" t="n"/>
       <c r="C419" s="2" t="n"/>
       <c r="G419" s="2" t="n"/>
       <c r="M419" s="3" t="n"/>
-      <c r="U419" s="2" t="n"/>
-      <c r="Y419" s="3" t="n"/>
+      <c r="V419" s="2" t="n"/>
+      <c r="Z419" s="3" t="n"/>
     </row>
     <row r="420">
       <c r="A420" s="2" t="n"/>
       <c r="C420" s="2" t="n"/>
       <c r="G420" s="2" t="n"/>
       <c r="M420" s="3" t="n"/>
-      <c r="U420" s="2" t="n"/>
-      <c r="Y420" s="3" t="n"/>
+      <c r="V420" s="2" t="n"/>
+      <c r="Z420" s="3" t="n"/>
     </row>
     <row r="421">
       <c r="A421" s="2" t="n"/>
       <c r="C421" s="2" t="n"/>
       <c r="G421" s="2" t="n"/>
       <c r="M421" s="3" t="n"/>
-      <c r="U421" s="2" t="n"/>
-      <c r="Y421" s="3" t="n"/>
+      <c r="V421" s="2" t="n"/>
+      <c r="Z421" s="3" t="n"/>
     </row>
     <row r="422">
       <c r="A422" s="2" t="n"/>
       <c r="C422" s="2" t="n"/>
       <c r="G422" s="2" t="n"/>
       <c r="M422" s="3" t="n"/>
-      <c r="U422" s="2" t="n"/>
-      <c r="Y422" s="3" t="n"/>
+      <c r="V422" s="2" t="n"/>
+      <c r="Z422" s="3" t="n"/>
     </row>
     <row r="423">
       <c r="A423" s="2" t="n"/>
       <c r="C423" s="2" t="n"/>
       <c r="G423" s="2" t="n"/>
       <c r="M423" s="3" t="n"/>
-      <c r="U423" s="2" t="n"/>
-      <c r="Y423" s="3" t="n"/>
+      <c r="V423" s="2" t="n"/>
+      <c r="Z423" s="3" t="n"/>
     </row>
     <row r="424">
       <c r="A424" s="2" t="n"/>
       <c r="C424" s="2" t="n"/>
       <c r="G424" s="2" t="n"/>
       <c r="M424" s="3" t="n"/>
-      <c r="U424" s="2" t="n"/>
-      <c r="Y424" s="3" t="n"/>
+      <c r="V424" s="2" t="n"/>
+      <c r="Z424" s="3" t="n"/>
     </row>
     <row r="425">
       <c r="A425" s="2" t="n"/>
       <c r="C425" s="2" t="n"/>
       <c r="G425" s="2" t="n"/>
       <c r="M425" s="3" t="n"/>
-      <c r="U425" s="2" t="n"/>
-      <c r="Y425" s="3" t="n"/>
+      <c r="V425" s="2" t="n"/>
+      <c r="Z425" s="3" t="n"/>
     </row>
     <row r="426">
       <c r="A426" s="2" t="n"/>
       <c r="C426" s="2" t="n"/>
       <c r="G426" s="2" t="n"/>
       <c r="M426" s="3" t="n"/>
-      <c r="U426" s="2" t="n"/>
-      <c r="Y426" s="3" t="n"/>
+      <c r="V426" s="2" t="n"/>
+      <c r="Z426" s="3" t="n"/>
     </row>
     <row r="427">
       <c r="A427" s="2" t="n"/>
       <c r="C427" s="2" t="n"/>
       <c r="G427" s="2" t="n"/>
       <c r="M427" s="3" t="n"/>
-      <c r="U427" s="2" t="n"/>
-      <c r="Y427" s="3" t="n"/>
+      <c r="V427" s="2" t="n"/>
+      <c r="Z427" s="3" t="n"/>
     </row>
     <row r="428">
       <c r="A428" s="2" t="n"/>
       <c r="C428" s="2" t="n"/>
       <c r="G428" s="2" t="n"/>
       <c r="M428" s="3" t="n"/>
-      <c r="U428" s="2" t="n"/>
-      <c r="Y428" s="3" t="n"/>
+      <c r="V428" s="2" t="n"/>
+      <c r="Z428" s="3" t="n"/>
     </row>
     <row r="429">
       <c r="A429" s="2" t="n"/>
       <c r="C429" s="2" t="n"/>
       <c r="G429" s="2" t="n"/>
       <c r="M429" s="3" t="n"/>
-      <c r="U429" s="2" t="n"/>
-      <c r="Y429" s="3" t="n"/>
+      <c r="V429" s="2" t="n"/>
+      <c r="Z429" s="3" t="n"/>
     </row>
     <row r="430">
       <c r="A430" s="2" t="n"/>
       <c r="C430" s="2" t="n"/>
       <c r="G430" s="2" t="n"/>
       <c r="M430" s="3" t="n"/>
-      <c r="U430" s="2" t="n"/>
-      <c r="Y430" s="3" t="n"/>
+      <c r="V430" s="2" t="n"/>
+      <c r="Z430" s="3" t="n"/>
     </row>
     <row r="431">
       <c r="A431" s="2" t="n"/>
       <c r="C431" s="2" t="n"/>
       <c r="G431" s="2" t="n"/>
       <c r="M431" s="3" t="n"/>
-      <c r="U431" s="2" t="n"/>
-      <c r="Y431" s="3" t="n"/>
+      <c r="V431" s="2" t="n"/>
+      <c r="Z431" s="3" t="n"/>
     </row>
     <row r="432">
       <c r="A432" s="2" t="n"/>
       <c r="C432" s="2" t="n"/>
       <c r="G432" s="2" t="n"/>
       <c r="M432" s="3" t="n"/>
-      <c r="U432" s="2" t="n"/>
-      <c r="Y432" s="3" t="n"/>
+      <c r="V432" s="2" t="n"/>
+      <c r="Z432" s="3" t="n"/>
     </row>
     <row r="433">
       <c r="A433" s="2" t="n"/>
       <c r="C433" s="2" t="n"/>
       <c r="G433" s="2" t="n"/>
       <c r="M433" s="3" t="n"/>
-      <c r="U433" s="2" t="n"/>
-      <c r="Y433" s="3" t="n"/>
+      <c r="V433" s="2" t="n"/>
+      <c r="Z433" s="3" t="n"/>
     </row>
     <row r="434">
       <c r="A434" s="2" t="n"/>
       <c r="C434" s="2" t="n"/>
       <c r="G434" s="2" t="n"/>
       <c r="M434" s="3" t="n"/>
-      <c r="U434" s="2" t="n"/>
-      <c r="Y434" s="3" t="n"/>
+      <c r="V434" s="2" t="n"/>
+      <c r="Z434" s="3" t="n"/>
     </row>
     <row r="435">
       <c r="A435" s="2" t="n"/>
       <c r="C435" s="2" t="n"/>
       <c r="G435" s="2" t="n"/>
       <c r="M435" s="3" t="n"/>
-      <c r="U435" s="2" t="n"/>
-      <c r="Y435" s="3" t="n"/>
+      <c r="V435" s="2" t="n"/>
+      <c r="Z435" s="3" t="n"/>
     </row>
     <row r="436">
       <c r="A436" s="2" t="n"/>
       <c r="C436" s="2" t="n"/>
       <c r="G436" s="2" t="n"/>
       <c r="M436" s="3" t="n"/>
-      <c r="U436" s="2" t="n"/>
-      <c r="Y436" s="3" t="n"/>
+      <c r="V436" s="2" t="n"/>
+      <c r="Z436" s="3" t="n"/>
     </row>
     <row r="437">
       <c r="A437" s="2" t="n"/>
       <c r="C437" s="2" t="n"/>
       <c r="G437" s="2" t="n"/>
       <c r="M437" s="3" t="n"/>
-      <c r="U437" s="2" t="n"/>
-      <c r="Y437" s="3" t="n"/>
+      <c r="V437" s="2" t="n"/>
+      <c r="Z437" s="3" t="n"/>
     </row>
     <row r="438">
       <c r="A438" s="2" t="n"/>
       <c r="C438" s="2" t="n"/>
       <c r="G438" s="2" t="n"/>
       <c r="M438" s="3" t="n"/>
-      <c r="U438" s="2" t="n"/>
-      <c r="Y438" s="3" t="n"/>
+      <c r="V438" s="2" t="n"/>
+      <c r="Z438" s="3" t="n"/>
     </row>
     <row r="439">
       <c r="A439" s="2" t="n"/>
       <c r="C439" s="2" t="n"/>
       <c r="G439" s="2" t="n"/>
       <c r="M439" s="3" t="n"/>
-      <c r="U439" s="2" t="n"/>
-      <c r="Y439" s="3" t="n"/>
+      <c r="V439" s="2" t="n"/>
+      <c r="Z439" s="3" t="n"/>
     </row>
     <row r="440">
       <c r="A440" s="2" t="n"/>
       <c r="C440" s="2" t="n"/>
       <c r="G440" s="2" t="n"/>
       <c r="M440" s="3" t="n"/>
-      <c r="U440" s="2" t="n"/>
-      <c r="Y440" s="3" t="n"/>
+      <c r="V440" s="2" t="n"/>
+      <c r="Z440" s="3" t="n"/>
     </row>
     <row r="441">
       <c r="A441" s="2" t="n"/>
       <c r="C441" s="2" t="n"/>
       <c r="G441" s="2" t="n"/>
       <c r="M441" s="3" t="n"/>
-      <c r="U441" s="2" t="n"/>
-      <c r="Y441" s="3" t="n"/>
+      <c r="V441" s="2" t="n"/>
+      <c r="Z441" s="3" t="n"/>
     </row>
     <row r="442">
       <c r="A442" s="2" t="n"/>
       <c r="C442" s="2" t="n"/>
       <c r="G442" s="2" t="n"/>
       <c r="M442" s="3" t="n"/>
-      <c r="U442" s="2" t="n"/>
-      <c r="Y442" s="3" t="n"/>
+      <c r="V442" s="2" t="n"/>
+      <c r="Z442" s="3" t="n"/>
     </row>
     <row r="443">
       <c r="A443" s="2" t="n"/>
       <c r="C443" s="2" t="n"/>
       <c r="G443" s="2" t="n"/>
       <c r="M443" s="3" t="n"/>
-      <c r="U443" s="2" t="n"/>
-      <c r="Y443" s="3" t="n"/>
+      <c r="V443" s="2" t="n"/>
+      <c r="Z443" s="3" t="n"/>
     </row>
     <row r="444">
       <c r="A444" s="2" t="n"/>
       <c r="C444" s="2" t="n"/>
       <c r="G444" s="2" t="n"/>
       <c r="M444" s="3" t="n"/>
-      <c r="U444" s="2" t="n"/>
-      <c r="Y444" s="3" t="n"/>
+      <c r="V444" s="2" t="n"/>
+      <c r="Z444" s="3" t="n"/>
     </row>
     <row r="445">
       <c r="A445" s="2" t="n"/>
       <c r="C445" s="2" t="n"/>
       <c r="G445" s="2" t="n"/>
       <c r="M445" s="3" t="n"/>
-      <c r="U445" s="2" t="n"/>
-      <c r="Y445" s="3" t="n"/>
+      <c r="V445" s="2" t="n"/>
+      <c r="Z445" s="3" t="n"/>
     </row>
     <row r="446">
       <c r="A446" s="2" t="n"/>
       <c r="C446" s="2" t="n"/>
       <c r="G446" s="2" t="n"/>
       <c r="M446" s="3" t="n"/>
-      <c r="U446" s="2" t="n"/>
-      <c r="Y446" s="3" t="n"/>
+      <c r="V446" s="2" t="n"/>
+      <c r="Z446" s="3" t="n"/>
     </row>
     <row r="447">
       <c r="A447" s="2" t="n"/>
       <c r="C447" s="2" t="n"/>
       <c r="G447" s="2" t="n"/>
       <c r="M447" s="3" t="n"/>
-      <c r="U447" s="2" t="n"/>
-      <c r="Y447" s="3" t="n"/>
+      <c r="V447" s="2" t="n"/>
+      <c r="Z447" s="3" t="n"/>
     </row>
     <row r="448">
       <c r="A448" s="2" t="n"/>
       <c r="C448" s="2" t="n"/>
       <c r="G448" s="2" t="n"/>
       <c r="M448" s="3" t="n"/>
-      <c r="U448" s="2" t="n"/>
-      <c r="Y448" s="3" t="n"/>
+      <c r="V448" s="2" t="n"/>
+      <c r="Z448" s="3" t="n"/>
     </row>
     <row r="449">
       <c r="A449" s="2" t="n"/>
       <c r="C449" s="2" t="n"/>
       <c r="G449" s="2" t="n"/>
       <c r="M449" s="3" t="n"/>
-      <c r="U449" s="2" t="n"/>
-      <c r="Y449" s="3" t="n"/>
+      <c r="V449" s="2" t="n"/>
+      <c r="Z449" s="3" t="n"/>
     </row>
     <row r="450">
       <c r="A450" s="2" t="n"/>
       <c r="C450" s="2" t="n"/>
       <c r="G450" s="2" t="n"/>
       <c r="M450" s="3" t="n"/>
-      <c r="U450" s="2" t="n"/>
-      <c r="Y450" s="3" t="n"/>
+      <c r="V450" s="2" t="n"/>
+      <c r="Z450" s="3" t="n"/>
     </row>
     <row r="451">
       <c r="A451" s="2" t="n"/>
       <c r="C451" s="2" t="n"/>
       <c r="G451" s="2" t="n"/>
       <c r="M451" s="3" t="n"/>
-      <c r="U451" s="2" t="n"/>
-      <c r="Y451" s="3" t="n"/>
+      <c r="V451" s="2" t="n"/>
+      <c r="Z451" s="3" t="n"/>
     </row>
     <row r="452">
       <c r="A452" s="2" t="n"/>
       <c r="C452" s="2" t="n"/>
       <c r="G452" s="2" t="n"/>
       <c r="M452" s="3" t="n"/>
-      <c r="U452" s="2" t="n"/>
-      <c r="Y452" s="3" t="n"/>
+      <c r="V452" s="2" t="n"/>
+      <c r="Z452" s="3" t="n"/>
     </row>
     <row r="453">
       <c r="A453" s="2" t="n"/>
       <c r="C453" s="2" t="n"/>
       <c r="G453" s="2" t="n"/>
       <c r="M453" s="3" t="n"/>
-      <c r="U453" s="2" t="n"/>
-      <c r="Y453" s="3" t="n"/>
+      <c r="V453" s="2" t="n"/>
+      <c r="Z453" s="3" t="n"/>
     </row>
     <row r="454">
       <c r="A454" s="2" t="n"/>
       <c r="C454" s="2" t="n"/>
       <c r="G454" s="2" t="n"/>
       <c r="M454" s="3" t="n"/>
-      <c r="U454" s="2" t="n"/>
-      <c r="Y454" s="3" t="n"/>
+      <c r="V454" s="2" t="n"/>
+      <c r="Z454" s="3" t="n"/>
     </row>
     <row r="455">
       <c r="A455" s="2" t="n"/>
       <c r="C455" s="2" t="n"/>
       <c r="G455" s="2" t="n"/>
       <c r="M455" s="3" t="n"/>
-      <c r="U455" s="2" t="n"/>
-      <c r="Y455" s="3" t="n"/>
+      <c r="V455" s="2" t="n"/>
+      <c r="Z455" s="3" t="n"/>
     </row>
     <row r="456">
       <c r="A456" s="2" t="n"/>
       <c r="C456" s="2" t="n"/>
       <c r="G456" s="2" t="n"/>
       <c r="M456" s="3" t="n"/>
-      <c r="U456" s="2" t="n"/>
-      <c r="Y456" s="3" t="n"/>
+      <c r="V456" s="2" t="n"/>
+      <c r="Z456" s="3" t="n"/>
     </row>
     <row r="457">
       <c r="A457" s="2" t="n"/>
       <c r="C457" s="2" t="n"/>
       <c r="G457" s="2" t="n"/>
       <c r="M457" s="3" t="n"/>
-      <c r="U457" s="2" t="n"/>
-      <c r="Y457" s="3" t="n"/>
+      <c r="V457" s="2" t="n"/>
+      <c r="Z457" s="3" t="n"/>
     </row>
     <row r="458">
       <c r="A458" s="2" t="n"/>
       <c r="C458" s="2" t="n"/>
       <c r="G458" s="2" t="n"/>
       <c r="M458" s="3" t="n"/>
-      <c r="U458" s="2" t="n"/>
-      <c r="Y458" s="3" t="n"/>
+      <c r="V458" s="2" t="n"/>
+      <c r="Z458" s="3" t="n"/>
     </row>
     <row r="459">
       <c r="A459" s="2" t="n"/>
       <c r="C459" s="2" t="n"/>
       <c r="G459" s="2" t="n"/>
       <c r="M459" s="3" t="n"/>
-      <c r="U459" s="2" t="n"/>
-      <c r="Y459" s="3" t="n"/>
+      <c r="V459" s="2" t="n"/>
+      <c r="Z459" s="3" t="n"/>
     </row>
     <row r="460">
       <c r="A460" s="2" t="n"/>
       <c r="C460" s="2" t="n"/>
       <c r="G460" s="2" t="n"/>
       <c r="M460" s="3" t="n"/>
-      <c r="U460" s="2" t="n"/>
-      <c r="Y460" s="3" t="n"/>
+      <c r="V460" s="2" t="n"/>
+      <c r="Z460" s="3" t="n"/>
     </row>
     <row r="461">
       <c r="A461" s="2" t="n"/>
       <c r="C461" s="2" t="n"/>
       <c r="G461" s="2" t="n"/>
       <c r="M461" s="3" t="n"/>
-      <c r="U461" s="2" t="n"/>
-      <c r="Y461" s="3" t="n"/>
+      <c r="V461" s="2" t="n"/>
+      <c r="Z461" s="3" t="n"/>
     </row>
     <row r="462">
       <c r="A462" s="2" t="n"/>
       <c r="C462" s="2" t="n"/>
       <c r="G462" s="2" t="n"/>
       <c r="M462" s="3" t="n"/>
-      <c r="U462" s="2" t="n"/>
-      <c r="Y462" s="3" t="n"/>
+      <c r="V462" s="2" t="n"/>
+      <c r="Z462" s="3" t="n"/>
     </row>
     <row r="463">
       <c r="A463" s="2" t="n"/>
       <c r="C463" s="2" t="n"/>
       <c r="G463" s="2" t="n"/>
       <c r="M463" s="3" t="n"/>
-      <c r="U463" s="2" t="n"/>
-      <c r="Y463" s="3" t="n"/>
+      <c r="V463" s="2" t="n"/>
+      <c r="Z463" s="3" t="n"/>
     </row>
     <row r="464">
       <c r="A464" s="2" t="n"/>
       <c r="C464" s="2" t="n"/>
       <c r="G464" s="2" t="n"/>
       <c r="M464" s="3" t="n"/>
-      <c r="U464" s="2" t="n"/>
-      <c r="Y464" s="3" t="n"/>
+      <c r="V464" s="2" t="n"/>
+      <c r="Z464" s="3" t="n"/>
     </row>
     <row r="465">
       <c r="A465" s="2" t="n"/>
       <c r="C465" s="2" t="n"/>
       <c r="G465" s="2" t="n"/>
       <c r="M465" s="3" t="n"/>
-      <c r="U465" s="2" t="n"/>
-      <c r="Y465" s="3" t="n"/>
+      <c r="V465" s="2" t="n"/>
+      <c r="Z465" s="3" t="n"/>
     </row>
     <row r="466">
       <c r="A466" s="2" t="n"/>
       <c r="C466" s="2" t="n"/>
       <c r="G466" s="2" t="n"/>
       <c r="M466" s="3" t="n"/>
-      <c r="U466" s="2" t="n"/>
-      <c r="Y466" s="3" t="n"/>
+      <c r="V466" s="2" t="n"/>
+      <c r="Z466" s="3" t="n"/>
     </row>
     <row r="467">
       <c r="A467" s="2" t="n"/>
       <c r="C467" s="2" t="n"/>
       <c r="G467" s="2" t="n"/>
       <c r="M467" s="3" t="n"/>
-      <c r="U467" s="2" t="n"/>
-      <c r="Y467" s="3" t="n"/>
+      <c r="V467" s="2" t="n"/>
+      <c r="Z467" s="3" t="n"/>
     </row>
     <row r="468">
       <c r="A468" s="2" t="n"/>
       <c r="C468" s="2" t="n"/>
       <c r="G468" s="2" t="n"/>
       <c r="M468" s="3" t="n"/>
-      <c r="U468" s="2" t="n"/>
-      <c r="Y468" s="3" t="n"/>
+      <c r="V468" s="2" t="n"/>
+      <c r="Z468" s="3" t="n"/>
     </row>
     <row r="469">
       <c r="A469" s="2" t="n"/>
       <c r="C469" s="2" t="n"/>
       <c r="G469" s="2" t="n"/>
       <c r="M469" s="3" t="n"/>
-      <c r="U469" s="2" t="n"/>
-      <c r="Y469" s="3" t="n"/>
+      <c r="V469" s="2" t="n"/>
+      <c r="Z469" s="3" t="n"/>
     </row>
     <row r="470">
       <c r="A470" s="2" t="n"/>
       <c r="C470" s="2" t="n"/>
       <c r="G470" s="2" t="n"/>
       <c r="M470" s="3" t="n"/>
-      <c r="U470" s="2" t="n"/>
-      <c r="Y470" s="3" t="n"/>
+      <c r="V470" s="2" t="n"/>
+      <c r="Z470" s="3" t="n"/>
     </row>
     <row r="471">
       <c r="A471" s="2" t="n"/>
       <c r="C471" s="2" t="n"/>
       <c r="G471" s="2" t="n"/>
       <c r="M471" s="3" t="n"/>
-      <c r="U471" s="2" t="n"/>
-      <c r="Y471" s="3" t="n"/>
+      <c r="V471" s="2" t="n"/>
+      <c r="Z471" s="3" t="n"/>
     </row>
     <row r="472">
       <c r="A472" s="2" t="n"/>
       <c r="C472" s="2" t="n"/>
       <c r="G472" s="2" t="n"/>
       <c r="M472" s="3" t="n"/>
-      <c r="U472" s="2" t="n"/>
-      <c r="Y472" s="3" t="n"/>
+      <c r="V472" s="2" t="n"/>
+      <c r="Z472" s="3" t="n"/>
     </row>
     <row r="473">
       <c r="A473" s="2" t="n"/>
       <c r="C473" s="2" t="n"/>
       <c r="G473" s="2" t="n"/>
       <c r="M473" s="3" t="n"/>
-      <c r="U473" s="2" t="n"/>
-      <c r="Y473" s="3" t="n"/>
+      <c r="V473" s="2" t="n"/>
+      <c r="Z473" s="3" t="n"/>
     </row>
     <row r="474">
       <c r="A474" s="2" t="n"/>
       <c r="C474" s="2" t="n"/>
       <c r="G474" s="2" t="n"/>
       <c r="M474" s="3" t="n"/>
-      <c r="U474" s="2" t="n"/>
-      <c r="Y474" s="3" t="n"/>
+      <c r="V474" s="2" t="n"/>
+      <c r="Z474" s="3" t="n"/>
     </row>
     <row r="475">
       <c r="A475" s="2" t="n"/>
       <c r="C475" s="2" t="n"/>
       <c r="G475" s="2" t="n"/>
       <c r="M475" s="3" t="n"/>
-      <c r="U475" s="2" t="n"/>
-      <c r="Y475" s="3" t="n"/>
+      <c r="V475" s="2" t="n"/>
+      <c r="Z475" s="3" t="n"/>
     </row>
     <row r="476">
       <c r="A476" s="2" t="n"/>
       <c r="C476" s="2" t="n"/>
       <c r="G476" s="2" t="n"/>
       <c r="M476" s="3" t="n"/>
-      <c r="U476" s="2" t="n"/>
-      <c r="Y476" s="3" t="n"/>
+      <c r="V476" s="2" t="n"/>
+      <c r="Z476" s="3" t="n"/>
     </row>
     <row r="477">
       <c r="A477" s="2" t="n"/>
       <c r="C477" s="2" t="n"/>
       <c r="G477" s="2" t="n"/>
       <c r="M477" s="3" t="n"/>
-      <c r="U477" s="2" t="n"/>
-      <c r="Y477" s="3" t="n"/>
+      <c r="V477" s="2" t="n"/>
+      <c r="Z477" s="3" t="n"/>
     </row>
     <row r="478">
       <c r="A478" s="2" t="n"/>
       <c r="C478" s="2" t="n"/>
       <c r="G478" s="2" t="n"/>
       <c r="M478" s="3" t="n"/>
-      <c r="U478" s="2" t="n"/>
-      <c r="Y478" s="3" t="n"/>
+      <c r="V478" s="2" t="n"/>
+      <c r="Z478" s="3" t="n"/>
     </row>
     <row r="479">
       <c r="A479" s="2" t="n"/>
       <c r="C479" s="2" t="n"/>
       <c r="G479" s="2" t="n"/>
       <c r="M479" s="3" t="n"/>
-      <c r="U479" s="2" t="n"/>
-      <c r="Y479" s="3" t="n"/>
+      <c r="V479" s="2" t="n"/>
+      <c r="Z479" s="3" t="n"/>
     </row>
     <row r="480">
       <c r="A480" s="2" t="n"/>
       <c r="C480" s="2" t="n"/>
       <c r="G480" s="2" t="n"/>
       <c r="M480" s="3" t="n"/>
-      <c r="U480" s="2" t="n"/>
-      <c r="Y480" s="3" t="n"/>
+      <c r="V480" s="2" t="n"/>
+      <c r="Z480" s="3" t="n"/>
     </row>
     <row r="481">
       <c r="A481" s="2" t="n"/>
       <c r="C481" s="2" t="n"/>
       <c r="G481" s="2" t="n"/>
       <c r="M481" s="3" t="n"/>
-      <c r="U481" s="2" t="n"/>
-      <c r="Y481" s="3" t="n"/>
+      <c r="V481" s="2" t="n"/>
+      <c r="Z481" s="3" t="n"/>
     </row>
     <row r="482">
       <c r="A482" s="2" t="n"/>
       <c r="C482" s="2" t="n"/>
       <c r="G482" s="2" t="n"/>
       <c r="M482" s="3" t="n"/>
-      <c r="U482" s="2" t="n"/>
-      <c r="Y482" s="3" t="n"/>
+      <c r="V482" s="2" t="n"/>
+      <c r="Z482" s="3" t="n"/>
     </row>
     <row r="483">
       <c r="A483" s="2" t="n"/>
       <c r="C483" s="2" t="n"/>
       <c r="G483" s="2" t="n"/>
       <c r="M483" s="3" t="n"/>
-      <c r="U483" s="2" t="n"/>
-      <c r="Y483" s="3" t="n"/>
+      <c r="V483" s="2" t="n"/>
+      <c r="Z483" s="3" t="n"/>
     </row>
     <row r="484">
       <c r="A484" s="2" t="n"/>
       <c r="C484" s="2" t="n"/>
       <c r="G484" s="2" t="n"/>
       <c r="M484" s="3" t="n"/>
-      <c r="U484" s="2" t="n"/>
-      <c r="Y484" s="3" t="n"/>
+      <c r="V484" s="2" t="n"/>
+      <c r="Z484" s="3" t="n"/>
     </row>
     <row r="485">
       <c r="A485" s="2" t="n"/>
       <c r="C485" s="2" t="n"/>
       <c r="G485" s="2" t="n"/>
       <c r="M485" s="3" t="n"/>
-      <c r="U485" s="2" t="n"/>
-      <c r="Y485" s="3" t="n"/>
+      <c r="V485" s="2" t="n"/>
+      <c r="Z485" s="3" t="n"/>
     </row>
     <row r="486">
       <c r="A486" s="2" t="n"/>
       <c r="C486" s="2" t="n"/>
       <c r="G486" s="2" t="n"/>
       <c r="M486" s="3" t="n"/>
-      <c r="U486" s="2" t="n"/>
-      <c r="Y486" s="3" t="n"/>
+      <c r="V486" s="2" t="n"/>
+      <c r="Z486" s="3" t="n"/>
     </row>
     <row r="487">
       <c r="A487" s="2" t="n"/>
       <c r="C487" s="2" t="n"/>
       <c r="G487" s="2" t="n"/>
       <c r="M487" s="3" t="n"/>
-      <c r="U487" s="2" t="n"/>
-      <c r="Y487" s="3" t="n"/>
+      <c r="V487" s="2" t="n"/>
+      <c r="Z487" s="3" t="n"/>
     </row>
     <row r="488">
       <c r="A488" s="2" t="n"/>
       <c r="C488" s="2" t="n"/>
       <c r="G488" s="2" t="n"/>
       <c r="M488" s="3" t="n"/>
-      <c r="U488" s="2" t="n"/>
-      <c r="Y488" s="3" t="n"/>
+      <c r="V488" s="2" t="n"/>
+      <c r="Z488" s="3" t="n"/>
     </row>
     <row r="489">
       <c r="A489" s="2" t="n"/>
       <c r="C489" s="2" t="n"/>
       <c r="G489" s="2" t="n"/>
       <c r="M489" s="3" t="n"/>
-      <c r="U489" s="2" t="n"/>
-      <c r="Y489" s="3" t="n"/>
+      <c r="V489" s="2" t="n"/>
+      <c r="Z489" s="3" t="n"/>
     </row>
     <row r="490">
       <c r="A490" s="2" t="n"/>
       <c r="C490" s="2" t="n"/>
       <c r="G490" s="2" t="n"/>
       <c r="M490" s="3" t="n"/>
-      <c r="U490" s="2" t="n"/>
-      <c r="Y490" s="3" t="n"/>
+      <c r="V490" s="2" t="n"/>
+      <c r="Z490" s="3" t="n"/>
     </row>
     <row r="491">
       <c r="A491" s="2" t="n"/>
       <c r="C491" s="2" t="n"/>
       <c r="G491" s="2" t="n"/>
       <c r="M491" s="3" t="n"/>
-      <c r="U491" s="2" t="n"/>
-      <c r="Y491" s="3" t="n"/>
+      <c r="V491" s="2" t="n"/>
+      <c r="Z491" s="3" t="n"/>
     </row>
     <row r="492">
       <c r="A492" s="2" t="n"/>
       <c r="C492" s="2" t="n"/>
       <c r="G492" s="2" t="n"/>
       <c r="M492" s="3" t="n"/>
-      <c r="U492" s="2" t="n"/>
-      <c r="Y492" s="3" t="n"/>
+      <c r="V492" s="2" t="n"/>
+      <c r="Z492" s="3" t="n"/>
     </row>
     <row r="493">
       <c r="A493" s="2" t="n"/>
       <c r="C493" s="2" t="n"/>
       <c r="G493" s="2" t="n"/>
       <c r="M493" s="3" t="n"/>
-      <c r="U493" s="2" t="n"/>
-      <c r="Y493" s="3" t="n"/>
+      <c r="V493" s="2" t="n"/>
+      <c r="Z493" s="3" t="n"/>
     </row>
     <row r="494">
       <c r="A494" s="2" t="n"/>
       <c r="C494" s="2" t="n"/>
       <c r="G494" s="2" t="n"/>
       <c r="M494" s="3" t="n"/>
-      <c r="U494" s="2" t="n"/>
-      <c r="Y494" s="3" t="n"/>
+      <c r="V494" s="2" t="n"/>
+      <c r="Z494" s="3" t="n"/>
     </row>
     <row r="495">
       <c r="A495" s="2" t="n"/>
       <c r="C495" s="2" t="n"/>
       <c r="G495" s="2" t="n"/>
       <c r="M495" s="3" t="n"/>
-      <c r="U495" s="2" t="n"/>
-      <c r="Y495" s="3" t="n"/>
+      <c r="V495" s="2" t="n"/>
+      <c r="Z495" s="3" t="n"/>
     </row>
     <row r="496">
       <c r="A496" s="2" t="n"/>
       <c r="C496" s="2" t="n"/>
       <c r="G496" s="2" t="n"/>
       <c r="M496" s="3" t="n"/>
-      <c r="U496" s="2" t="n"/>
-      <c r="Y496" s="3" t="n"/>
+      <c r="V496" s="2" t="n"/>
+      <c r="Z496" s="3" t="n"/>
     </row>
     <row r="497">
       <c r="A497" s="2" t="n"/>
       <c r="C497" s="2" t="n"/>
       <c r="G497" s="2" t="n"/>
       <c r="M497" s="3" t="n"/>
-      <c r="U497" s="2" t="n"/>
-      <c r="Y497" s="3" t="n"/>
+      <c r="V497" s="2" t="n"/>
+      <c r="Z497" s="3" t="n"/>
     </row>
     <row r="498">
       <c r="A498" s="2" t="n"/>
       <c r="C498" s="2" t="n"/>
       <c r="G498" s="2" t="n"/>
       <c r="M498" s="3" t="n"/>
-      <c r="U498" s="2" t="n"/>
-      <c r="Y498" s="3" t="n"/>
+      <c r="V498" s="2" t="n"/>
+      <c r="Z498" s="3" t="n"/>
     </row>
     <row r="499">
       <c r="A499" s="2" t="n"/>
       <c r="C499" s="2" t="n"/>
       <c r="G499" s="2" t="n"/>
       <c r="M499" s="3" t="n"/>
-      <c r="U499" s="2" t="n"/>
-      <c r="Y499" s="3" t="n"/>
+      <c r="V499" s="2" t="n"/>
+      <c r="Z499" s="3" t="n"/>
     </row>
     <row r="500">
       <c r="A500" s="2" t="n"/>
       <c r="C500" s="2" t="n"/>
       <c r="G500" s="2" t="n"/>
       <c r="M500" s="3" t="n"/>
-      <c r="U500" s="2" t="n"/>
-      <c r="Y500" s="3" t="n"/>
+      <c r="V500" s="2" t="n"/>
+      <c r="Z500" s="3" t="n"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:Z1"/>
-  <dataValidations count="7">
+  <autoFilter ref="A1:AA1"/>
+  <dataValidations count="8">
     <dataValidation sqref="S2:S500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Ongeldige invoer" error="Kies een geldige waarde uit de lijst." promptTitle="Segment" prompt="Kies een segment uit de lijst." type="list">
       <formula1>"50+,regionaal &lt;50,nog te bepalen,onbekend"</formula1>
     </dataValidation>
-    <dataValidation sqref="W2:W500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Ongeldige invoer" error="Kies een geldige waarde uit de lijst." promptTitle="Resultaat vergelijking" prompt="Kies het resultaat van de vergelijking met de acquisitielijst." type="list">
+    <dataValidation sqref="X2:X500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Ongeldige invoer" error="Kies een geldige waarde uit de lijst." promptTitle="Resultaat vergelijking" prompt="Kies het resultaat van de vergelijking met de acquisitielijst." type="list">
       <formula1>"nog niet gecontroleerd,nieuw,bestaat al"</formula1>
     </dataValidation>
     <dataValidation sqref="L2:L500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Ongeldige invoer" error="Kies een geldige waarde uit de lijst." promptTitle="Bronniveau medewerkers" prompt="Kies het bronniveau voor het medewerkersaantal." type="list">
@@ -5169,13 +5200,16 @@
       <formula1>"Expliciet gedateerd,Actueel/live,Historisch/verouderd,Actualiteit onduidelijk"</formula1>
     </dataValidation>
     <dataValidation sqref="O2:O500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Ongeldige invoer" error="Kies een geldige waarde uit de lijst." promptTitle="Meetniveau medewerkers" prompt="Kies het meetniveau van het medewerkersaantal." type="list">
-      <formula1>"Vestiging,Entiteit,Groep,Onbekend"</formula1>
+      <formula1>"Organisatie,Entiteit,Vestiging,Onbekend"</formula1>
     </dataValidation>
     <dataValidation sqref="P2:P500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Ongeldige invoer" error="Kies een geldige waarde uit de lijst." promptTitle="Eenheid medewerkers" prompt="Werkzame personen is de voorkeursmaatstaf voor de grens van 50 medewerkers." type="list">
       <formula1>"Werkzame personen,FTE,Onbekend"</formula1>
     </dataValidation>
     <dataValidation sqref="Q2:Q500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Ongeldige invoer" error="Kies een geldige waarde uit de lijst." promptTitle="Handmatig beoordeeld" prompt="Is deze lead handmatig beoordeeld?" type="list">
       <formula1>"Ja,Nee"</formula1>
+    </dataValidation>
+    <dataValidation sqref="T2:T500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Ongeldige invoer" error="Kies een geldige waarde uit de lijst." promptTitle="Doelgroepstatus" prompt="Kies: binnen doelgroep / buiten doelgroep / nog niet te bepalen." type="list">
+      <formula1>"binnen doelgroep,buiten doelgroep,nog niet te bepalen"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5188,7 +5222,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B27"/>
+  <dimension ref="A1:B28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -5383,7 +5417,7 @@
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>Keuzelijst: Vestiging / Entiteit / Groep / Onbekend. Niveau waarop het medewerkersaantal is gemeten.</t>
+          <t>Keuzelijst: Organisatie / Entiteit / Vestiging / Onbekend. Organisatie: de onderneming of organisatie als commercieel geheel waarop HAHEBO de prospectbenadering richt. Entiteit: een juridische entiteit, bijvoorbeeld een B.V. binnen een grotere organisatie. Vestiging: een fysieke locatie. Onbekend: niet betrouwbaar vast te stellen op welk niveau het medewerkersgegeven betrekking heeft.</t>
         </is>
       </c>
     </row>
@@ -5438,82 +5472,94 @@
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>Algemeen e-mailadres</t>
+          <t>Doelgroepstatus</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>Algemeen of centraal e-mailadres van het bedrijf.</t>
+          <t>Keuzelijst: binnen doelgroep / buiten doelgroep / nog niet te bepalen. Geeft aan of een lead binnen de commerciele doelgroep van HAHEBO valt nadat onder andere geografische criteria zijn toegepast. binnen doelgroep: lead voldoet aan de vastgestelde doelgroepcriteria. buiten doelgroep: lead is wel geidentificeerd maar valt op basis van vastgestelde criteria buiten de doelgroep. nog niet te bepalen: nog niet alle criteria zijn door HAHEBO vastgesteld of voldoende informatie ontbreekt.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>Telefoonnummer</t>
+          <t>Algemeen e-mailadres</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>Telefoonnummer als tekst, zodat voorloopnullen behouden blijven.</t>
+          <t>Algemeen of centraal e-mailadres van het bedrijf.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>Bron contactgegevens</t>
+          <t>Telefoonnummer</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>Bron waaruit het e-mailadres en/of telefoonnummer afkomstig is.</t>
+          <t>Telefoonnummer als tekst, zodat voorloopnullen behouden blijven.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>Resultaat vergelijking acquisitielijst</t>
+          <t>Bron contactgegevens</t>
         </is>
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>Keuzelijst: nog niet gecontroleerd / nieuw / bestaat al. Standaard 'nog niet gecontroleerd' bij nieuwe regels.</t>
+          <t>Bron waaruit het e-mailadres en/of telefoonnummer afkomstig is.</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>Matchwijze acquisitielijst</t>
+          <t>Resultaat vergelijking acquisitielijst</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>Manier waarop de vergelijking met de acquisitielijst is uitgevoerd (bijv. op naam, KVK-nummer of domein).</t>
+          <t>Keuzelijst: nog niet gecontroleerd / nieuw / bestaat al. Standaard 'nog niet gecontroleerd' bij nieuwe regels.</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>Datum verzameld</t>
+          <t>Matchwijze acquisitielijst</t>
         </is>
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>Datum waarop de leadgegevens zijn verzameld, notatie dd-mm-jjjj.</t>
+          <t>Manier waarop de vergelijking met de acquisitielijst is uitgevoerd (bijv. op naam, KVK-nummer of domein).</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
+          <t>Datum verzameld</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="inlineStr">
+        <is>
+          <t>Datum waarop de leadgegevens zijn verzameld, notatie dd-mm-jjjj.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="5" t="inlineStr">
+        <is>
           <t>Opmerkingen</t>
         </is>
       </c>
-      <c r="B27" s="5" t="inlineStr">
+      <c r="B28" s="5" t="inlineStr">
         <is>
           <t>Vrij invulveld voor aanvullende opmerkingen of bijzonderheden.</t>
         </is>

--- a/data/HAHEBO_leadbestand_pilot.xlsx
+++ b/data/HAHEBO_leadbestand_pilot.xlsx
@@ -1295,28 +1295,409 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="n"/>
-      <c r="E7" s="2" t="n"/>
-      <c r="I7" s="2" t="n"/>
-      <c r="O7" s="3" t="n"/>
-      <c r="X7" s="2" t="n"/>
-      <c r="AB7" s="3" t="n"/>
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>L0006</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>aaff kantoor Boxmeer</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>aaff</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>https://www.aaff.nl/en/locations/boxmeer en https://www.aaff.nl/werken-bij-aaff/over-ons</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>Niet gevonden</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>aaff.nl</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>https://www.aaff.nl</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Boxmeer</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>5831 PJ</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Akkerdistel 4</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Circa 2000</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>Niet gevonden</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>https://www.aaff.nl/werken-bij-aaff/over-ons</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="O7" s="3" t="inlineStr">
+        <is>
+          <t>Onbekend</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Actueel/live</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>Organisatie</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>Onbekend</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>Nee</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>50+</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>nog niet te bepalen</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>info@aaff.nl</t>
+        </is>
+      </c>
+      <c r="X7" s="2" t="inlineStr">
+        <is>
+          <t>+31 485 572120</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>https://www.aaff.nl/en/locations/boxmeer</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>nog niet gecontroleerd</t>
+        </is>
+      </c>
+      <c r="AB7" s="3" t="n">
+        <v>46280</v>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Aantal gebaseerd op de eigen werken-bij-pagina, die spreekt over circa 2000 collega's verspreid over 50 kantoren in Nederland. De bron maakt niet expliciet duidelijk of dit werkzame personen/headcount of fte betreft, daarom staat Eenheid medewerkers op Onbekend. De formulering verwijst wel duidelijk naar personen en het genoemde aantal ligt boven de grens van 50, waardoor segment 50+ volgens de vastgestelde regel mag worden toegekend. Het jaarverslag 2025 noemt 1723 co-eigenaren; dit cijfer is niet als medewerkersaantal gebruikt. Adres, telefoonnummer en e-mailadres komen van de eigen locatiepagina. Het e-mailadres is organisatiebreed en niet vestigingsspecifiek. KVK-nummer van de entiteit achter deze vestiging is niet vastgesteld.</t>
+        </is>
+      </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="n"/>
-      <c r="E8" s="2" t="n"/>
-      <c r="I8" s="2" t="n"/>
-      <c r="O8" s="3" t="n"/>
-      <c r="X8" s="2" t="n"/>
-      <c r="AB8" s="3" t="n"/>
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>L0007</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Mezzo Elzendaal Boxmeer</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Onbekend</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>https://www.omo.nl/scholen/ en https://allecijfers.nl/middelbare-school/mezzo-scholen/</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>Niet gevonden</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>elzendaalcollege.nl</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>https://www.elzendaalcollege.nl</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Boxmeer</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>5831 CW</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>Bilderbeekstraat 27</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Onbekend</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>Niet gevonden</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>Niet gevonden</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>Onbekend</t>
+        </is>
+      </c>
+      <c r="O8" s="3" t="inlineStr">
+        <is>
+          <t>Onbekend</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Actualiteit onduidelijk</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>Onbekend</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>Onbekend</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>Nee</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>onbekend</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>nog niet te bepalen</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>info@elzendaalcollege.nl</t>
+        </is>
+      </c>
+      <c r="X8" s="2" t="inlineStr">
+        <is>
+          <t>0485-572032</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>https://schoolkeuzehulp.nl/middelbare-school/elzendaalcollege-boxmeer/ en https://www.dekonnectkever.nl/organisatie/elzendaalcollege-boxmeer/</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>nog niet gecontroleerd</t>
+        </is>
+      </c>
+      <c r="AB8" s="3" t="n">
+        <v>46280</v>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Organisatiestructuur onzeker: er zijn twee verdedigbare niveaus boven de vestiging. Mezzo Scholen omvat vijf VO-vestigingen en Ons Middelbaar Onderwijs is het bevoegd gezag boven meerdere scholen. Geen onderzochte bron stelt voldoende vast welk niveau voor onze 50-grens als Organisatie moet gelden. Daarom staat Organisatienaam op Onbekend. Er is geen medewerkersgegeven uit een bruikbare A- of B-bron gevonden. Leerlingaantallen zijn geen medewerkersgegevens en zijn niet gebruikt.</t>
+        </is>
+      </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="n"/>
-      <c r="E9" s="2" t="n"/>
-      <c r="I9" s="2" t="n"/>
-      <c r="O9" s="3" t="n"/>
-      <c r="X9" s="2" t="n"/>
-      <c r="AB9" s="3" t="n"/>
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>L0008</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>SPGPrints B.V. Boxmeer</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Onbekend</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>https://companyinfo.nl/organisatieprofiel/drukkerijen-van-dagbladen/spgprints-boxmeer-16032034-000018930794</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>16032034</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>spgprints.com</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>https://www.spgprints.com</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Boxmeer</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>5831 AT</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>Raamstraat 1-3</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Onbekend</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>Niet gevonden</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>Niet gevonden</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>Onbekend</t>
+        </is>
+      </c>
+      <c r="O9" s="3" t="inlineStr">
+        <is>
+          <t>Onbekend</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Actualiteit onduidelijk</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>Onbekend</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>Onbekend</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>Nee</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>onbekend</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>nog niet te bepalen</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Niet gevonden</t>
+        </is>
+      </c>
+      <c r="X9" s="2" t="inlineStr">
+        <is>
+          <t>+31 485 599 555</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>https://www.spgprints.com/contact</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>nog niet gecontroleerd</t>
+        </is>
+      </c>
+      <c r="AB9" s="3" t="n">
+        <v>46280</v>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Organisatiestructuur onzeker. KVK-gegevens noemen Print I B.V. als eigenaar van SPGPrints B.V. en daarnaast bestaat de naam SPGPrints Group met buitenlandse vestigingen. Niet vastgesteld welk niveau de canonieke Organisatie voor de 50-grens is. De eigen site noemt Raamstraat 1-3 en de KVK-registratie Raamstraat 3; het adres van de eigen site is aangehouden. Geen algemeen e-mailadres gevonden. Circulerende medewerkersaantallen uit niveau D-bronnen zijn niet gebruikt.</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n"/>

--- a/data/HAHEBO_leadbestand_pilot.xlsx
+++ b/data/HAHEBO_leadbestand_pilot.xlsx
@@ -459,7 +459,7 @@
     <col width="20" customWidth="1" min="16" max="16"/>
     <col width="18" customWidth="1" min="17" max="17"/>
     <col width="18" customWidth="1" min="18" max="18"/>
-    <col width="16" customWidth="1" min="19" max="19"/>
+    <col width="24" customWidth="1" min="19" max="19"/>
     <col width="32" customWidth="1" min="20" max="20"/>
     <col width="16" customWidth="1" min="21" max="21"/>
     <col width="20" customWidth="1" min="22" max="22"/>
@@ -565,7 +565,7 @@
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
-          <t>Handmatig beoordeeld</t>
+          <t>Status handmatige beoordeling</t>
         </is>
       </c>
       <c r="T1" s="1" t="inlineStr">
@@ -712,7 +712,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>Nee</t>
+          <t>niet nodig</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>Nee</t>
+          <t>niet nodig</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -982,7 +982,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>Nee</t>
+          <t>niet nodig</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -1117,7 +1117,7 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>Nee</t>
+          <t>niet nodig</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -1252,7 +1252,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>Nee</t>
+          <t>niet nodig</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -1387,7 +1387,7 @@
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>Nee</t>
+          <t>niet nodig</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
@@ -1522,7 +1522,7 @@
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>Nee</t>
+          <t>niet nodig</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
@@ -1657,7 +1657,7 @@
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>Nee</t>
+          <t>niet nodig</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
@@ -5648,8 +5648,8 @@
     <dataValidation sqref="R2:R500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Ongeldige invoer" error="Kies een geldige waarde uit de lijst." promptTitle="Eenheid medewerkers" prompt="Werkzame personen is de voorkeursmaatstaf voor de grens van 50 medewerkers." type="list">
       <formula1>"Werkzame personen,FTE,Onbekend"</formula1>
     </dataValidation>
-    <dataValidation sqref="S2:S500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Ongeldige invoer" error="Kies een geldige waarde uit de lijst." promptTitle="Handmatig beoordeeld" prompt="Is deze lead handmatig beoordeeld?" type="list">
-      <formula1>"Ja,Nee"</formula1>
+    <dataValidation sqref="S2:S500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Ongeldige invoer" error="Kies een geldige waarde uit de lijst." promptTitle="Status handmatige beoordeling" prompt="Kies: niet nodig / nodig / afgerond." type="list">
+      <formula1>"niet nodig,nodig,afgerond"</formula1>
     </dataValidation>
     <dataValidation sqref="V2:V500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Ongeldige invoer" error="Kies een geldige waarde uit de lijst." promptTitle="Doelgroepstatus" prompt="Kies: binnen doelgroep / buiten doelgroep / nog niet te bepalen." type="list">
       <formula1>"binnen doelgroep,buiten doelgroep,nog niet te bepalen"</formula1>
@@ -5903,12 +5903,12 @@
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>Handmatig beoordeeld</t>
+          <t>Status handmatige beoordeling</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>Keuzelijst: Ja / Nee. Geeft aan of deze lead handmatig is beoordeeld.</t>
+          <t>Keuzelijst: niet nodig / nodig / afgerond. Geeft aan of voor deze lead een menselijke beoordeling nodig is en of deze al is uitgevoerd. niet nodig: de automatische bron- en beslisregels leveren voldoende duidelijkheid op, of er ontbreekt simpelweg informatie zonder dat er materiaal is dat een mens inhoudelijk moet wegen. nodig: er is informatie beschikbaar die een mens inhoudelijk moet beoordelen, maar deze beoordeling is nog niet uitgevoerd. afgerond: de benodigde menselijke beoordeling is daadwerkelijk uitgevoerd.</t>
         </is>
       </c>
     </row>
@@ -5920,7 +5920,7 @@
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>Vrij tekstveld voor een of meerdere gebruikte bron-URL's of een korte verwijzing naar de gebruikte bronnen. Mag leeg blijven als Handmatig beoordeeld = Nee.</t>
+          <t>Vrij tekstveld voor een of meerdere gebruikte bron-URL's of een korte verwijzing naar de gebruikte bronnen. Bij Status handmatige beoordeling = niet nodig: leeg. Bij nodig: de bronnen die aanleiding geven tot de benodigde beoordeling. Bij afgerond: de bronnen waarop de uitgevoerde beoordeling is gebaseerd.</t>
         </is>
       </c>
     </row>

--- a/data/HAHEBO_leadbestand_pilot.xlsx
+++ b/data/HAHEBO_leadbestand_pilot.xlsx
@@ -1700,28 +1700,414 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="n"/>
-      <c r="E10" s="2" t="n"/>
-      <c r="I10" s="2" t="n"/>
-      <c r="O10" s="3" t="n"/>
-      <c r="X10" s="2" t="n"/>
-      <c r="AB10" s="3" t="n"/>
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>L0009</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Bibliotheek Boxmeer / hoofdkantoor BiblioPlus</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Stichting BiblioPlus</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>https://www.biblioplus.nl/overons/over-biblioplus.html en https://www.biblioplus.nl/klantenservice/contact.html</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>17169778</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>biblioplus.nl</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>https://www.biblioplus.nl</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Boxmeer</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>5831 KC</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>De Raetsingel 1</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>Niet gevonden</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>https://www.biblioplus.nl/overons/over-biblioplus.html</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="O10" s="3" t="inlineStr">
+        <is>
+          <t>Onbekend</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Actueel/live</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>Organisatie</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>Onbekend</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>niet nodig</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>50+</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>nog niet te bepalen</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>info@biblioplus.nl</t>
+        </is>
+      </c>
+      <c r="X10" s="2" t="inlineStr">
+        <is>
+          <t>+31 (0)485 583 500</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>https://www.biblioplus.nl/klantenservice/contact.html</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>nog niet gecontroleerd</t>
+        </is>
+      </c>
+      <c r="AB10" s="3" t="n">
+        <v>46280</v>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>De eigen pagina meldt in de huidige tekst 51 medewerkers en meer dan 560 vrijwilligers. Oudere of externe weergaven noemen 35 of 37 medewerkers, maar die zijn niet als actuele onafhankelijke bron gebruikt. Vrijwilligers zijn niet meegeteld. De bron noemt medewerkers maar maakt niet expliciet duidelijk of dit headcount of fte betreft; daarom staat Eenheid medewerkers op Onbekend. Omdat het genoemde aantal personen 50 of meer is, is segment 50+ toegestaan volgens de vastgestelde regel. Boxmeer is het hoofdkantoor in De Weijer.</t>
+        </is>
+      </c>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="n"/>
-      <c r="E11" s="2" t="n"/>
-      <c r="I11" s="2" t="n"/>
-      <c r="O11" s="3" t="n"/>
-      <c r="X11" s="2" t="n"/>
-      <c r="AB11" s="3" t="n"/>
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>L0010</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Sociom, locatie De Weijer Boxmeer</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Sociom</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>https://sociom.nl/over-ons/ en https://sociom.nl/locaties/</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>Niet gevonden</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>sociom.nl</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>https://sociom.nl</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Boxmeer</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>5831 KC</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>De Raetsingel 1</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Onbekend</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>Niet gevonden</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>Niet gevonden</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>Onbekend</t>
+        </is>
+      </c>
+      <c r="O11" s="3" t="inlineStr">
+        <is>
+          <t>Onbekend</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Actualiteit onduidelijk</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>Onbekend</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>Onbekend</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>niet nodig</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>onbekend</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>nog niet te bepalen</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>info@sociom.nl</t>
+        </is>
+      </c>
+      <c r="X11" s="2" t="inlineStr">
+        <is>
+          <t>0485-700 500</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>https://sociom.nl/locaties/</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>nog niet gecontroleerd</t>
+        </is>
+      </c>
+      <c r="AB11" s="3" t="n">
+        <v>46280</v>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Geen bruikbaar medewerkersgegeven gevonden na toepassing van de vastgestelde stopregel. Ontbrekende data zijn op zichzelf geen reden voor handmatige beoordeling. Sociom werkt in Land van Cuijk en West Maas en Waal met meerdere locaties, waarvan De Weijer in Boxmeer er één is. Eén externe bron noemt De Raetsingel 5; het adres van de eigen site is aangehouden.</t>
+        </is>
+      </c>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="n"/>
-      <c r="E12" s="2" t="n"/>
-      <c r="I12" s="2" t="n"/>
-      <c r="O12" s="3" t="n"/>
-      <c r="X12" s="2" t="n"/>
-      <c r="AB12" s="3" t="n"/>
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>L0011</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Bouwbedrijf Van Oijen B.V. Boxmeer</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Bouwbedrijf Van Oijen B.V.</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>https://www.oijen-bouw.nl/ en https://www.bouwgarant.nl/aannemers/boxmeer/bouwbedrijf-van-oijen-bv</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>16046049</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>oijen-bouw.nl</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>https://www.oijen-bouw.nl</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Boxmeer</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>5831 AP</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>Kleine Broekstraat 7</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>Niet gevonden</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>https://www.oijen-bouw.nl/</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="O12" s="3" t="inlineStr">
+        <is>
+          <t>Onbekend</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Actueel/live</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>Organisatie</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>Onbekend</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>nodig</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>https://www.oijen-bouw.nl/</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>onbekend</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>nog niet te bepalen</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>algemeen@oijen-bouw.nl</t>
+        </is>
+      </c>
+      <c r="X12" s="2" t="inlineStr">
+        <is>
+          <t>0485 57 14 32</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>https://www.oijen-bouw.nl/contact</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>nog niet gecontroleerd</t>
+        </is>
+      </c>
+      <c r="AB12" s="3" t="n">
+        <v>46280</v>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>De eigen site spreekt over een 20-koppig team. Dat is een aantal personen zonder expliciete eenheid en ligt onder de grens van 50. Daarom mag volgens de vastgestelde regel nog geen segment regionaal &lt;50 of nog te bepalen worden toegekend. Een menselijke beoordeling is nodig om te bepalen of het om headcount of fte gaat of om andersoortige teaminformatie. Daarom staat Status handmatige beoordeling op nodig. Eén externe bron noemt een afwijkend KVK-nummer en plaats; die gegevens zijn niet overgenomen.</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n"/>

--- a/data/HAHEBO_leadbestand_pilot.xlsx
+++ b/data/HAHEBO_leadbestand_pilot.xlsx
@@ -2057,22 +2057,22 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>Onbekend</t>
+          <t>Werkzame personen</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>nodig</t>
+          <t>afgerond</t>
         </is>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>https://www.oijen-bouw.nl/</t>
+          <t>https://www.oijen-bouw.nl/ en https://drimble.nl/bedrijf/boxmeer/000015501116/bouwbedrijf-van-oijen-bv.html en https://drimble.nl/bedrijf/gemeente/land-van-cuijk/15501116/bouwbedrijf-van-oijen-bv.html</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>onbekend</t>
+          <t>nog te bepalen</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
@@ -2105,7 +2105,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>De eigen site spreekt over een 20-koppig team. Dat is een aantal personen zonder expliciete eenheid en ligt onder de grens van 50. Daarom mag volgens de vastgestelde regel nog geen segment regionaal &lt;50 of nog te bepalen worden toegekend. Een menselijke beoordeling is nodig om te bepalen of het om headcount of fte gaat of om andersoortige teaminformatie. Daarom staat Status handmatige beoordeling op nodig. Eén externe bron noemt een afwijkend KVK-nummer en plaats; die gegevens zijn niet overgenomen.</t>
+          <t>Handmatige beoordeling afgerond. De eigen website beschrijft een 20-koppig team en koppelt dit aan medewerkers/vakmensen van Bouwbedrijf Van Oijen B.V.; daarom is het aantal 20 vastgelegd als Werkzame personen. De onderneming treedt onder eigen naam naar buiten met een eigen website en contactstructuur. Er bestaat een holdingstructuur met MJE Beheer B.V. als moedermaatschappij. Op basis van de voorlopige HAHEBO-werkregel blokkeert een holdingstructuur de Organisatienaam niet wanneer de werkmaatschappij aantoonbaar als operationele onderneming naar buiten treedt en er geen duidelijke groepsbrede commerciële organisatie zichtbaar is. De precieze rol van MJE Beheer is niet met een registeruittreksel vastgesteld en blijft daarom als aandachtspunt genoteerd. Op hetzelfde adres staat daarnaast Metaalgieterij Kinheim B.V.; de relatie daarvan tot Bouwbedrijf Van Oijen is niet vastgesteld. Met 20 werkzame personen krijgt de lead Segment = nog te bepalen totdat HAHEBO de regionale afbakening heeft vastgesteld.</t>
         </is>
       </c>
     </row>

--- a/data/HAHEBO_leadbestand_pilot.xlsx
+++ b/data/HAHEBO_leadbestand_pilot.xlsx
@@ -1442,12 +1442,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Onbekend</t>
+          <t>Mezzo Scholen voor vwo havo en vmbo</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>https://www.omo.nl/scholen/ en https://allecijfers.nl/middelbare-school/mezzo-scholen/</t>
+          <t>DUO vestigingen VO — data/duo/vestigingen_vo.csv</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -1482,7 +1482,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>Onbekend</t>
+          <t>440</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -1492,32 +1492,32 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>Niet gevonden</t>
+          <t>DUO Onderwijspersoneel VO in aantal personen 2011-2025 — data/duo/onderwijspersoneel_vo_personen_2011_2025.xlsx</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>Onbekend</t>
+          <t>B</t>
         </is>
       </c>
       <c r="O8" s="3" t="inlineStr">
         <is>
-          <t>Onbekend</t>
+          <t>01-10-2025</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Actualiteit onduidelijk</t>
+          <t>Expliciet gedateerd</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>Onbekend</t>
+          <t>Organisatie</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>Onbekend</t>
+          <t>Werkzame personen</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
@@ -1527,7 +1527,7 @@
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>onbekend</t>
+          <t>50+</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
@@ -1560,7 +1560,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Organisatiestructuur onzeker: er zijn twee verdedigbare niveaus boven de vestiging. Mezzo Scholen omvat vijf VO-vestigingen en Ons Middelbaar Onderwijs is het bevoegd gezag boven meerdere scholen. Geen onderzochte bron stelt voldoende vast welk niveau voor onze 50-grens als Organisatie moet gelden. Daarom staat Organisatienaam op Onbekend. Er is geen medewerkersgegeven uit een bruikbare A- of B-bron gevonden. Leerlingaantallen zijn geen medewerkersgegevens en zijn niet gebruikt.</t>
+          <t>Onderwijsregel toegepast: Organisatienaam is vastgesteld op BRIN-niveau via de DUO-lookup (python scripts/duo_onderwijs_lookup.py 17HN). Officiële instelling: Mezzo Scholen voor vwo havo en vmbo. Bevoegd gezag: Ons Middelbaar Onderwijs, bestuursnummer 41211. DUO PERSONEN 2025 = 440 op instellingsniveau, peildatum 1 oktober 2025. Dit totaal geldt voor alle vier vestigingen onder BRIN 17HN samen (Boxmeer x3, Gennep x1) en niet alleen voor de fysieke locatie Bilderbeekstraat 27. Segment = 50+. KVK-nummer blijft ongewijzigd / Niet gevonden.</t>
         </is>
       </c>
     </row>

--- a/data/HAHEBO_leadbestand_pilot.xlsx
+++ b/data/HAHEBO_leadbestand_pilot.xlsx
@@ -2110,28 +2110,409 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="2" t="n"/>
-      <c r="E13" s="2" t="n"/>
-      <c r="I13" s="2" t="n"/>
-      <c r="O13" s="3" t="n"/>
-      <c r="X13" s="2" t="n"/>
-      <c r="AB13" s="3" t="n"/>
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>L0012</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Gemeente Land van Cuijk, gemeentehuis Boxmeer</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Gemeente Land van Cuijk</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>https://www.gemeentelandvancuijk.nl</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>Niet gevonden</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>gemeentelandvancuijk.nl</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>https://www.gemeentelandvancuijk.nl</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Boxmeer</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>5831 JX</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>Raadhuisplein 1</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Ongeveer 800</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>Niet gevonden</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>eigen werken-bij/vacaturepagina van Gemeente Land van Cuijk</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="O13" s="3" t="inlineStr">
+        <is>
+          <t>Niet gevonden</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Actueel/live</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>Organisatie</t>
+        </is>
+      </c>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>Onbekend</t>
+        </is>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>niet nodig</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>50+</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>nog niet te bepalen</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>gemeente@landvancuijk.nl</t>
+        </is>
+      </c>
+      <c r="X13" s="2" t="inlineStr">
+        <is>
+          <t>0485-854000</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>https://www.gemeentelandvancuijk.nl</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>nog niet gecontroleerd</t>
+        </is>
+      </c>
+      <c r="AB13" s="3" t="n">
+        <v>46280</v>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Organisatie = Gemeente Land van Cuijk; lead betreft het gemeentehuis/locatie Boxmeer. Personeelsbron (eigen werken-bij/vacaturepagina) noemt ongeveer 800 medewerkers op organisatieniveau, bronkwaliteit A; de bron benoemt dit aantal niet expliciet als headcount of FTE, daarom staat Eenheid medewerkers op Onbekend. Omdat circa 800 ruim boven de grens van 50 ligt, is Segment = 50+. Raadhuisplein 1 is als huidig adres gebruikt; een eerdere, verzwakte vermelding van Raadsstraat 1 is niet gebruikt. Het nummer 28523612 is niet als KVK-nummer ingevuld omdat dit niet als KVK-nummer is bevestigd. Acquisitielijst nog niet gecontroleerd.</t>
+        </is>
+      </c>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="n"/>
-      <c r="E14" s="2" t="n"/>
-      <c r="I14" s="2" t="n"/>
-      <c r="O14" s="3" t="n"/>
-      <c r="X14" s="2" t="n"/>
-      <c r="AB14" s="3" t="n"/>
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>L0013</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>SBO Palet Boxmeer</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>School voor Speciaal Basisonderwijs Palet</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>DUO vestigingen SBO/SO/VSO — data/duo/vestigingen_sbo_so_vso.csv</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>41081122</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>paletboxmeer.nl</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>https://www.paletboxmeer.nl</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Boxmeer</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>5831 EW</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>Pastoor Kerstenstraat 38</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>Niet gevonden</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>DUO Onderwijspersoneel PO in aantal personen 2011-2025 — afgeleide compacte dataset data/duo/duo_po_brin_personen_2011_2025_compact.xlsx</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="O14" s="3" t="inlineStr">
+        <is>
+          <t>01-10-2025</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Expliciet gedateerd</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>Organisatie</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>Werkzame personen</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>niet nodig</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>nog te bepalen</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>nog niet te bepalen</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>dir.palet@optimusonderwijs.nl</t>
+        </is>
+      </c>
+      <c r="X14" s="2" t="inlineStr">
+        <is>
+          <t>0485-571685</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>Optimus scholenoverzicht + SBO Palet schoolgids 2025-2026</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>nog niet gecontroleerd</t>
+        </is>
+      </c>
+      <c r="AB14" s="3" t="n">
+        <v>46280</v>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Onderwijsregel toegepast: Organisatienaam is vastgesteld op BRIN-niveau via de DUO-lookup. Officiële instelling: School voor Speciaal Basisonderwijs Palet, BRIN 20GB, vestigingscode 20GB00. Bevoegd gezag: OPTIMUS, bestuursnummer 48348. DUO PERSONEN 2025 = 18 op instellingsniveau, peildatum 1 oktober 2025; dit cijfer geldt op BRIN-/instellingsniveau. Personeelsdata komt uit de afgeleide compacte PO-dataset, traceerbaar naar het officiële DUO-bronbestand (zie data/duo/README.md). Segment = nog te bepalen. Het bestuursniveau van OPTIMUS is niet gebruikt voor segmentatie.</t>
+        </is>
+      </c>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="n"/>
-      <c r="E15" s="2" t="n"/>
-      <c r="I15" s="2" t="n"/>
-      <c r="O15" s="3" t="n"/>
-      <c r="X15" s="2" t="n"/>
-      <c r="AB15" s="3" t="n"/>
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>L0014</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Bol Adviseurs, locatie Boxmeer</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Bol Adviseurs</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>https://www.boladviseurs.nl</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>16064022</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>boladviseurs.nl</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>https://www.boladviseurs.nl</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Boxmeer</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>5831 CK</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>Spoorstraat 73</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Onbekend</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>Niet gevonden</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>Niet gevonden</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>Onbekend</t>
+        </is>
+      </c>
+      <c r="O15" s="3" t="inlineStr">
+        <is>
+          <t>Niet gevonden</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Actualiteit onduidelijk</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>Onbekend</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>Onbekend</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>niet nodig</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>onbekend</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>nog niet te bepalen</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>info@boladviseurs.nl</t>
+        </is>
+      </c>
+      <c r="X15" s="2" t="inlineStr">
+        <is>
+          <t>088 1211 300</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>https://www.boladviseurs.nl/boxmeer</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>nog niet gecontroleerd</t>
+        </is>
+      </c>
+      <c r="AB15" s="3" t="n">
+        <v>46280</v>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Bol Adviseurs is volgens de eigen disclaimer een collectieve naam voor meerdere juridische entiteiten. Voor deze Boxmeer-lead is KVK 16064022 van Bol Accountants B.V. gebruikt, vestigingsnummer 000017116937. STAK Bol Accountants is een eigendoms-/holdingstructuur en is niet als Organisatienaam gebruikt. Er is geen betrouwbare A- of B-bron met een bruikbaar medewerkersaantal gevonden; een eerder aangetroffen C-bron met 1 medewerker is niet gebruikt voor segmentatie. Aantal medewerkers = Onbekend, Segment = onbekend. Telefoonnummer en e-mailadres zijn organisatiebrede contactgegevens; de officiële Boxmeer-locatiepagina bevestigt deze gegevens expliciet voor Spoorstraat 73. Bol International noemt een afwijkend generiek telefoonnummer en is daarom niet als primaire contactbron gebruikt. Acquisitielijst nog niet gecontroleerd.</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n"/>

--- a/data/HAHEBO_leadbestand_pilot.xlsx
+++ b/data/HAHEBO_leadbestand_pilot.xlsx
@@ -2515,12 +2515,144 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="n"/>
-      <c r="E16" s="2" t="n"/>
-      <c r="I16" s="2" t="n"/>
-      <c r="O16" s="3" t="n"/>
-      <c r="X16" s="2" t="n"/>
-      <c r="AB16" s="3" t="n"/>
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>L0015</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Toolstation Boxmeer</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Toolstation NL B.V.</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>https://www.toolstation.nl/content/terms</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>63449595</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>toolstation.nl</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>https://www.toolstation.nl/branches/boxmeer</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Boxmeer</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>5831 AD</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>Sint Anthonisweg 53</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Onbekend</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>Niet gevonden</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>Niet gevonden</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>Onbekend</t>
+        </is>
+      </c>
+      <c r="O16" s="3" t="inlineStr">
+        <is>
+          <t>Niet gevonden</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Actualiteit onduidelijk</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>Onbekend</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>Onbekend</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>afgerond</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>https://www.toolstation.nl/content/jobs en https://www.toolstation.nl/content/terms en https://toolstation.jobilla.com/ en https://toolstation.otys.website/</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>onbekend</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>nog niet te bepalen</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>info@toolstation.nl</t>
+        </is>
+      </c>
+      <c r="X16" s="2" t="inlineStr">
+        <is>
+          <t>+31 71 581 5050</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>Toolstation Boxmeer vestigingspagina + Toolstation algemene voorwaarden: https://www.toolstation.nl/branches/boxmeer en https://www.toolstation.nl/content/terms</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>nog niet gecontroleerd</t>
+        </is>
+      </c>
+      <c r="AB16" s="3" t="n">
+        <v>46281</v>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Toolstation NL B.V. is via de eigen algemene voorwaarden bevestigd als Nederlandse organisatie, KVK 63449595; Boxmeer is een vestiging van deze organisatie op Sint Anthonisweg 53, 5831 AD Boxmeer. Het vestigingsnummer van Boxmeer is niet gevonden; vestigingsnummer 000032364911 hoort bij Bleiswijk (hoofdvestiging) en is niet aan Boxmeer toegeschreven. Er is geen bruikbaar A- of B-medewerkerscijfer gevonden. Jobilla noemt ruim 1.000 medewerkers, maar deze bron is na handmatige beoordeling niet gebruikt: onvoldoende aantoonbare provenance als officieel Toolstation-kanaal, en de Jobilla-tekst spreekt over meer dan 100 vestigingen en een hoofdzetel in Houten, terwijl actuele eigen Toolstation-bronnen 94 Nederlandse vestigingen en Bleiswijk noemen — organisatorisch/geografisch niveau sluit dus niet betrouwbaar aan. Deze bron is beoordeeld als C. Het officiële recruitmentkanaal toolstation.otys.website is gecontroleerd, maar blokkeert geautomatiseerde toegang en leverde daardoor geen bruikbaar medewerkersaantal op. De eigen Toolstation jobs-pagina noemt 94 Nederlandse vestigingen en Bleiswijk, maar geen medewerkersaantal. Het medewerkersonderzoek voor deze lead is hiermee afgerond; Aantal medewerkers blijft Onbekend, Segment blijft onbekend. E-mail en telefoon zijn organisatiebrede contactgegevens en niet uniek voor Boxmeer. Acquisitielijst nog niet gecontroleerd.</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n"/>

--- a/data/HAHEBO_leadbestand_pilot.xlsx
+++ b/data/HAHEBO_leadbestand_pilot.xlsx
@@ -2655,44 +2655,684 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="2" t="n"/>
-      <c r="E17" s="2" t="n"/>
-      <c r="I17" s="2" t="n"/>
-      <c r="O17" s="3" t="n"/>
-      <c r="X17" s="2" t="n"/>
-      <c r="AB17" s="3" t="n"/>
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>L0016</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Abiks B.V.</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Abiks B.V.</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>https://abiks.nl/over-ons/</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>Niet gevonden</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>abiks.nl</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>https://www.abiks.nl</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Wanroij</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>5446 XE</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>Hank 20</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Onbekend</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>Niet gevonden</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>Niet gevonden</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>Onbekend</t>
+        </is>
+      </c>
+      <c r="O17" s="3" t="inlineStr">
+        <is>
+          <t>Niet gevonden</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Actualiteit onduidelijk</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>Onbekend</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>Onbekend</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>niet nodig</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>onbekend</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>nog niet te bepalen</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>info@abiks.nl</t>
+        </is>
+      </c>
+      <c r="X17" s="2" t="inlineStr">
+        <is>
+          <t>085-0201336</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>https://abiks.nl/privacybeleid/ voor adres; e-mailadres en telefoonnummer uit een externe vacaturepublicatie met Abiks-tekst, niet bevestigd op abiks.nl</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>nog niet gecontroleerd</t>
+        </is>
+      </c>
+      <c r="AB17" s="3" t="n">
+        <v>46281</v>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Eigen website bevestigt Hank 20 als vestigingsadres. Een externe leerbedrijvenbron noemt Hank 10; de actuele eigen bron is leidend, het afwijkende adres is genoteerd. KVK-nummer niet betrouwbaar gevonden. Mogelijke relatie met Aben B.V. van de oprichters is niet verder uitgewerkt. Medewerkersaantal niet gevonden. Let op: e-mailadres en telefoonnummer staan in een vacaturetekst op een extern platform en niet op de eigen site; het eigen privacybeleid noemt 06-83529858.</t>
+        </is>
+      </c>
     </row>
     <row r="18">
-      <c r="A18" s="2" t="n"/>
-      <c r="E18" s="2" t="n"/>
-      <c r="I18" s="2" t="n"/>
-      <c r="O18" s="3" t="n"/>
-      <c r="X18" s="2" t="n"/>
-      <c r="AB18" s="3" t="n"/>
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>L0017</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Holland Drilling B.V.</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Holland Drilling B.V.</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>https://hollanddrilling.nl/contact/</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>67002706</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>hollanddrilling.nl</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>https://www.hollanddrilling.nl</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Cuijk</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>5431 NN</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>Simon Homburgstraat 17</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Onbekend</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>Niet gevonden</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>Niet gevonden</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>Onbekend</t>
+        </is>
+      </c>
+      <c r="O18" s="3" t="inlineStr">
+        <is>
+          <t>Niet gevonden</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Actualiteit onduidelijk</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>Onbekend</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>Onbekend</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>niet nodig</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>onbekend</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>nog niet te bepalen</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>info@hollanddrilling.nl</t>
+        </is>
+      </c>
+      <c r="X18" s="2" t="inlineStr">
+        <is>
+          <t>+31 485 74 50 40</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>https://hollanddrilling.nl/contact/</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>nog niet gecontroleerd</t>
+        </is>
+      </c>
+      <c r="AB18" s="3" t="n">
+        <v>46281</v>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Eigen website bevestigt de vestiging. KVK 67002706 met vestigingsnummer 000035580305. Er zijn gerelateerde entiteiten zichtbaar: Holland Drilling Beheer, Holland Drilling Projects en BMG Nederland. Er is geen bruikbaar medewerkersaantal gevonden. Holland Drilling B.V. blijft voor deze lead als organisatie gebruikt. De eigen site beschrijft een moderne en ruime kantooromgeving met binnen- en buitenwerkers.</t>
+        </is>
+      </c>
     </row>
     <row r="19">
-      <c r="A19" s="2" t="n"/>
-      <c r="E19" s="2" t="n"/>
-      <c r="I19" s="2" t="n"/>
-      <c r="O19" s="3" t="n"/>
-      <c r="X19" s="2" t="n"/>
-      <c r="AB19" s="3" t="n"/>
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>L0018</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Huijskes VRT B.V.</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Huijskes Verkeersregeltechniek B.V.</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>https://www.huijskesvrt.nl/contact/</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>50169858</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>huijskesvrt.nl</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>https://www.huijskesvrt.nl</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Overloon</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>5825 CC</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>14 Oktoberplein 6</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Onbekend</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>Niet gevonden</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>Niet gevonden</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>Onbekend</t>
+        </is>
+      </c>
+      <c r="O19" s="3" t="inlineStr">
+        <is>
+          <t>Niet gevonden</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Actualiteit onduidelijk</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>Onbekend</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>Onbekend</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>niet nodig</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>onbekend</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>nog niet te bepalen</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>info@huijskesvrt.nl</t>
+        </is>
+      </c>
+      <c r="X19" s="2" t="inlineStr">
+        <is>
+          <t>+31 478 640021</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>https://www.huijskesvrt.nl/contact/ voor adres en e-mailadres; telefoonnummer uit niveau-2-bedrijvengids, niet op de eigen contactpagina</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>nog niet gecontroleerd</t>
+        </is>
+      </c>
+      <c r="AB19" s="3" t="n">
+        <v>46281</v>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Eigen contactpagina bevestigt het bezoekadres en KVK 50169858. Huijskes VRT B.V. wordt als handelsnaam gebruikt; de juridische entiteit is Huijskes Verkeersregeltechniek B.V. De eigen site noemt ook Postbus 6, 5825 ZG Overloon, maar het bezoekadres is 14 Oktoberplein 6. Het telefoonnummer is extern bevestigd en staat niet op de eigen contactpagina. Geen bruikbaar medewerkersaantal gevonden. Er is ook een Huijskes VRT Beheer B.V. zichtbaar.</t>
+        </is>
+      </c>
     </row>
     <row r="20">
-      <c r="A20" s="2" t="n"/>
-      <c r="E20" s="2" t="n"/>
-      <c r="I20" s="2" t="n"/>
-      <c r="O20" s="3" t="n"/>
-      <c r="X20" s="2" t="n"/>
-      <c r="AB20" s="3" t="n"/>
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>L0019</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Jacobs &amp; Smits Metaalbewerking B.V.</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Jacobs &amp; Smits Metaalbewerking B.V.</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>https://www.jacobsensmits.nl/contact-met-jacobs-smits/</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>17166075</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>jacobsensmits.nl</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>https://www.jacobsensmits.nl</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Boxmeer</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>5831 AK</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>Lionstraat 18</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>Niet gevonden</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>https://www.jacobsensmits.nl/metaalbewerking-in-boxmeer/</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="O20" s="3" t="inlineStr">
+        <is>
+          <t>Niet gevonden</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Actueel/live</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>Organisatie</t>
+        </is>
+      </c>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>Werkzame personen</t>
+        </is>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>afgerond</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>https://www.jacobsensmits.nl/metaalbewerking-in-boxmeer/</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>nog te bepalen</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>nog niet te bepalen</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>info@jacobsensmits.nl</t>
+        </is>
+      </c>
+      <c r="X20" s="2" t="inlineStr">
+        <is>
+          <t>0485-575677</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>https://www.jacobsensmits.nl/contact-met-jacobs-smits/</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>nog niet gecontroleerd</t>
+        </is>
+      </c>
+      <c r="AB20" s="3" t="n">
+        <v>46281</v>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Eigen bron noemt exact een team van 15 vakbekwame medewerkers. De handmatige beoordeling heeft vastgesteld dat dit personen betreft en niet arbeidsjaren, waarmee de eenheid op werkzame personen staat. Het cijfer geldt voor de organisatie als geheel. Segment daarom nog te bepalen totdat de regio is vastgesteld. Makomar wordt op de eigen site genoemd voor aanvullende metaal- en kunststofbewerking; die relatie is niet verder onderzocht.</t>
+        </is>
+      </c>
     </row>
     <row r="21">
-      <c r="A21" s="2" t="n"/>
-      <c r="E21" s="2" t="n"/>
-      <c r="I21" s="2" t="n"/>
-      <c r="O21" s="3" t="n"/>
-      <c r="X21" s="2" t="n"/>
-      <c r="AB21" s="3" t="n"/>
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>L0020</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Kepser B.V.</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Onbekend</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>https://www.kepser.nl/en/about-kepser en https://drimble.nl/bedrijf/cuijk/16261844/kepser-bv.html</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>16045039</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>kepser.nl</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>https://www.kepser.nl</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Cuijk</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>5431 NN</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>Simon Homburgstraat 12</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Onbekend</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>Niet gevonden</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>Niet gevonden</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>Onbekend</t>
+        </is>
+      </c>
+      <c r="O21" s="3" t="inlineStr">
+        <is>
+          <t>Niet gevonden</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Actualiteit onduidelijk</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>Onbekend</t>
+        </is>
+      </c>
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>Onbekend</t>
+        </is>
+      </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>niet nodig</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>onbekend</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>nog niet te bepalen</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>welkom@kepser.nl</t>
+        </is>
+      </c>
+      <c r="X21" s="2" t="inlineStr">
+        <is>
+          <t>0485 33 60 60</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>https://www.landvancuijk.nl/vermelding/kepser/ voor telefoonnummer en een afwijkend e-mailadres; welkom@kepser.nl komt uit een extern zakenblad en is niet op kepser.nl bevestigd</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>nog niet gecontroleerd</t>
+        </is>
+      </c>
+      <c r="AB21" s="3" t="n">
+        <v>46281</v>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Eigen website van Kepser B.V. bevestigd, met Simon Homburgstraat 12 en postbus 70, 5430 AB Cuijk. KVK 16045039. Op hetzelfde adres zijn ook Kepser Holding B.V. en Kepser Pro-Metaal B.V. zichtbaar, en er wordt een dochterbedrijf Venrooy genoemd. Daardoor is de canonieke organisatienaam volgens onze organisatieregel nog Onbekend. Een externe bron noemt circa 80 medewerkers, maar dat is niet gebruikt omdat er binnen deze ronde geen voldoende sterke personeelsbron is gevonden. Identiteit, adres en contactgegevens zijn wel voldoende onderbouwd voor opname.</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n"/>

--- a/data/HAHEBO_leadbestand_pilot.xlsx
+++ b/data/HAHEBO_leadbestand_pilot.xlsx
@@ -3335,44 +3335,689 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="2" t="n"/>
-      <c r="E22" s="2" t="n"/>
-      <c r="I22" s="2" t="n"/>
-      <c r="O22" s="3" t="n"/>
-      <c r="X22" s="2" t="n"/>
-      <c r="AB22" s="3" t="n"/>
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>L0021</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Infrascoop B.V.</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Onbekend</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>https://www.infrascoop.nl/over-infrascoop/ en https://www.ploegam.nl/dit-is-ploegam/historie</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>17198388</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>infrascoop.nl</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>https://www.infrascoop.nl</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Cuijk</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>5431 NS</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>De Hork 25</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>Onbekend</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>Niet gevonden</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>Niet gevonden</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>Onbekend</t>
+        </is>
+      </c>
+      <c r="O22" s="3" t="inlineStr">
+        <is>
+          <t>Niet gevonden</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Actualiteit onduidelijk</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>Onbekend</t>
+        </is>
+      </c>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>Onbekend</t>
+        </is>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>afgerond</t>
+        </is>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>https://www.infrascoop.nl/over-infrascoop/, https://www.infrascoop.nl/vacatures/, https://www.ploegam.nl/dit-is-ploegam/historie</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>onbekend</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>nog niet te bepalen</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>info@infrascoop.nl</t>
+        </is>
+      </c>
+      <c r="X22" s="2" t="inlineStr">
+        <is>
+          <t>0485-312477</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>https://www.infrascoop.nl/contact/</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>nog niet gecontroleerd</t>
+        </is>
+      </c>
+      <c r="AB22" s="3" t="n">
+        <v>46282</v>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Infrascoop maakt sinds 1 januari 2023 deel uit van de Ploegam Groep. Het bedrijf heeft een eigen handelsnaam, website, vestiging, directie en bedrijfsbureau, maar Ploegam is zelf een operationele onderneming en geen zuivere holding, en er zijn aanwijzingen voor groepsbrede processen en recruitment. Daardoor blijft de canonieke Organisatienaam volgens onze huidige regel Onbekend. Vestigingsnummer 000017858062. Geen bruikbaar medewerkersaantal gevonden. Handmatige beoordeling afgerond. Het eigen pand op bedrijventerrein De Beijerd en 't Riet heeft een duidelijke kantoororganisatie naast het project- en buitenwerk.</t>
+        </is>
+      </c>
     </row>
     <row r="23">
-      <c r="A23" s="2" t="n"/>
-      <c r="E23" s="2" t="n"/>
-      <c r="I23" s="2" t="n"/>
-      <c r="O23" s="3" t="n"/>
-      <c r="X23" s="2" t="n"/>
-      <c r="AB23" s="3" t="n"/>
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>L0022</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Cybox Internet &amp; Communicatie</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Cybox Internet &amp; Communicatie</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>https://www.cybox.nl/contact/</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>16088598</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>cybox.nl</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>https://www.cybox.nl</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Boxmeer</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>5831 CJ</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>Spoorstraat 55k</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>Onbekend</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>Niet gevonden</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>Niet gevonden</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>Onbekend</t>
+        </is>
+      </c>
+      <c r="O23" s="3" t="inlineStr">
+        <is>
+          <t>Niet gevonden</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Actualiteit onduidelijk</t>
+        </is>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>Onbekend</t>
+        </is>
+      </c>
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>Onbekend</t>
+        </is>
+      </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>niet nodig</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>onbekend</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>nog niet te bepalen</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>info@cybox.nl</t>
+        </is>
+      </c>
+      <c r="X23" s="2" t="inlineStr">
+        <is>
+          <t>0485 47 17 74</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>https://www.cybox.nl/contact/</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>nog niet gecontroleerd</t>
+        </is>
+      </c>
+      <c r="AB23" s="3" t="n">
+        <v>46282</v>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>De eigen contactpagina bevestigt Mediaplein, Spoorstraat 55k, 5831 CJ Boxmeer. Een eerder gevonden niveau-2-bron noemde Spoorstraat 55f; de actuele eigen bron is leidend. De eigen site bevestigt KvK 16088598. Er bestaat daarnaast support@cybox.nl als technisch supportadres, maar dat wordt niet als algemeen e-mailadres gebruikt. Geen bruikbaar medewerkersaantal gevonden.</t>
+        </is>
+      </c>
     </row>
     <row r="24">
-      <c r="A24" s="2" t="n"/>
-      <c r="E24" s="2" t="n"/>
-      <c r="I24" s="2" t="n"/>
-      <c r="O24" s="3" t="n"/>
-      <c r="X24" s="2" t="n"/>
-      <c r="AB24" s="3" t="n"/>
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>L0023</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>EEF Makelaars</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>EEF Makelaars</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>https://www.eefmakelaars.nl/contact</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>68298684</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>eefmakelaars.nl</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>https://www.eefmakelaars.nl</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Boxmeer</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>5831 EJ</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>Burgemeester Verkuijlstraat 55</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>Onbekend</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>Niet gevonden</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>Niet gevonden</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>Onbekend</t>
+        </is>
+      </c>
+      <c r="O24" s="3" t="inlineStr">
+        <is>
+          <t>Niet gevonden</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Actualiteit onduidelijk</t>
+        </is>
+      </c>
+      <c r="Q24" t="inlineStr">
+        <is>
+          <t>Onbekend</t>
+        </is>
+      </c>
+      <c r="R24" t="inlineStr">
+        <is>
+          <t>Onbekend</t>
+        </is>
+      </c>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>niet nodig</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>onbekend</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>nog niet te bepalen</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>info@eefmakelaars.nl</t>
+        </is>
+      </c>
+      <c r="X24" s="2" t="inlineStr">
+        <is>
+          <t>0485 745 758</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>https://www.eefmakelaars.nl/contact</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>nog niet gecontroleerd</t>
+        </is>
+      </c>
+      <c r="AB24" s="3" t="n">
+        <v>46282</v>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>De eigen site bevestigt adres en contactgegevens, maar noemt geen juridische entiteit en geen KvK-nummer. KvK 68298684 is via een niveau-2-bron gevonden en niet op de eigen site bevestigd. EEF Makelaars blijft daarom als commerciële Organisatienaam gebruikt. Geen bruikbaar medewerkersaantal gevonden. Het kantoor heeft klantontvangst als kernfunctie.</t>
+        </is>
+      </c>
     </row>
     <row r="25">
-      <c r="A25" s="2" t="n"/>
-      <c r="E25" s="2" t="n"/>
-      <c r="I25" s="2" t="n"/>
-      <c r="O25" s="3" t="n"/>
-      <c r="X25" s="2" t="n"/>
-      <c r="AB25" s="3" t="n"/>
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>L0024</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>GH Advocaten Boxmeer B.V.</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>GH Advocaten Boxmeer B.V.</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>https://www.ghadvocaten.nl/contact/ en companyinfo.nl-profiel van GH Advocaten Boxmeer B.V.</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>17166606</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>ghadvocaten.nl</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>https://www.ghadvocaten.nl</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Boxmeer</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>5831 CM</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>Spoorstraat 66</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>Onbekend</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>Niet gevonden</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>Niet gevonden</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>Onbekend</t>
+        </is>
+      </c>
+      <c r="O25" s="3" t="inlineStr">
+        <is>
+          <t>Niet gevonden</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Actualiteit onduidelijk</t>
+        </is>
+      </c>
+      <c r="Q25" t="inlineStr">
+        <is>
+          <t>Onbekend</t>
+        </is>
+      </c>
+      <c r="R25" t="inlineStr">
+        <is>
+          <t>Onbekend</t>
+        </is>
+      </c>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>afgerond</t>
+        </is>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>https://www.ghadvocaten.nl/contact/, companyinfo.nl-profiel van GH Advocaten Boxmeer B.V. voor KVK, vestigingsnummer en bestuurder, advocatengids.net-vermelding van GH Advocaten Groesbeek B.V.</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>onbekend</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>nog niet te bepalen</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>info@ghadvocaten.nl</t>
+        </is>
+      </c>
+      <c r="X25" s="2" t="inlineStr">
+        <is>
+          <t>0485-561646</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>https://www.ghadvocaten.nl/contact/</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>nog niet gecontroleerd</t>
+        </is>
+      </c>
+      <c r="AB25" s="3" t="n">
+        <v>46282</v>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>De eigen site presenteert het kantoor in Boxmeer aan Spoorstraat 66. KvK 17166606, vestigingsnummer 000018741657. GH Advocaten Groesbeek B.V. staat volgens externe bronnen op hetzelfde adres maar heeft geen aparte commerciële uiting. GH Advocaten Beheer B.V. is bestuurder en wordt als beheerstructuur behandeld. De handmatige beoordeling heeft vastgesteld dat GH Advocaten Boxmeer B.V. voor deze lead als operationele Organisatienaam kan worden gebruikt. Gidsen noemen soms Spoorstraat 6; de eigen site en de KVK-gegevens bevestigen Spoorstraat 66. Geen bruikbaar medewerkersaantal gevonden.</t>
+        </is>
+      </c>
     </row>
     <row r="26">
-      <c r="A26" s="2" t="n"/>
-      <c r="E26" s="2" t="n"/>
-      <c r="I26" s="2" t="n"/>
-      <c r="O26" s="3" t="n"/>
-      <c r="X26" s="2" t="n"/>
-      <c r="AB26" s="3" t="n"/>
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>L0025</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Notariskantoor Boxmeer B.V.</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Notariskantoor Boxmeer B.V.</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Ledenlijstvermelding van Notariskantoor Boxmeer B.V. op cubox.nl</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>Niet gevonden</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>notariskantoorboxmeer.nl</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>https://www.notariskantoorboxmeer.nl</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Boxmeer</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>5831 PE</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>Bereklauw 1, 2e verdieping</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>Onbekend</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>Niet gevonden</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>Niet gevonden</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>Onbekend</t>
+        </is>
+      </c>
+      <c r="O26" s="3" t="inlineStr">
+        <is>
+          <t>Niet gevonden</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Actualiteit onduidelijk</t>
+        </is>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>Onbekend</t>
+        </is>
+      </c>
+      <c r="R26" t="inlineStr">
+        <is>
+          <t>Onbekend</t>
+        </is>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>niet nodig</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>onbekend</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>nog niet te bepalen</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>notaris@notariskantoorboxmeer.nl</t>
+        </is>
+      </c>
+      <c r="X26" s="2" t="inlineStr">
+        <is>
+          <t>0485 573472</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>https://www.notariskantoorboxmeer.nl/contact</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>nog niet gecontroleerd</t>
+        </is>
+      </c>
+      <c r="AB26" s="3" t="n">
+        <v>46282</v>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>De huidige eigen contactpagina bevestigt Bereklauw 1, 2e verdieping, 5831 PE Boxmeer, en het telefoonnummer 0485 573472. Oudere gidsvermeldingen koppelen dit nummer aan andere notariskantoornamen en aan Steenstraat 152; de huidige eigen bron is leidend. De juridische naam Notariskantoor Boxmeer B.V. is via de Cubox-ledenlijst gevonden en niet op de eigen site bevestigd. KvK-nummer niet betrouwbaar gevonden. Geen bruikbaar medewerkersaantal gevonden.</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="n"/>

--- a/data/HAHEBO_leadbestand_pilot.xlsx
+++ b/data/HAHEBO_leadbestand_pilot.xlsx
@@ -4020,44 +4020,694 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="2" t="n"/>
-      <c r="E27" s="2" t="n"/>
-      <c r="I27" s="2" t="n"/>
-      <c r="O27" s="3" t="n"/>
-      <c r="X27" s="2" t="n"/>
-      <c r="AB27" s="3" t="n"/>
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>L0026</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>ES Metaaltechniek</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>ES Metaaltechniek</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>https://www.esmetaaltechniek.nl/contact/</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>17264544</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>esmetaaltechniek.nl</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>https://www.esmetaaltechniek.nl</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Beugen</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>5835 CZ</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>Provincialeweg 19-21</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>Onbekend</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>Niet gevonden</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>Niet gevonden</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>Onbekend</t>
+        </is>
+      </c>
+      <c r="O27" s="3" t="inlineStr">
+        <is>
+          <t>Niet gevonden</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Actualiteit onduidelijk</t>
+        </is>
+      </c>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>Onbekend</t>
+        </is>
+      </c>
+      <c r="R27" t="inlineStr">
+        <is>
+          <t>Onbekend</t>
+        </is>
+      </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>niet nodig</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>onbekend</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>nog niet te bepalen</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>info@esmetaaltechniek.nl</t>
+        </is>
+      </c>
+      <c r="X27" s="2" t="inlineStr">
+        <is>
+          <t>06 2725 2494</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>https://www.esmetaaltechniek.nl/contact/</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>nog niet gecontroleerd</t>
+        </is>
+      </c>
+      <c r="AB27" s="3" t="n">
+        <v>46282</v>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>De eigen contactpagina bevestigt Provincialeweg 19-21, 5835 CZ Beugen als werkadres. Kerkstraat Noord 9 in Oeffelt is het postadres en niet de vestiging die voor deze lead wordt gebruikt. De eigen site bevestigt KvK 17264544. Rechtsvorm is niet verder vastgesteld. De eigen site noemt Erwin Schaminée en samenwerking met vakspecialisten; de omvang is onbekend. Geen bruikbaar medewerkersaantal gevonden. Commerciële relevantie is voorlopig twijfel vanwege een mogelijk kleine organisatie.</t>
+        </is>
+      </c>
     </row>
     <row r="28">
-      <c r="A28" s="2" t="n"/>
-      <c r="E28" s="2" t="n"/>
-      <c r="I28" s="2" t="n"/>
-      <c r="O28" s="3" t="n"/>
-      <c r="X28" s="2" t="n"/>
-      <c r="AB28" s="3" t="n"/>
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>L0027</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Verberk Boxmeer Grond- en Wegenbouw</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>V.A.B. Boxmeer B.V.</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>https://www.verberk-boxmeer.nl/contact</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>71896317</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>verberk-boxmeer.nl</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>https://www.verberk-boxmeer.nl</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Boxmeer</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>5831 AX</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>Saxe Gothastraat 2</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>Onbekend</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>Niet gevonden</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>Niet gevonden</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>Onbekend</t>
+        </is>
+      </c>
+      <c r="O28" s="3" t="inlineStr">
+        <is>
+          <t>Niet gevonden</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Actualiteit onduidelijk</t>
+        </is>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>Onbekend</t>
+        </is>
+      </c>
+      <c r="R28" t="inlineStr">
+        <is>
+          <t>Onbekend</t>
+        </is>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>afgerond</t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>https://www.verberk-boxmeer.nl/contact en de eerder gebruikte oozo-registervermelding met het oude KVK-nummer 17136107</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>onbekend</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>nog niet te bepalen</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>info@verberk-boxmeer.nl</t>
+        </is>
+      </c>
+      <c r="X28" s="2" t="inlineStr">
+        <is>
+          <t>(0485) 57 63 64</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>https://www.verberk-boxmeer.nl/contact</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>nog niet gecontroleerd</t>
+        </is>
+      </c>
+      <c r="AB28" s="3" t="n">
+        <v>46282</v>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Verberk Boxmeer Grond- en Wegenbouw is volgens de eigen contactpagina een handelsnaam van V.A.B. Boxmeer B.V. De eigen bron bevestigt KvK 71896317. Het eerder gevonden KvK 17136107 hoort bij de oudere entiteitsnaam Verberk Boxmeer Grond- en Wegenbouw B.V.; de actuele eigen bron is leidend. De externe indicatie van 6 tot 10 personen hoort bij dat oude nummer en is niet gebruikt. Handmatige beoordeling afgerond. Geen bruikbaar medewerkersaantal gevonden.</t>
+        </is>
+      </c>
     </row>
     <row r="29">
-      <c r="A29" s="2" t="n"/>
-      <c r="E29" s="2" t="n"/>
-      <c r="I29" s="2" t="n"/>
-      <c r="O29" s="3" t="n"/>
-      <c r="X29" s="2" t="n"/>
-      <c r="AB29" s="3" t="n"/>
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>L0028</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Grafisch Huis Boxmeer</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Onbekend</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>https://www.grafisch-huis.nl/onze-vestigingen-in-nijmegen-en-boxmeer/</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>Niet gevonden</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>grafisch-huis.nl</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>https://www.grafisch-huis.nl</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Boxmeer</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>5831 CJ</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>Spoorstraat 55H</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>Onbekend</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>Niet gevonden</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>Niet gevonden</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>Onbekend</t>
+        </is>
+      </c>
+      <c r="O29" s="3" t="inlineStr">
+        <is>
+          <t>Niet gevonden</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Actualiteit onduidelijk</t>
+        </is>
+      </c>
+      <c r="Q29" t="inlineStr">
+        <is>
+          <t>Onbekend</t>
+        </is>
+      </c>
+      <c r="R29" t="inlineStr">
+        <is>
+          <t>Onbekend</t>
+        </is>
+      </c>
+      <c r="S29" t="inlineStr">
+        <is>
+          <t>afgerond</t>
+        </is>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>https://www.grafisch-huis.nl/onze-vestigingen-in-nijmegen-en-boxmeer/, https://www.grafisch-huis.nl en de eerder gebruikte Cubox-vermelding van Grafisch Huis Boxmeer</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>onbekend</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>nog niet te bepalen</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>boxmeer@grafisch-huis.nl</t>
+        </is>
+      </c>
+      <c r="X29" s="2" t="inlineStr">
+        <is>
+          <t>0485 34 68 62</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>https://www.grafisch-huis.nl/onze-vestigingen-in-nijmegen-en-boxmeer/</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>nog niet gecontroleerd</t>
+        </is>
+      </c>
+      <c r="AB29" s="3" t="n">
+        <v>46282</v>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>De eigen vestigingenpagina bevestigt Spoorstraat 55H, 5831 CJ Boxmeer. Een Cubox-bron noemde postcode 5831 JC; de actuele eigen bron is leidend. De website presenteert Grafisch Huis van Mameren en Grafisch Huis Boxmeer als twee vestigingen en namen onder één merk en domein, en een externe sociale bron staat op naam van Grafisch Huis van Mameren B.V. Het is niet betrouwbaar vastgesteld welke juridische entiteit de Boxmeerse vestiging exploiteert, daarom Organisatienaam Onbekend. Handmatige beoordeling afgerond. Geen bruikbaar medewerkersaantal gevonden.</t>
+        </is>
+      </c>
     </row>
     <row r="30">
-      <c r="A30" s="2" t="n"/>
-      <c r="E30" s="2" t="n"/>
-      <c r="I30" s="2" t="n"/>
-      <c r="O30" s="3" t="n"/>
-      <c r="X30" s="2" t="n"/>
-      <c r="AB30" s="3" t="n"/>
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>L0029</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>MAAY Drukwerk</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>MAAY Group B.V.</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>https://www.maay-drukwerk.nl/contact/</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>Niet gevonden</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>maay-drukwerk.nl</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>https://www.maay-drukwerk.nl</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Boxmeer</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>5831 CM</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>Spoorstraat 40</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>Onbekend</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>Niet gevonden</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>Niet gevonden</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>Onbekend</t>
+        </is>
+      </c>
+      <c r="O30" s="3" t="inlineStr">
+        <is>
+          <t>Niet gevonden</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Actualiteit onduidelijk</t>
+        </is>
+      </c>
+      <c r="Q30" t="inlineStr">
+        <is>
+          <t>Onbekend</t>
+        </is>
+      </c>
+      <c r="R30" t="inlineStr">
+        <is>
+          <t>Onbekend</t>
+        </is>
+      </c>
+      <c r="S30" t="inlineStr">
+        <is>
+          <t>niet nodig</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>onbekend</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>nog niet te bepalen</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>info@maay.nl</t>
+        </is>
+      </c>
+      <c r="X30" s="2" t="inlineStr">
+        <is>
+          <t>0485 82 03 00</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>https://www.maay-drukwerk.nl/contact/</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>nog niet gecontroleerd</t>
+        </is>
+      </c>
+      <c r="AB30" s="3" t="n">
+        <v>46282</v>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>De eigen contactpagina voert MAAY Group B.V. als afzender, met bezoekadres Spoorstraat 40, 5831 CM Boxmeer. KvK 74160397 en vestigingsnummer 000042140315 zijn alleen via een C-bron gevonden en daarom niet als bewezen KVK overgenomen. Een C-bron noemt 2 personen; dat is alleen een indicatie en wordt niet gebruikt voor segmentatie. Geen bruikbaar medewerkersaantal uit een A- of B-bron. Commerciële relevantie voorlopig twijfel vanwege een mogelijk kleine organisatie.</t>
+        </is>
+      </c>
     </row>
     <row r="31">
-      <c r="A31" s="2" t="n"/>
-      <c r="E31" s="2" t="n"/>
-      <c r="I31" s="2" t="n"/>
-      <c r="O31" s="3" t="n"/>
-      <c r="X31" s="2" t="n"/>
-      <c r="AB31" s="3" t="n"/>
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>L0030</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Van Gemert Installatiegroep, vestiging Overloon</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Onbekend</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>https://www.vangemertbv.nl en https://www.vangemertbv.nl/contact</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>16058704</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>vangemertbv.nl</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>https://www.vangemertbv.nl</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Overloon</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>5825 HN</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>Oploseweg 12b</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>Onbekend</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>Niet gevonden</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>Niet gevonden</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>Onbekend</t>
+        </is>
+      </c>
+      <c r="O31" s="3" t="inlineStr">
+        <is>
+          <t>Niet gevonden</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Actualiteit onduidelijk</t>
+        </is>
+      </c>
+      <c r="Q31" t="inlineStr">
+        <is>
+          <t>Onbekend</t>
+        </is>
+      </c>
+      <c r="R31" t="inlineStr">
+        <is>
+          <t>Onbekend</t>
+        </is>
+      </c>
+      <c r="S31" t="inlineStr">
+        <is>
+          <t>afgerond</t>
+        </is>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>https://www.vangemertbv.nl, https://www.vangemertbv.nl/contact en https://www.vangemertbv.nl/onze-winkels/</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>onbekend</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>nog niet te bepalen</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>info@vangemertbv.nl</t>
+        </is>
+      </c>
+      <c r="X31" s="2" t="inlineStr">
+        <is>
+          <t>0478 50 71 71</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>https://www.vangemertbv.nl/contact</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>nog niet gecontroleerd</t>
+        </is>
+      </c>
+      <c r="AB31" s="3" t="n">
+        <v>46282</v>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>De eigen site bevestigt de vestiging Overloon aan Oploseweg 12b, 5825 HN; daarnaast bestaat een vestiging in Mill aan Karstraat 33. Van Gemert Installatiegroep maakt volgens de eigen site deel uit van De Groot Installatiegroep. De Groot is een operationele installatiegroep en geen zuivere holding, de contactpagina van Van Gemert is geïntegreerd met De Groot, en bestuurder is DGI Van Gemert B.V. Daardoor blijft de canonieke Organisatienaam volgens onze huidige organisatieregel Onbekend. Handmatige beoordeling afgerond. Twee C-bronnen noemen circa 70 respectievelijk 60 medewerkers; deze cijfers zijn niet gebruikt voor segmentatie. Eén A- of B-bron voor medewerkers zou mogelijk tot segment 50+ kunnen leiden. Voorlopig Segment onbekend.</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n"/>

--- a/data/HAHEBO_leadbestand_pilot.xlsx
+++ b/data/HAHEBO_leadbestand_pilot.xlsx
@@ -2432,7 +2432,7 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>Onbekend</t>
+          <t>Meer dan 300</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
@@ -2442,27 +2442,27 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
+          <t>https://www.boladviseurs.nl/over-bol/medewerkers</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="O15" s="3" t="inlineStr">
+        <is>
           <t>Niet gevonden</t>
         </is>
       </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>Onbekend</t>
-        </is>
-      </c>
-      <c r="O15" s="3" t="inlineStr">
-        <is>
-          <t>Niet gevonden</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Actualiteit onduidelijk</t>
+          <t>Actueel/live</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>Onbekend</t>
+          <t>Organisatie</t>
         </is>
       </c>
       <c r="R15" t="inlineStr">
@@ -2477,7 +2477,7 @@
       </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>onbekend</t>
+          <t>50+</t>
         </is>
       </c>
       <c r="V15" t="inlineStr">
@@ -2510,7 +2510,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Bol Adviseurs is volgens de eigen disclaimer een collectieve naam voor meerdere juridische entiteiten. Voor deze Boxmeer-lead is KVK 16064022 van Bol Accountants B.V. gebruikt, vestigingsnummer 000017116937. STAK Bol Accountants is een eigendoms-/holdingstructuur en is niet als Organisatienaam gebruikt. Er is geen betrouwbare A- of B-bron met een bruikbaar medewerkersaantal gevonden; een eerder aangetroffen C-bron met 1 medewerker is niet gebruikt voor segmentatie. Aantal medewerkers = Onbekend, Segment = onbekend. Telefoonnummer en e-mailadres zijn organisatiebrede contactgegevens; de officiële Boxmeer-locatiepagina bevestigt deze gegevens expliciet voor Spoorstraat 73. Bol International noemt een afwijkend generiek telefoonnummer en is daarom niet als primaire contactbron gebruikt. Acquisitielijst nog niet gecontroleerd.</t>
+          <t>Bol Adviseurs is volgens de eigen disclaimer een collectieve naam voor meerdere juridische entiteiten. Voor deze Boxmeer-lead is KVK 16064022 van Bol Accountants B.V. gebruikt, vestigingsnummer 000017116937. STAK Bol Accountants is een eigendoms-/holdingstructuur en is niet als Organisatienaam gebruikt. Er is geen betrouwbare A- of B-bron met een bruikbaar medewerkersaantal gevonden; een eerder aangetroffen C-bron met 1 medewerker is niet gebruikt voor segmentatie. Aantal medewerkers = Onbekend, Segment = onbekend. Telefoonnummer en e-mailadres zijn organisatiebrede contactgegevens; de officiële Boxmeer-locatiepagina bevestigt deze gegevens expliciet voor Spoorstraat 73. Bol International noemt een afwijkend generiek telefoonnummer en is daarom niet als primaire contactbron gebruikt. Acquisitielijst nog niet gecontroleerd. De eigen medewerkerspagina van Bol Adviseurs vermeldt actueel "meer dan 300 professionals". Dit cijfer heeft betrekking op Bol Adviseurs als organisatie en niet uitsluitend op locatie Boxmeer. De formulering is een persoonsaanduiding zonder expliciet fte-label; Eenheid medewerkers blijft daarom Onbekend. Omdat het betrouwbare organisatiecijfer ruim boven de grens van 50 ligt, is Segment vastgesteld op 50+.</t>
         </is>
       </c>
     </row>
@@ -4622,7 +4622,7 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>Onbekend</t>
+          <t>Ruim 60</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
@@ -4632,32 +4632,32 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
+          <t>https://www.vangemertbv.nl/over-ons</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="O31" s="3" t="inlineStr">
+        <is>
           <t>Niet gevonden</t>
         </is>
       </c>
-      <c r="N31" t="inlineStr">
-        <is>
-          <t>Onbekend</t>
-        </is>
-      </c>
-      <c r="O31" s="3" t="inlineStr">
-        <is>
-          <t>Niet gevonden</t>
-        </is>
-      </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Actualiteit onduidelijk</t>
+          <t>Actueel/live</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>Onbekend</t>
+          <t>Entiteit</t>
         </is>
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>Onbekend</t>
+          <t>Werkzame personen</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
@@ -4667,12 +4667,12 @@
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>https://www.vangemertbv.nl, https://www.vangemertbv.nl/contact en https://www.vangemertbv.nl/onze-winkels/</t>
+          <t>https://www.vangemertbv.nl, https://www.vangemertbv.nl/contact en https://www.vangemertbv.nl/onze-winkels/ en https://www.vangemertbv.nl/over-ons</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
         <is>
-          <t>onbekend</t>
+          <t>50+</t>
         </is>
       </c>
       <c r="V31" t="inlineStr">
@@ -4705,7 +4705,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>De eigen site bevestigt de vestiging Overloon aan Oploseweg 12b, 5825 HN; daarnaast bestaat een vestiging in Mill aan Karstraat 33. Van Gemert Installatiegroep maakt volgens de eigen site deel uit van De Groot Installatiegroep. De Groot is een operationele installatiegroep en geen zuivere holding, de contactpagina van Van Gemert is geïntegreerd met De Groot, en bestuurder is DGI Van Gemert B.V. Daardoor blijft de canonieke Organisatienaam volgens onze huidige organisatieregel Onbekend. Handmatige beoordeling afgerond. Twee C-bronnen noemen circa 70 respectievelijk 60 medewerkers; deze cijfers zijn niet gebruikt voor segmentatie. Eén A- of B-bron voor medewerkers zou mogelijk tot segment 50+ kunnen leiden. Voorlopig Segment onbekend.</t>
+          <t>De eigen site bevestigt de vestiging Overloon aan Oploseweg 12b, 5825 HN; daarnaast bestaat een vestiging in Mill aan Karstraat 33. Van Gemert Installatiegroep maakt volgens de eigen site deel uit van De Groot Installatiegroep. De Groot is een operationele installatiegroep en geen zuivere holding, de contactpagina van Van Gemert is geïntegreerd met De Groot, en bestuurder is DGI Van Gemert B.V. Daardoor blijft de canonieke Organisatienaam volgens onze huidige organisatieregel Onbekend. Handmatige beoordeling afgerond. De eigen over-ons-pagina van Van Gemert vermeldt actueel "ruim 60 betrokken medewerkers". Deze formulering heeft betrekking op Van Gemert zelf en onderscheidt Van Gemert expliciet van moederorganisatie De Groot Installatiegroep. Het cijfer wordt daarom als A-bron gebruikt op entiteitsniveau. "Betrokken medewerkers" betreft personen; Eenheid medewerkers = Werkzame personen. Het betrouwbare cijfer ligt boven de grens van 50, waardoor Segment = 50+. De eerder onderzochte optelling van losse teamgroottes uit vacaturepagina's is niet gebruikt voor deze segmentatie.</t>
         </is>
       </c>
     </row>

--- a/data/HAHEBO_leadbestand_pilot.xlsx
+++ b/data/HAHEBO_leadbestand_pilot.xlsx
@@ -2510,7 +2510,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Bol Adviseurs is volgens de eigen disclaimer een collectieve naam voor meerdere juridische entiteiten. Voor deze Boxmeer-lead is KVK 16064022 van Bol Accountants B.V. gebruikt, vestigingsnummer 000017116937. STAK Bol Accountants is een eigendoms-/holdingstructuur en is niet als Organisatienaam gebruikt. Er is geen betrouwbare A- of B-bron met een bruikbaar medewerkersaantal gevonden; een eerder aangetroffen C-bron met 1 medewerker is niet gebruikt voor segmentatie. Aantal medewerkers = Onbekend, Segment = onbekend. Telefoonnummer en e-mailadres zijn organisatiebrede contactgegevens; de officiële Boxmeer-locatiepagina bevestigt deze gegevens expliciet voor Spoorstraat 73. Bol International noemt een afwijkend generiek telefoonnummer en is daarom niet als primaire contactbron gebruikt. Acquisitielijst nog niet gecontroleerd. De eigen medewerkerspagina van Bol Adviseurs vermeldt actueel "meer dan 300 professionals". Dit cijfer heeft betrekking op Bol Adviseurs als organisatie en niet uitsluitend op locatie Boxmeer. De formulering is een persoonsaanduiding zonder expliciet fte-label; Eenheid medewerkers blijft daarom Onbekend. Omdat het betrouwbare organisatiecijfer ruim boven de grens van 50 ligt, is Segment vastgesteld op 50+.</t>
+          <t>Bol Adviseurs is volgens de eigen disclaimer een collectieve naam voor meerdere juridische entiteiten. Voor deze Boxmeer-lead is KVK 16064022 van Bol Accountants B.V. gebruikt, vestigingsnummer 000017116937. STAK Bol Accountants is een eigendoms-/holdingstructuur en is niet als Organisatienaam gebruikt. Er is geen betrouwbare A- of B-bron met een bruikbaar medewerkersaantal gevonden; een eerder aangetroffen C-bron met 1 medewerker is niet gebruikt voor segmentatie. Telefoonnummer en e-mailadres zijn organisatiebrede contactgegevens; de officiële Boxmeer-locatiepagina bevestigt deze gegevens expliciet voor Spoorstraat 73. Bol International noemt een afwijkend generiek telefoonnummer en is daarom niet als primaire contactbron gebruikt. Acquisitielijst nog niet gecontroleerd. De eigen medewerkerspagina van Bol Adviseurs vermeldt actueel "meer dan 300 professionals". Dit cijfer heeft betrekking op Bol Adviseurs als organisatie en niet uitsluitend op locatie Boxmeer. De formulering is een persoonsaanduiding zonder expliciet fte-label; Eenheid medewerkers blijft daarom Onbekend. Omdat het betrouwbare organisatiecijfer ruim boven de grens van 50 ligt, is Segment vastgesteld op 50+.</t>
         </is>
       </c>
     </row>

--- a/data/HAHEBO_leadbestand_pilot.xlsx
+++ b/data/HAHEBO_leadbestand_pilot.xlsx
@@ -1887,7 +1887,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>Onbekend</t>
+          <t>Ongeveer 75</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1897,12 +1897,12 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>Niet gevonden</t>
+          <t>https://sociom.nl/medewerkers/</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>Onbekend</t>
+          <t>A</t>
         </is>
       </c>
       <c r="O11" s="3" t="inlineStr">
@@ -1912,17 +1912,17 @@
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Actualiteit onduidelijk</t>
+          <t>Actueel/live</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>Onbekend</t>
+          <t>Organisatie</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>Onbekend</t>
+          <t>Werkzame personen</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>onbekend</t>
+          <t>50+</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
@@ -1965,7 +1965,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Geen bruikbaar medewerkersgegeven gevonden na toepassing van de vastgestelde stopregel. Ontbrekende data zijn op zichzelf geen reden voor handmatige beoordeling. Sociom werkt in Land van Cuijk en West Maas en Waal met meerdere locaties, waarvan De Weijer in Boxmeer er één is. Eén externe bron noemt De Raetsingel 5; het adres van de eigen site is aangehouden.</t>
+          <t>Geen bruikbaar medewerkersgegeven gevonden na toepassing van de vastgestelde stopregel. Ontbrekende data zijn op zichzelf geen reden voor handmatige beoordeling. Sociom werkt in Land van Cuijk en West Maas en Waal met meerdere locaties, waarvan De Weijer in Boxmeer er één is. Eén externe bron noemt De Raetsingel 5; het adres van de eigen site is aangehouden. De eigen medewerkerspagina van Sociom vermeldt actueel ongeveer 75 medewerkers, ruim 350 vrijwilligers en circa 50 stagiairs. Alleen de circa 75 medewerkers worden gebruikt voor segmentatie; vrijwilligers en stagiairs worden niet meegeteld. Het cijfer heeft betrekking op Sociom als organisatie, waarvan De Weijer Boxmeer een locatie is. Bronniveau = A, Meetniveau = Organisatie, Eenheid = Werkzame personen. Omdat het betrouwbare organisatiecijfer boven de grens van 50 ligt, is Segment vastgesteld op 50+.</t>
         </is>
       </c>
     </row>
